--- a/naver-place-crawler/results_nail/서대문_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/서대문_네일샵.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>네일소브 북가좌본점</t>
+          <t>아임모어 신촌점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>hbs2002i@naver.com</t>
+          <t>iam_more@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1448-3319</t>
+          <t>0507-1451-3414</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 거북골로 184 1층 좌측중앙(네일샵)</t>
+          <t>서울특별시 서대문구 명물길 6 9층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_sove</t>
+          <t>https://pf.kakao.com/_tauxad</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>105</v>
+        <v>1454</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>892</v>
       </c>
       <c r="R2" t="n">
-        <v>108</v>
+        <v>2346</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1192995175</t>
+          <t>387024661</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1192995175</t>
+          <t>https://m.place.naver.com/place/387024661</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,20 +658,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>프로젝트 앨리스</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>쏭뷰티샵</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>aryangjiu@naver.com</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1383-3681</t>
+          <t>070-8248-9565</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세검정로3길 38-2 1층</t>
+          <t>서울특별시 서대문구 세검정로1길 48 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -711,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1788377896</t>
+          <t>32284905</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1788377896</t>
+          <t>https://m.place.naver.com/place/32284905</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -748,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>수아라네일 가좌라운지점</t>
+          <t>미호네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>matata4@naver.com</t>
+          <t>kikijj0206@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1304-0817</t>
+          <t>02-303-4117</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 수색로 56 6층 609호</t>
+          <t>서울특별시 서대문구 가재울미래로 2 205동상가 104-2 미호네일</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/sooara0817</t>
+          <t>http://www.instagram.com/nail_in_miho</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -796,7 +800,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -805,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1640</v>
+        <v>10</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>1648</v>
+        <v>12</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1386960813</t>
+          <t>1494438581</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1386960813</t>
+          <t>https://m.place.naver.com/place/1494438581</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -842,30 +846,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일 아이보리</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>오늘네일</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>barbie0903@naver.com</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0507-1463-7021</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대5길 35 신촌영타운지웰에스테이트 상가동 2층 네일, 아이보리</t>
+          <t>서울특별시 서대문구 이화여대5길 9 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/770181/items/4634924</t>
+          <t>https://www.instagram.com/ilovetan_oneulnail</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -895,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>276</v>
+        <v>10</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -910,12 +914,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1572186883</t>
+          <t>1348096581</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1572186883</t>
+          <t>https://m.place.naver.com/place/1348096581</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -932,29 +936,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>굥뷰티</t>
+          <t>토드네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sunday020@naver.com</t>
+          <t>0728helen@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0505-685-7683</t>
+          <t>0507-1486-0620</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌역로 10</t>
+          <t>서울특별시 서대문구 이화여대5길 35 지하1층 114호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/todnail_</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -964,7 +968,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -980,22 +984,22 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>436</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>466</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,12 +1008,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1137345145</t>
+          <t>1674577867</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1137345145</t>
+          <t>https://m.place.naver.com/place/1674577867</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1026,29 +1030,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>공간네일 신촌점</t>
+          <t>꾸밈</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>tomi6@naver.com</t>
+          <t>hairccumim@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1367-0798</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 명물길 49 3층</t>
+          <t>서울특별시 서대문구 수색로2길 39 DMC금호리첸시아 상가 지하101호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://linktr.ee/gonggan_sc</t>
+          <t>http://www.instagram.com/ggoomim</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1074,22 +1074,22 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1759</v>
+        <v>289</v>
       </c>
       <c r="Q7" t="n">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="R7" t="n">
-        <v>1812</v>
+        <v>402</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1412908076</t>
+          <t>1649834362</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1412908076</t>
+          <t>https://m.place.naver.com/place/1649834362</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1120,29 +1120,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>포쉬네일 하이푸스 신촌점</t>
+          <t>루미가넷 현대백화점 신촌점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>freegirl11@naver.com</t>
+          <t>nuroonge@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1335-4241</t>
+          <t>0507-1461-9296</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 73 2층</t>
+          <t>서울특별시 서대문구 신촌로 83 현대백화점신촌점 3F</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sh_forsynail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1173,17 +1173,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3133</v>
+        <v>67</v>
       </c>
       <c r="Q8" t="n">
-        <v>337</v>
+        <v>14</v>
       </c>
       <c r="R8" t="n">
-        <v>3470</v>
+        <v>81</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1944620503</t>
+          <t>31229559</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1944620503</t>
+          <t>https://m.place.naver.com/place/31229559</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1214,25 +1214,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>코이네일</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>히카리 살롱 네일&amp;아이래쉬</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yeooonyummy@naver.com</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1494-6711</t>
+          <t>0507-1369-1853</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세검정로 46 1층 9호</t>
+          <t>서울특별시 서대문구 신촌로 109 지하1층 비112 히카리살롱</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/k.o.i.nail/</t>
+          <t>https://open.kakao.com/o/sY3GnTpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1258,7 +1262,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1267,13 +1271,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>163</v>
+        <v>433</v>
       </c>
       <c r="Q9" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="R9" t="n">
-        <v>182</v>
+        <v>460</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1282,12 +1286,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1956411597</t>
+          <t>1696710543</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1956411597</t>
+          <t>https://m.place.naver.com/place/1696710543</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1304,25 +1308,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>옌그리다</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>멜트네일</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ckckcl1357@naver.com</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1358-6121</t>
+          <t>0507-1323-6269</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 홍제내길 118 1층</t>
+          <t>서울특별시 서대문구 연희로 85 인사이드빌딩 1층 104호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCoLUjj2k9oeAU5y7IS50qOQ</t>
+          <t>https://www.instagram.com/melt_nail_/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,7 +1356,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1357,13 +1365,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>228</v>
+        <v>93</v>
       </c>
       <c r="Q10" t="n">
-        <v>212</v>
+        <v>10</v>
       </c>
       <c r="R10" t="n">
-        <v>440</v>
+        <v>103</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1372,12 +1380,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1611348671</t>
+          <t>1591157927</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611348671</t>
+          <t>https://m.place.naver.com/place/1591157927</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1394,26 +1402,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>아르젠떼네일</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>네일살롱</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>wing3527@naver.com</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1303-0241</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대8길 123 상가동 105호</t>
+          <t>서울특별시 서대문구 연희맛로 20 연희빌딩 1층 1호네일실롱</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_kqfCG</t>
+          <t>http://instagram.com/nailsalon7775</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1434,22 +1450,22 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="R11" t="n">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1458,12 +1474,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1142718935</t>
+          <t>1527535605</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1142718935</t>
+          <t>https://m.place.naver.com/place/1527535605</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1480,25 +1496,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>썸네일</t>
+          <t>온더네일스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>hackerstalk11@naver.com</t>
+          <t>k14150@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1330-5812</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대길 58</t>
+          <t>서울특별시 서대문구 통일로 400 2F</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/_onthenails</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1508,7 +1528,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1529,17 +1549,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>142</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1548,12 +1568,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1217647474</t>
+          <t>1484695115</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1217647474</t>
+          <t>https://m.place.naver.com/place/1484695115</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1570,25 +1590,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>제이앤제이네일</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>네일뿐</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>cuiyushan20-19@naver.com</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1342-8430</t>
+          <t>0507-1487-1503</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 402 1층 제이엔제이네일</t>
+          <t>서울특별시 서대문구 신촌로 127 2층 205호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_fMNYxj</t>
+          <t>http://pf.kakao.com/_Fhxemxj</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1623,13 +1647,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="Q13" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="R13" t="n">
-        <v>127</v>
+        <v>33</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1638,12 +1662,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1722436082</t>
+          <t>1627245540</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722436082</t>
+          <t>https://m.place.naver.com/place/1627245540</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1660,34 +1684,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>네일써니데이</t>
+          <t>제이앤제이네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>songhs1226@naver.com</t>
+          <t>sallyhome_@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1403-0327</t>
+          <t>0507-1342-8430</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로10길 48-6 101호</t>
+          <t>서울특별시 서대문구 통일로 402 1층 제이엔제이네일</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_s.day</t>
+          <t>http://pf.kakao.com/_fMNYxj</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1708,7 +1732,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1717,13 +1741,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>220</v>
+        <v>78</v>
       </c>
       <c r="Q14" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="R14" t="n">
-        <v>228</v>
+        <v>127</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1732,12 +1756,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1324725520</t>
+          <t>1722436082</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324725520</t>
+          <t>https://m.place.naver.com/place/1722436082</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1754,29 +1778,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>네일, 여유</t>
+          <t>오드리네일</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>knl_95@naver.com</t>
+          <t>ardusy@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1433-1620</t>
+          <t>0507-1407-8532</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 간호대로2길 9 1층</t>
+          <t>서울특별시 서대문구 거북골로 84 상가2동 108호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail.healing_</t>
+          <t>https://www.instagram.com/audreynail__</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1811,13 +1835,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>179</v>
+        <v>77</v>
       </c>
       <c r="Q15" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>211</v>
+        <v>79</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1826,12 +1850,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1492064846</t>
+          <t>1472183656</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1492064846</t>
+          <t>https://m.place.naver.com/place/1472183656</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1848,25 +1872,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>소소람</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>리본 네일</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>feelringhair@naver.com</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1312-4806</t>
+          <t>0507-1445-1169</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로28길 18 1층</t>
+          <t>서울특별시 서대문구 이화여대길 33 2층 리본네일</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_sosoram</t>
+          <t>https://blog.naver.com/feelringhair</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1881,7 +1909,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1901,13 +1929,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>34</v>
+        <v>644</v>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>439</v>
       </c>
       <c r="R16" t="n">
-        <v>40</v>
+        <v>1083</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1916,12 +1944,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2044971493</t>
+          <t>1561804134</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2044971493</t>
+          <t>https://m.place.naver.com/place/1561804134</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1938,29 +1966,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>뮤즈네일</t>
+          <t>네일띵크</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>jiji012636@naver.com</t>
+          <t>goqlsl7895@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1300-4636</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 인왕시장길 18</t>
+          <t>서울특별시 서대문구 연희로11가길 36 신관 1층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jiji012636</t>
+          <t>https://open.kakao.com/o/snfSrVOh</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1975,7 +1999,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1986,7 +2010,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1995,13 +2019,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="Q17" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2010,12 +2034,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1179732435</t>
+          <t>1472586988</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1179732435</t>
+          <t>https://m.place.naver.com/place/1472586988</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2032,29 +2056,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>쏭뷰티샵</t>
+          <t>더 꼼네일</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>aryangjiu@naver.com</t>
+          <t>kjuuu0716@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>070-8248-9565</t>
+          <t>0507-1322-3992</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세검정로1길 48 1층</t>
+          <t>서울특별시 서대문구 명지대길 56 1층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/the_kkom</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2064,7 +2088,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2085,17 +2109,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2104,12 +2128,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>32284905</t>
+          <t>1616221232</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32284905</t>
+          <t>https://m.place.naver.com/place/1616221232</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2126,29 +2150,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>루나네일</t>
+          <t>글리밍네일</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>lunamika@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1329-7109</t>
+          <t>02-312-7769</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 가재울미래로 15 1층 103호 루나네일</t>
+          <t>서울특별시 서대문구 신촌로35길 10 e편한세상신촌상가 지하1층 글리밍네일</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>http://instagram.com/lunarnail__</t>
+          <t>http://www.instagram.com/gleaming_nail</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2183,13 +2207,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="R19" t="n">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2198,12 +2222,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1427499799</t>
+          <t>302039845</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1427499799</t>
+          <t>https://m.place.naver.com/place/302039845</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2220,25 +2244,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>네일도행운</t>
+          <t>메리네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>stellacafe@naver.com</t>
+          <t>qaqzqsaw2@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>02-303-1194</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 모래내로 245 2층 더미뷰티 내부</t>
+          <t>서울특별시 서대문구 증가로 143</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luck__with_nail?igsh=aWltam43aTkwdDJu&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2248,7 +2276,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2264,22 +2292,22 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2288,12 +2316,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2049561266</t>
+          <t>13492671</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2049561266</t>
+          <t>https://m.place.naver.com/place/13492671</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2310,25 +2338,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>네일미야오</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>제이네일</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>rhkdmswl@naver.com</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1471-2420</t>
+          <t>0507-1329-0346</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌역로 17 203호</t>
+          <t>서울특별시 서대문구 독립문공원길 13 독립문극동아파트</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailmeow.2025?igsh=NDNhbmw0ZGgxN3d0</t>
+          <t>https://www.instagram.com/j_nail_2503</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2363,13 +2395,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R21" t="n">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2378,12 +2410,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1516469775</t>
+          <t>321319088</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1516469775</t>
+          <t>https://m.place.naver.com/place/321319088</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2400,34 +2432,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>네일까사</t>
+          <t>네일 아이보리</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ptypoohpooh0820@naver.com</t>
+          <t>052young@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1404-1654</t>
+          <t>0507-1463-7021</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로4길 28 2F</t>
+          <t>서울특별시 서대문구 이화여대5길 35 신촌영타운지웰에스테이트 상가동 2층 네일, 아이보리</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nailcasa</t>
+          <t>https://booking.naver.com/booking/13/bizes/770181/items/4634924</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2457,13 +2489,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="Q22" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="R22" t="n">
-        <v>304</v>
+        <v>276</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2472,12 +2504,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>38015918</t>
+          <t>1572186883</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38015918</t>
+          <t>https://m.place.naver.com/place/1572186883</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2494,29 +2526,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>미호네일</t>
+          <t>달달한네일</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>kikijj0206@naver.com</t>
+          <t>nail0danji@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>02-303-4117</t>
+          <t>0507-1433-3262</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 가재울미래로 2 205동상가 104-2 미호네일</t>
+          <t>서울특별시 서대문구 세무서2길 16 1층 2호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_in_miho</t>
+          <t>https://www.instagram.com/thedaldalnail</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2542,7 +2574,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2551,13 +2583,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>10</v>
+        <v>233</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="R23" t="n">
-        <v>12</v>
+        <v>323</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2566,12 +2598,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1494438581</t>
+          <t>1257856428</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1494438581</t>
+          <t>https://m.place.naver.com/place/1257856428</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2588,29 +2620,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>위드앤네일</t>
+          <t>BK맨즈네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jelly0355@naver.com</t>
+          <t>bkmensnail@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1322-3690</t>
+          <t>02-365-7449</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 510 상가212호 위드앤네일</t>
+          <t>서울특별시 서대문구 이화여대길 82 3층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/_with_n_nail_</t>
+          <t>https://blog.naver.com/bkmensnail</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2625,7 +2657,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2645,13 +2677,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="R24" t="n">
-        <v>22</v>
+        <v>337</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2660,12 +2692,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1070279609</t>
+          <t>1573880950</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1070279609</t>
+          <t>https://m.place.naver.com/place/1573880950</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2682,20 +2714,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>행복한 네일</t>
+          <t>프로젝트 앨리스</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>etbjj@naver.com</t>
+          <t>uer1130@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1383-3681</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로 204 상가동 1층 105호</t>
+          <t>서울특별시 서대문구 세검정로3길 38-2 1층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2735,13 +2771,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2750,12 +2786,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2064316137</t>
+          <t>1788377896</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2064316137</t>
+          <t>https://m.place.naver.com/place/1788377896</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2772,35 +2808,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>에스뷰티</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>메이퀸네일살롱</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ogsohd@naver.com</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0507-1478-9939</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로4길 58-11 1층</t>
+          <t>서울특별시 서대문구 신촌로 169-7 이대포레스트 1층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/936347</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2825,13 +2861,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2840,12 +2876,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1456809966</t>
+          <t>82617755</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1456809966</t>
+          <t>https://m.place.naver.com/place/82617755</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2862,21 +2898,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>스윕네일</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>BK민방경네일</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>acquidigio7@naver.com</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>02-393-7449</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대5길 35 지하1층 104호</t>
+          <t>서울특별시 서대문구 이화여대길 82 2층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sweepnail/</t>
+          <t>https://blog.naver.com/acquidigio7</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2891,7 +2935,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2911,13 +2955,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>178</v>
+        <v>553</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>1153</v>
       </c>
       <c r="R27" t="n">
-        <v>181</v>
+        <v>1706</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2926,12 +2970,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1462276902</t>
+          <t>38314950</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1462276902</t>
+          <t>https://m.place.naver.com/place/38314950</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2948,29 +2992,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>더 꼼네일</t>
+          <t>더블유네일</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>kjuuu0716@naver.com</t>
+          <t>ybbbbinn@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1322-3992</t>
+          <t>02-335-4321</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 명지대길 56 1층</t>
+          <t>서울특별시 서대문구 연희로4길 9 1충</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://instagram.com/the_kkom</t>
+          <t>http://instagram.com/private_nailsalon_w</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3005,13 +3049,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>146</v>
+        <v>5</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3020,12 +3064,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1616221232</t>
+          <t>20322720</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1616221232</t>
+          <t>https://m.place.naver.com/place/20322720</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3042,25 +3086,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>네일오엔</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>마요네일</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ynh3377@naver.com</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0507-1362-3291</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로7길 58 102호</t>
+          <t>서울특별시 서대문구 연희로11가길 33-3 1층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.oen?igsh=c2poN3MxZG5kcmR1&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/mayonail_official</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3086,7 +3130,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3095,13 +3139,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R29" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3110,12 +3154,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1478444590</t>
+          <t>1434998291</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1478444590</t>
+          <t>https://m.place.naver.com/place/1434998291</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3132,25 +3176,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>컬러라운지 네일&amp;태닝</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>뮤즈네일</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>jiji012636@naver.com</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>02-395-1196</t>
+          <t>0507-1300-4636</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 461 2층</t>
+          <t>서울특별시 서대문구 인왕시장길 18</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/jiji012636</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3160,12 +3208,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3181,17 +3229,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P30" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q30" t="n">
         <v>14</v>
       </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
       <c r="R30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3200,12 +3248,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>13118581</t>
+          <t>1179732435</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13118581</t>
+          <t>https://m.place.naver.com/place/1179732435</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3222,25 +3270,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>로지네일</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>루나네일</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>lunamika@naver.com</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1387-0314</t>
+          <t>0507-1329-7109</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로7안길 1 3층 로지네일</t>
+          <t>서울특별시 서대문구 가재울미래로 15 1층 103호 루나네일</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/rosy___nail</t>
+          <t>http://instagram.com/lunarnail__</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3275,13 +3327,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>292</v>
+        <v>10</v>
       </c>
       <c r="Q31" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>320</v>
+        <v>10</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3290,12 +3342,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1244771586</t>
+          <t>1427499799</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1244771586</t>
+          <t>https://m.place.naver.com/place/1427499799</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3312,30 +3364,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>로렐네일</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>네일뷰</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>darkyoon85@naver.com</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0507-1436-9020</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대3길 45 리브하임 B1층 로렐</t>
+          <t>서울특별시 서대문구 증가로32안길 82 1층 101호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xcXaxgn/friend</t>
+          <t>https://www.instagram.com/nailview__</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3356,7 +3408,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3365,13 +3417,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>233</v>
+        <v>41</v>
       </c>
       <c r="Q32" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>319</v>
+        <v>41</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3380,12 +3432,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1883098019</t>
+          <t>2068137219</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1883098019</t>
+          <t>https://m.place.naver.com/place/2068137219</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3402,29 +3454,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>아띠네일</t>
+          <t>행복한 네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>attinail_@naver.com</t>
+          <t>etbjj@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0507-1322-6612</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 193 2층 아띠네일</t>
+          <t>서울특별시 서대문구 연희로 204 상가동 1층 105호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/addi_nail_/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3434,7 +3482,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3455,17 +3503,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>344</v>
+        <v>81</v>
       </c>
       <c r="Q33" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>385</v>
+        <v>81</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3474,12 +3522,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1631947370</t>
+          <t>2064316137</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1631947370</t>
+          <t>https://m.place.naver.com/place/2064316137</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3496,29 +3544,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>시즈닝네일</t>
+          <t>보석</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>blue991013@naver.com</t>
+          <t>marble1120@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1362-1065</t>
+          <t>02-322-1915</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로40길 28</t>
+          <t>서울특별시 서대문구 연희로15안길 6</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/blue991013</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3528,12 +3576,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3549,17 +3597,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>155</v>
+        <v>10</v>
       </c>
       <c r="Q34" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="R34" t="n">
-        <v>207</v>
+        <v>12</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3568,12 +3616,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1888898614</t>
+          <t>992322635</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1888898614</t>
+          <t>https://m.place.naver.com/place/992322635</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3590,34 +3638,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>네일바이엔 이대역본점</t>
+          <t>네일 블라썸</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>makeup_byn@naver.com</t>
+          <t>wilklove@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1316-9910</t>
+          <t>0507-1324-7644</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 169-7 이대 포레스트 1층 105호</t>
+          <t>서울특별시 서대문구 세검정로1길 39 풍림2차아파트 상가동 241호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>http://instagram.com/arim_happy</t>
+          <t>https://naver.me/FRL0RGyl</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3643,17 +3691,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>665</v>
+        <v>74</v>
       </c>
       <c r="Q35" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="R35" t="n">
-        <v>695</v>
+        <v>111</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3662,12 +3710,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1282451640</t>
+          <t>1423228794</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1282451640</t>
+          <t>https://m.place.naver.com/place/1423228794</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3684,29 +3732,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>수네일</t>
+          <t>네일이끌림</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>yjh1000j@naver.com</t>
+          <t>nail_drag@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1332-4612</t>
+          <t>02-393-9948</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로10길 16-20 1층</t>
+          <t>서울특별시 서대문구 신촌로35길 10</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lovely.sunail</t>
+          <t>https://www.instagram.com/cong__vely</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3741,13 +3789,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>334</v>
+        <v>49</v>
       </c>
       <c r="Q36" t="n">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="R36" t="n">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3756,12 +3804,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1027173445</t>
+          <t>1698891603</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027173445</t>
+          <t>https://m.place.naver.com/place/1698891603</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3778,29 +3826,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>루미가넷 현대백화점 신촌점</t>
+          <t>네일온</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>nuroonge@naver.com</t>
+          <t>nailon22@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1461-9296</t>
+          <t>0507-1331-5593</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 83 현대백화점신촌점 3F</t>
+          <t>서울특별시 서대문구 충정로9길 4 2층(충정로2가)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/nailon22</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3810,12 +3858,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3831,17 +3879,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>67</v>
+        <v>447</v>
       </c>
       <c r="Q37" t="n">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="R37" t="n">
-        <v>81</v>
+        <v>578</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3850,12 +3898,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>31229559</t>
+          <t>1272307920</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31229559</t>
+          <t>https://m.place.naver.com/place/1272307920</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3872,30 +3920,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>마디마다네일</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>안젤리크네일</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>webmore@naver.com</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1326-2539</t>
+          <t>070-8648-3432</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 149 206호</t>
+          <t>서울특별시 서대문구 북아현동 199-1 힐스테이트신촌상가 105호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/madi_mada_nail/</t>
+          <t>http://pf.kakao.com/_qZgeb</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3916,22 +3968,22 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>804</v>
+        <v>41</v>
       </c>
       <c r="Q38" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>821</v>
+        <v>44</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3940,12 +3992,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1156545059</t>
+          <t>1976256692</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156545059</t>
+          <t>https://m.place.naver.com/place/1976256692</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -3962,29 +4014,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>릴리네일</t>
+          <t>아이원네일아트</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jain_im_@naver.com</t>
+          <t>fpwlsk8877@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0507-1350-0862</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로39가길 27</t>
+          <t>서울특별시 서대문구 연세로5길 38 1층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lily.s_nail_studio</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3994,7 +4042,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4015,17 +4063,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>198</v>
+        <v>148</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R39" t="n">
-        <v>201</v>
+        <v>152</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4034,12 +4082,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1863831189</t>
+          <t>1544991635</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1863831189</t>
+          <t>https://m.place.naver.com/place/1544991635</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4056,34 +4104,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일 블라썸</t>
+          <t>네일살롱무아</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>wilklove@naver.com</t>
+          <t>min_0_97@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1324-7644</t>
+          <t>0507-1436-1705</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세검정로1길 39 풍림2차아파트 상가동 241호</t>
+          <t>서울특별시 서대문구 신촌로 109 신촌르메이에르타운 5차 1층 110-1-2</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://naver.me/FRL0RGyl</t>
+          <t>https://www.instagram.com/nailmuah_</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4109,17 +4157,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="Q40" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="R40" t="n">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4128,12 +4176,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1423228794</t>
+          <t>1027772524</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1423228794</t>
+          <t>https://m.place.naver.com/place/1027772524</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4150,35 +4198,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일살롱무아</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>네일올리브 신촌 연대캠퍼스점</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>cxdbs@naver.com</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1436-1705</t>
+          <t>02-2123-8273</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 109 신촌르메이에르타운 5차 1층 110-1-2</t>
+          <t>서울특별시 서대문구 연세로 50 연세대학교 내 국제학사 지하 2층</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailmuah_</t>
+          <t>http://www.nailolive.com/</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4199,17 +4251,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="Q41" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4218,12 +4270,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1027772524</t>
+          <t>13332586</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027772524</t>
+          <t>https://m.place.naver.com/place/13332586</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4240,25 +4292,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>글리밍네일</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>공간네일 신촌점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>tomi6@naver.com</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>02-312-7769</t>
+          <t>0507-1367-0798</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로35길 10 e편한세상신촌상가 지하1층 글리밍네일</t>
+          <t>서울특별시 서대문구 명물길 49 3층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/gleaming_nail</t>
+          <t>https://linktr.ee/gonggan_sc</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4273,7 +4329,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4284,22 +4340,22 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>61</v>
+        <v>1760</v>
       </c>
       <c r="Q42" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="R42" t="n">
-        <v>104</v>
+        <v>1813</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4308,12 +4364,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>302039845</t>
+          <t>1412908076</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/302039845</t>
+          <t>https://m.place.naver.com/place/1412908076</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4330,34 +4386,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>네일소솜</t>
+          <t>더네일</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>wnzhd1203@naver.com</t>
+          <t>thenail_@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0507-1430-3550</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대길 88-15 1층 왼편점포호</t>
+          <t>서울특별시 서대문구 서소문로 43-22 한흥빌딩 2층 더 네일</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailsosom</t>
+          <t>https://pf.kakao.com/_mYaaxl</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4378,7 +4430,7 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4387,13 +4439,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R43" t="n">
-        <v>220</v>
+        <v>102</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4402,12 +4454,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1529665185</t>
+          <t>1800993616</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1529665185</t>
+          <t>https://m.place.naver.com/place/1800993616</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4424,29 +4476,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>네일에비뉴_연세대</t>
+          <t>오늘도네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>dyk6614@naver.com</t>
+          <t>j2lang@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1377-0744</t>
+          <t>02-6364-4901</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로 50 학생회관 지하1층 헤어에비뉴 內 네일에비뉴</t>
+          <t>서울특별시 서대문구 충정로 7</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/nail2day</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4456,7 +4508,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4477,17 +4529,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4496,12 +4548,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1303420092</t>
+          <t>1277557209</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1303420092</t>
+          <t>https://m.place.naver.com/place/1277557209</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4518,29 +4570,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>영네일</t>
+          <t>로지네일</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>youngnail423@naver.com</t>
+          <t>wonderfuuul@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1368-4230</t>
+          <t>0507-1387-0314</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 109 르메이에르타운5 B103-3</t>
+          <t>서울특별시 서대문구 연세로7안길 1 3층 로지네일</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/youngnail423</t>
+          <t>http://www.instagram.com/rosy___nail</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4555,7 +4607,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4575,13 +4627,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>59</v>
+        <v>292</v>
       </c>
       <c r="Q45" t="n">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="R45" t="n">
-        <v>126</v>
+        <v>320</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4590,12 +4642,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>36505109</t>
+          <t>1244771586</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36505109</t>
+          <t>https://m.place.naver.com/place/1244771586</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4612,25 +4664,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>히카리 살롱 네일&amp;아이래쉬</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>위드앤네일</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>jelly0355@naver.com</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1369-1853</t>
+          <t>0507-1322-3690</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 109 지하1층 비112 히카리살롱</t>
+          <t>서울특별시 서대문구 통일로 510 상가212호 위드앤네일</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sY3GnTpg</t>
+          <t>http://www.instagram.com/_with_n_nail_</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4656,7 +4712,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4665,13 +4721,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>433</v>
+        <v>22</v>
       </c>
       <c r="Q46" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>460</v>
+        <v>22</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4680,12 +4736,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1696710543</t>
+          <t>1070279609</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1696710543</t>
+          <t>https://m.place.naver.com/place/1070279609</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4702,12 +4758,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>수네일</t>
+          <t>숨네일</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>yjh1000j@naver.com</t>
+          <t>traineran@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -4715,12 +4771,12 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세검정로1길 50 1층 수네일</t>
+          <t>서울특별시 서대문구 홍은중앙로 100-2 1층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>http://instagram.com/soonail_kim</t>
+          <t>https://www.instagram.com/sumnail9901</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4755,13 +4811,13 @@
         </is>
       </c>
       <c r="P47" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q47" t="n">
         <v>1</v>
       </c>
-      <c r="Q47" t="n">
-        <v>16</v>
-      </c>
       <c r="R47" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4770,12 +4826,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1835439095</t>
+          <t>1326174975</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835439095</t>
+          <t>https://m.place.naver.com/place/1326174975</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4792,30 +4848,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>꾸밈</t>
+          <t>비포유</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>hairccumim@naver.com</t>
+          <t>hansse_db@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1313-6448</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 수색로2길 39 DMC금호리첸시아 상가 지하101호</t>
+          <t>서울특별시 서대문구 가재울미래로 2 203동 104-2호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/ggoomim</t>
+          <t>http://pf.kakao.com/_IrLMG</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4836,7 +4896,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4845,13 +4905,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="Q48" t="n">
-        <v>113</v>
+        <v>16</v>
       </c>
       <c r="R48" t="n">
-        <v>402</v>
+        <v>280</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4860,12 +4920,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1649834362</t>
+          <t>1150022642</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1649834362</t>
+          <t>https://m.place.naver.com/place/1150022642</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4882,29 +4942,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>오네일드잇 신촌점</t>
+          <t>옌그리다</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>travelsudal@naver.com</t>
+          <t>tmfddd@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1379-5740</t>
+          <t>0507-1358-6121</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 123 2층</t>
+          <t>서울특별시 서대문구 홍제내길 118 1층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oh_nailed_it</t>
+          <t>https://youtube.com/channel/UCoLUjj2k9oeAU5y7IS50qOQ</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4939,13 +4999,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>602</v>
+        <v>228</v>
       </c>
       <c r="Q49" t="n">
-        <v>9</v>
+        <v>212</v>
       </c>
       <c r="R49" t="n">
-        <v>611</v>
+        <v>440</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -4954,12 +5014,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1930241791</t>
+          <t>1611348671</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1930241791</t>
+          <t>https://m.place.naver.com/place/1611348671</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -4976,29 +5036,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>지젤네일</t>
+          <t>네일 소아나</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>shinesparis@naver.com</t>
+          <t>missyou106@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1339-4329</t>
+          <t>0507-1363-1483</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌역로 16 1층 104-1호 지젤네일</t>
+          <t>서울특별시 서대문구 이화여대5길 35 지하1층 104호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://booking.kakao.com/short/lBeB2nWTzo</t>
+          <t>http://pf.kakao.com/_VExgxmn</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5024,7 +5084,7 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5033,13 +5093,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="Q50" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R50" t="n">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5048,12 +5108,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1215364308</t>
+          <t>2057189903</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1215364308</t>
+          <t>https://m.place.naver.com/place/2057189903</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5070,25 +5130,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>네일도Nail</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>빔빔네일</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>yznnim@naver.com</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1444-2889</t>
+          <t>0507-1406-5642</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 109 (신촌르메이에르타운)B109-1 네일도Nail</t>
+          <t>서울특별시 서대문구 세무서길 77 1층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sIQTg2Uc</t>
+          <t>http://www.instagram.com/beam2nail</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5114,7 +5178,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5123,13 +5187,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="Q51" t="n">
-        <v>121</v>
+        <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>176</v>
+        <v>21</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5138,12 +5202,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1887906221</t>
+          <t>84828356</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1887906221</t>
+          <t>https://m.place.naver.com/place/84828356</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5160,34 +5224,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>알지네일</t>
+          <t>원더네일</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>handsos@naver.com</t>
+          <t>noweunn@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1352-1908</t>
+          <t>0507-1360-1515</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로31길 9</t>
+          <t>서울특별시 서대문구 독립문로12길 2</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>http://instagram.com/r.g_nail</t>
+          <t>http://pf.kakao.com/_xczxmaj</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5208,7 +5272,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5217,13 +5281,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="Q52" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="R52" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5232,12 +5296,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>32528538</t>
+          <t>37196672</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32528538</t>
+          <t>https://m.place.naver.com/place/37196672</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5254,25 +5318,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>네일, 온미</t>
+          <t>로뎀스킨케어</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>cjsdks518@naver.com</t>
+          <t>bealove0508@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>02-303-9955</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세검정로 93 . 1층 네일샵</t>
+          <t>서울특별시 서대문구 응암로 77</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_onme_/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5282,7 +5350,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5303,17 +5371,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Q53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5322,12 +5390,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1881659470</t>
+          <t>1985190980</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1881659470</t>
+          <t>https://m.place.naver.com/place/1985190980</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5344,30 +5412,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>동네살롱</t>
+          <t>안씨네일</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>hoteltt@naver.com</t>
+          <t>an_c_nail@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1352-3893</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 가재울로6길 53-55 1층</t>
+          <t>서울특별시 서대문구 통일로35길 66 1층 103호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>http://instagram.com/dn.salon</t>
+          <t>http://pf.kakao.com/_rxoxiqX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5388,7 +5460,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5397,13 +5469,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>49</v>
+        <v>376</v>
       </c>
       <c r="Q54" t="n">
-        <v>13</v>
+        <v>247</v>
       </c>
       <c r="R54" t="n">
-        <v>62</v>
+        <v>623</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5412,12 +5484,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1209907072</t>
+          <t>1657626219</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1209907072</t>
+          <t>https://m.place.naver.com/place/1657626219</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5434,25 +5506,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>네일띵크</t>
+          <t>네일에비뉴_연세대</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>goqlsl7895@naver.com</t>
+          <t>dyk6614@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1377-0744</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로11가길 36 신관 1층</t>
+          <t>서울특별시 서대문구 연세로 50 학생회관 지하1층 헤어에비뉴 內 네일에비뉴</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/snfSrVOh</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5462,7 +5538,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5478,22 +5554,22 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5502,12 +5578,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1472586988</t>
+          <t>1303420092</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1472586988</t>
+          <t>https://m.place.naver.com/place/1303420092</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5524,21 +5600,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>미뜨네일</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>유네일</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>luvu1016@naver.com</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1412-2114</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로10길 16-6 미뜨네일</t>
+          <t>서울특별시 서대문구 증가로24마길 47 1층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/meett_nail</t>
+          <t>https://www.instagram.com/_u_nail_</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5573,13 +5657,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="Q56" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="R56" t="n">
-        <v>199</v>
+        <v>267</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5588,12 +5672,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1274572984</t>
+          <t>1610895712</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1274572984</t>
+          <t>https://m.place.naver.com/place/1610895712</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5610,12 +5694,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>네일홍</t>
+          <t>미뜨네일</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>jjanga4774@naver.com</t>
+          <t>annykoh@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -5623,12 +5707,12 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 서소문로 21 충정타워빌딩 지하1층</t>
+          <t>서울특별시 서대문구 증가로10길 16-6 미뜨네일</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jjanga4774</t>
+          <t>https://www.instagram.com/meett_nail</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5643,7 +5727,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5659,17 +5743,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>126</v>
+        <v>198</v>
       </c>
       <c r="Q57" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>151</v>
+        <v>199</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5678,12 +5762,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>35624131</t>
+          <t>1274572984</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35624131</t>
+          <t>https://m.place.naver.com/place/1274572984</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5700,21 +5784,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>마요네일</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>굥뷰티</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>sunday020@naver.com</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0505-685-7683</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로11가길 33-3 1층</t>
+          <t>서울특별시 서대문구 신촌역로 10</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mayonail_official</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5724,7 +5816,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5745,17 +5837,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5764,12 +5856,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1434998291</t>
+          <t>1137345145</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1434998291</t>
+          <t>https://m.place.naver.com/place/1137345145</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5786,29 +5878,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>네일온</t>
+          <t>세컨드네일</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>dlgksmf3595@naver.com</t>
+          <t>nail2nd@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1412-0791</t>
+          <t>0507-1395-7369</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 불광천길 264 1층좌측</t>
+          <t>서울특별시 서대문구 홍연길 69 1층 세컨드네일</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailon_0790</t>
+          <t>https://www.instagram.com/xecond_nail</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5843,13 +5935,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>35</v>
+        <v>206</v>
       </c>
       <c r="Q59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R59" t="n">
-        <v>37</v>
+        <v>211</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5858,12 +5950,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1376233513</t>
+          <t>1131608621</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1376233513</t>
+          <t>https://m.place.naver.com/place/1131608621</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -5880,25 +5972,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>빔빔네일</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>동네살롱</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>hoteltt@naver.com</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0507-1406-5642</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세무서길 77 1층</t>
+          <t>서울특별시 서대문구 가재울로6길 53-55 1층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/beam2nail</t>
+          <t>http://instagram.com/dn.salon</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5933,13 +6025,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="Q60" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R60" t="n">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -5948,12 +6040,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>84828356</t>
+          <t>1209907072</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/84828356</t>
+          <t>https://m.place.naver.com/place/1209907072</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -5970,29 +6062,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>풋케어 로미네일</t>
+          <t>아띠네일</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>kangsogood@naver.com</t>
+          <t>attinail_@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1301-6236</t>
+          <t>0507-1322-6612</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 139 2층 좌측호</t>
+          <t>서울특별시 서대문구 통일로 193 2층 아띠네일</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/footcare_romi_nail?igsh=cjVmanNvMWZ5OGRt</t>
+          <t>http://www.instagram.com/addi_nail_/</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6027,13 +6119,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>7</v>
+        <v>345</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="R61" t="n">
-        <v>7</v>
+        <v>386</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6042,12 +6134,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>2080263501</t>
+          <t>1631947370</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2080263501</t>
+          <t>https://m.place.naver.com/place/1631947370</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6064,29 +6156,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>위드네일</t>
+          <t>꽃물 네일 &amp; 속눈썹 &amp; 왁싱</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>hahaha_1226@naver.com</t>
+          <t>ddalgy00@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1308-2035</t>
+          <t>02-394-4141</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 홍제천로 158 1층</t>
+          <t>서울특별시 서대문구 통일로 420 2층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/with.nail_</t>
+          <t>https://www.instagram.com/kina8843/</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6112,7 +6204,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6121,13 +6213,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R62" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6136,12 +6228,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>2099359388</t>
+          <t>882778770</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099359388</t>
+          <t>https://m.place.naver.com/place/882778770</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6158,25 +6250,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>메리제이네일</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>살롱드선네일</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>jam_d@naver.com</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1424-8411</t>
+          <t>0507-1338-2605</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 거북골로 120 제상가 2동 2층 13호</t>
+          <t>서울특별시 서대문구 북아현로1가길 20 이편한세상신촌 1단지상가 110호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://instagram.com/merry_j_nail</t>
+          <t>http://instagram.com/salonde_seon</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6211,13 +6307,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>109</v>
+        <v>426</v>
       </c>
       <c r="Q63" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R63" t="n">
-        <v>112</v>
+        <v>438</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6226,12 +6322,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>42246094</t>
+          <t>1688455455</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/42246094</t>
+          <t>https://m.place.naver.com/place/1688455455</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6248,29 +6344,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BK민방경네일</t>
+          <t>디디뷰티</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>acquidigio7@naver.com</t>
+          <t>ddb0301@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>02-393-7449</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대길 82 2층</t>
+          <t>서울특별시 서대문구 세무서8길 30 상가 B1(2층) 41호 디디뷰티</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/acquidigio7</t>
+          <t>https://blog.naver.com/ddb0301</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6305,13 +6397,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>553</v>
+        <v>271</v>
       </c>
       <c r="Q64" t="n">
-        <v>1153</v>
+        <v>17</v>
       </c>
       <c r="R64" t="n">
-        <v>1706</v>
+        <v>288</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6320,12 +6412,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>38314950</t>
+          <t>1056660215</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38314950</t>
+          <t>https://m.place.naver.com/place/1056660215</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6342,34 +6434,30 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>네일어라모드 홍대점</t>
+          <t>네일, 온미</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>icanbemyself@naver.com</t>
+          <t>cjsdks518@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>070-8844-3030</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로3가길 3-4 3층 301호</t>
+          <t>서울특별시 서대문구 세검정로 93 . 1층 네일샵</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xfYVQj/chat</t>
+          <t>https://www.instagram.com/nail_onme_/</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6390,7 +6478,7 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6399,13 +6487,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>572</v>
+        <v>10</v>
       </c>
       <c r="Q65" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="R65" t="n">
-        <v>612</v>
+        <v>13</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6414,12 +6502,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1086898312</t>
+          <t>1881659470</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1086898312</t>
+          <t>https://m.place.naver.com/place/1881659470</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6436,25 +6524,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>세컨드네일</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>네일마이데이</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ohmyhotelnco@naver.com</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1395-7369</t>
+          <t>0507-1325-2840</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 홍연길 69 1층 세컨드네일</t>
+          <t>서울특별시 서대문구 연희로15길 90 1층 차고 옆 출입문</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/xecond_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6464,7 +6556,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6485,17 +6577,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>206</v>
+        <v>28</v>
       </c>
       <c r="Q66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R66" t="n">
-        <v>211</v>
+        <v>29</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6504,12 +6596,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1131608621</t>
+          <t>2027784358</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1131608621</t>
+          <t>https://m.place.naver.com/place/2027784358</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6526,25 +6618,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>베이네일</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>소우네일</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>snflcjswo54@naver.com</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1337-7446</t>
+          <t>0507-1328-7467</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로 217</t>
+          <t>서울특별시 서대문구 연희맛로 7-17 1층 202호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/baeynail</t>
+          <t>https://www.instagram.com/sounail__</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6579,13 +6675,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>139</v>
+        <v>1</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6594,12 +6690,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1239283152</t>
+          <t>2021939074</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1239283152</t>
+          <t>https://m.place.naver.com/place/2021939074</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6616,35 +6712,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>로뎀스킨케어</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>에스뷰티</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ssooke114@naver.com</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>02-303-9955</t>
+          <t>0507-1478-9939</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 응암로 77</t>
+          <t>서울특별시 서대문구 증가로4길 58-11 1층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://booking.naver.com/booking/13/bizes/936347</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6669,13 +6769,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6684,12 +6784,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1985190980</t>
+          <t>1456809966</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1985190980</t>
+          <t>https://m.place.naver.com/place/1456809966</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6706,39 +6806,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>메리네일</t>
+          <t>리즈네일</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>qaqzqsaw2@naver.com</t>
+          <t>jozzin@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>02-303-1194</t>
+          <t>0507-1491-2458</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로 143</t>
+          <t>서울특별시 서대문구 연세로7안길 1 3층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_KQAFn</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6754,22 +6854,22 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="Q69" t="n">
         <v>2</v>
       </c>
       <c r="R69" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6778,12 +6878,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>13492671</t>
+          <t>2007984773</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13492671</t>
+          <t>https://m.place.naver.com/place/2007984773</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6800,29 +6900,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BK맨즈네일</t>
+          <t>영네일</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>bkmensnail@naver.com</t>
+          <t>youngnail423@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>02-365-7449</t>
+          <t>0507-1368-4230</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대길 82 3층</t>
+          <t>서울특별시 서대문구 신촌로 109 르메이에르타운5 B103-3</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bkmensnail</t>
+          <t>https://blog.naver.com/youngnail423</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6857,13 +6957,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="Q70" t="n">
-        <v>310</v>
+        <v>67</v>
       </c>
       <c r="R70" t="n">
-        <v>337</v>
+        <v>126</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6872,12 +6972,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1573880950</t>
+          <t>36505109</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1573880950</t>
+          <t>https://m.place.naver.com/place/36505109</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -6894,25 +6994,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>오늘네일</t>
+          <t>네일온</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>barbie0903@naver.com</t>
+          <t>dlgksmf3595@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1412-0791</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대5길 9 2층</t>
+          <t>서울특별시 서대문구 불광천길 264 1층좌측</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ilovetan_oneulnail</t>
+          <t>https://www.instagram.com/nailon_0790</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6947,13 +7051,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R71" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -6962,12 +7066,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1348096581</t>
+          <t>1376233513</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1348096581</t>
+          <t>https://m.place.naver.com/place/1376233513</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -6984,30 +7088,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>네일에피소드</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>네일포시즌 풋풋한리쌤 신촌점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>nail4season@naver.com</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1370-4811</t>
+          <t>02-332-3239</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세무서길 55 1층</t>
+          <t>서울특별시 서대문구 연세로5나길 16 2층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhbrZn</t>
+          <t>https://www.instagram.com/nail4season/ww.instagram.com/</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7028,7 +7136,7 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7037,13 +7145,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>78</v>
+        <v>3936</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>308</v>
       </c>
       <c r="R72" t="n">
-        <v>78</v>
+        <v>4244</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7052,12 +7160,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1897148944</t>
+          <t>1902803079</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1897148944</t>
+          <t>https://m.place.naver.com/place/1902803079</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7074,29 +7182,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>네일이끌림</t>
+          <t>보라다</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>nail_drag@naver.com</t>
+          <t>kordipr@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>02-393-9948</t>
+          <t>02-303-3188</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로35길 10</t>
+          <t>서울특별시 서대문구 증가로25길 11 1층 보라다</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cong__vely</t>
+          <t>http://www.instagram.com/iam.borada</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7131,13 +7239,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="Q73" t="n">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="R73" t="n">
-        <v>131</v>
+        <v>183</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7146,12 +7254,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1698891603</t>
+          <t>34484907</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1698891603</t>
+          <t>https://m.place.naver.com/place/34484907</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7168,35 +7276,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>보석</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>네일에피소드</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>daonnail0305@naver.com</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>02-322-1915</t>
+          <t>0507-1370-4811</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로15안길 6</t>
+          <t>서울특별시 서대문구 세무서길 55 1층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xhbrZn</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7212,22 +7324,22 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="Q74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7236,12 +7348,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>992322635</t>
+          <t>1897148944</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/992322635</t>
+          <t>https://m.place.naver.com/place/1897148944</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7258,25 +7370,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>디에고푸스 연희점 네일바이은</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>모뜨네일</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>mott_nail@naver.com</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1412-1747</t>
+          <t>0507-1385-6099</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희맛로 17-49</t>
+          <t>서울특별시 서대문구 이화여대1안길 25 2층 203호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nailbyeun</t>
+          <t>https://www.instagram.com/mott.nail</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7311,13 +7427,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>99</v>
+        <v>1330</v>
       </c>
       <c r="Q75" t="n">
-        <v>109</v>
+        <v>42</v>
       </c>
       <c r="R75" t="n">
-        <v>208</v>
+        <v>1372</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7326,12 +7442,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>37452801</t>
+          <t>1774073621</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37452801</t>
+          <t>https://m.place.naver.com/place/1774073621</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7348,30 +7464,34 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>모모네일</t>
+          <t>지젤네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>brenda70@naver.com</t>
+          <t>shinesparis@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1339-4329</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로36가길 13-2 1층 일부호</t>
+          <t>서울특별시 서대문구 신촌역로 16 1층 104-1호 지젤네일</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_momo__nail</t>
+          <t>https://booking.kakao.com/short/lBeB2nWTzo</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7401,13 +7521,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>157</v>
+        <v>32</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>157</v>
+        <v>33</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7416,12 +7536,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1284552321</t>
+          <t>1215364308</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284552321</t>
+          <t>https://m.place.naver.com/place/1215364308</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7438,21 +7558,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>코알라네일</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>네일까사</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ptypoohpooh0820@naver.com</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0507-1404-1654</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 홍제원3길 17 1층 가운데호</t>
+          <t>서울특별시 서대문구 연세로4길 28 2F</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/___nail.by.koala?igsh=MWpjaDB0MjIyNHBzcw%3D%3D&amp;utm_source=qr</t>
+          <t>http://www.instagram.com/nailcasa</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7478,7 +7606,7 @@
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -7487,13 +7615,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>25</v>
+        <v>255</v>
       </c>
       <c r="Q77" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="R77" t="n">
-        <v>27</v>
+        <v>304</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7502,12 +7630,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1997616944</t>
+          <t>38015918</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1997616944</t>
+          <t>https://m.place.naver.com/place/38015918</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7524,29 +7652,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>살롱드선네일</t>
+          <t>네일바이엔 이대역본점</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>jam_d@naver.com</t>
+          <t>makeup_byn@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0507-1338-2605</t>
+          <t>0507-1316-9910</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 북아현로1가길 20 이편한세상신촌 1단지상가 110호</t>
+          <t>서울특별시 서대문구 신촌로 169-7 이대 포레스트 1층 105호</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>http://instagram.com/salonde_seon</t>
+          <t>http://instagram.com/arim_happy</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7581,13 +7709,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>426</v>
+        <v>665</v>
       </c>
       <c r="Q78" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="R78" t="n">
-        <v>438</v>
+        <v>695</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7596,12 +7724,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1688455455</t>
+          <t>1282451640</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1688455455</t>
+          <t>https://m.place.naver.com/place/1282451640</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7618,25 +7746,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The서이</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>스윕네일</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>tong2star@naver.com</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>0507-1410-5589</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 수색로 100 DMC레미안e편한세상 103동상가 2호</t>
+          <t>서울특별시 서대문구 이화여대5길 35 지하1층 104호</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/sweepnail/</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7646,7 +7774,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -7667,17 +7795,17 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>8</v>
+        <v>178</v>
       </c>
       <c r="Q79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R79" t="n">
-        <v>9</v>
+        <v>181</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7686,12 +7814,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>33928722</t>
+          <t>1462276902</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33928722</t>
+          <t>https://m.place.naver.com/place/1462276902</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7708,39 +7836,35 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>아임모어 신촌점</t>
+          <t>연희동네일</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>iam_more@naver.com</t>
+          <t>love1nlove@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>0507-1451-3414</t>
-        </is>
-      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 명물길 6 9층</t>
+          <t>서울특별시 서대문구 연희로11길 22</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_tauxad</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -7756,22 +7880,22 @@
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1454</v>
+        <v>9</v>
       </c>
       <c r="Q80" t="n">
-        <v>892</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>2346</v>
+        <v>9</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7780,12 +7904,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>387024661</t>
+          <t>1631395937</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/387024661</t>
+          <t>https://m.place.naver.com/place/1631395937</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -7802,30 +7926,34 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>리즈네일</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>곰지네일</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>gom_gnail@naver.com</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1491-2458</t>
+          <t>0507-1323-0257</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로7안길 1 3층</t>
+          <t>서울특별시 서대문구 세무서길 73 2층 202호</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_KQAFn</t>
+          <t>http://instagram.com/gom_gnail</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -7855,13 +7983,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>6</v>
+        <v>185</v>
       </c>
       <c r="Q81" t="n">
-        <v>2</v>
+        <v>135</v>
       </c>
       <c r="R81" t="n">
-        <v>8</v>
+        <v>320</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -7870,12 +7998,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>2007984773</t>
+          <t>1468017488</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2007984773</t>
+          <t>https://m.place.naver.com/place/1468017488</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -7892,30 +8020,30 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>오늘도네일</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>아르젠떼네일</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>dmswnrjsl213@naver.com</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>02-6364-4901</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 충정로 7</t>
+          <t>서울특별시 서대문구 이화여대8길 123 상가동 105호</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail2day</t>
+          <t>https://pf.kakao.com/_kqfCG</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -7936,22 +8064,22 @@
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -7960,12 +8088,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1277557209</t>
+          <t>1142718935</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1277557209</t>
+          <t>https://m.place.naver.com/place/1142718935</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -7982,21 +8110,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>아이원네일아트</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+          <t>릴리네일</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>jain_im_@naver.com</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1350-0862</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로5길 38 1층</t>
+          <t>서울특별시 서대문구 통일로39가길 27</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lily.s_nail_studio</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8006,7 +8142,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -8027,17 +8163,17 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>148</v>
+        <v>198</v>
       </c>
       <c r="Q83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R83" t="n">
-        <v>152</v>
+        <v>201</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8046,12 +8182,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1544991635</t>
+          <t>1863831189</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1544991635</t>
+          <t>https://m.place.naver.com/place/1863831189</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8068,21 +8204,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>메이퀸네일살롱</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>메리제이네일</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>tnsend3020@naver.com</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1424-8411</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 169-7 이대포레스트 1층</t>
+          <t>서울특별시 서대문구 거북골로 120 제상가 2동 2층 13호</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/merry_j_nail</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8092,7 +8236,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -8113,17 +8257,17 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>13</v>
+        <v>109</v>
       </c>
       <c r="Q84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R84" t="n">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8132,12 +8276,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>82617755</t>
+          <t>42246094</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/82617755</t>
+          <t>https://m.place.naver.com/place/42246094</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -8154,25 +8298,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>숨네일</t>
+          <t>네일소솜</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>traineran@naver.com</t>
+          <t>wnzhd1203@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0507-1430-3550</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 홍은중앙로 100-2 1층</t>
+          <t>서울특별시 서대문구 이화여대길 88-15 1층 왼편점포호</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sumnail9901</t>
+          <t>https://www.instagram.com/nailsosom</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8207,13 +8355,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>26</v>
+        <v>218</v>
       </c>
       <c r="Q85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R85" t="n">
-        <v>27</v>
+        <v>220</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8222,12 +8370,12 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1326174975</t>
+          <t>1529665185</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1326174975</t>
+          <t>https://m.place.naver.com/place/1529665185</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -8244,25 +8392,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>루블리뷰티</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>티파니네일</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>lovemw3@naver.com</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0507-1352-9350</t>
+          <t>0507-1328-8847</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로 27 3층</t>
+          <t>서울특별시 서대문구 독립문로 34-1 티파니 네일</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lu_vely_beauty</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8272,7 +8424,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -8293,17 +8445,17 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="Q86" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="R86" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8312,12 +8464,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1078815275</t>
+          <t>1601161816</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1078815275</t>
+          <t>https://m.place.naver.com/place/1601161816</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -8334,29 +8486,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>네일샘</t>
+          <t>수네일</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>namyuri1004@naver.com</t>
+          <t>yjh1000j@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>02-312-0744</t>
+          <t>0507-1332-4612</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로 50</t>
+          <t>서울특별시 서대문구 증가로10길 16-20 1층</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lovely.sunail</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8366,7 +8518,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -8387,17 +8539,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8406,12 +8558,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>813067384</t>
+          <t>1027173445</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/813067384</t>
+          <t>https://m.place.naver.com/place/1027173445</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -8428,29 +8580,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>꽃물 네일 &amp; 속눈썹 &amp; 왁싱</t>
+          <t>네일도행운</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ddalgy00@naver.com</t>
+          <t>stellacafe@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>02-394-4141</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 420 2층</t>
+          <t>서울특별시 서대문구 모래내로 245 2층 더미뷰티 내부</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kina8843/</t>
+          <t>https://www.instagram.com/luck__with_nail?igsh=aWltam43aTkwdDJu&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8476,7 +8624,7 @@
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -8485,13 +8633,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>13</v>
+        <v>131</v>
       </c>
       <c r="Q88" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>32</v>
+        <v>131</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8500,12 +8648,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>882778770</t>
+          <t>2049561266</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/882778770</t>
+          <t>https://m.place.naver.com/place/2049561266</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -8522,25 +8670,25 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>오드리네일</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+          <t>코알라네일</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>zhdkffkekfekfo@naver.com</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>0507-1407-8532</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 거북골로 84 상가2동 108호</t>
+          <t>서울특별시 서대문구 홍제원3길 17 1층 가운데호</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/audreynail__</t>
+          <t>https://www.instagram.com/___nail.by.koala?igsh=MWpjaDB0MjIyNHBzcw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8566,7 +8714,7 @@
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -8575,13 +8723,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="Q89" t="n">
         <v>2</v>
       </c>
       <c r="R89" t="n">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8590,12 +8738,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1472183656</t>
+          <t>1997616944</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1472183656</t>
+          <t>https://m.place.naver.com/place/1997616944</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8612,29 +8760,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>네일넘버8</t>
+          <t>네일써니데이</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>sjhfox2000@naver.com</t>
+          <t>songhs1226@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>02-365-8008</t>
+          <t>0507-1403-0327</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌역로 7</t>
+          <t>서울특별시 서대문구 증가로10길 48-6 101호</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_s.day</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8644,7 +8792,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -8665,17 +8813,17 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>5</v>
+        <v>220</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R90" t="n">
-        <v>5</v>
+        <v>228</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8684,12 +8832,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>35751127</t>
+          <t>1324725520</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35751127</t>
+          <t>https://m.place.naver.com/place/1324725520</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -8706,25 +8854,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>연희동네일</t>
+          <t>시즈닝네일</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>love1nlove@naver.com</t>
+          <t>blue991013@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0507-1362-1065</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로11길 22</t>
+          <t>서울특별시 서대문구 통일로40길 28</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/blue991013</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8734,12 +8886,12 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -8755,17 +8907,17 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>9</v>
+        <v>155</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="R91" t="n">
-        <v>9</v>
+        <v>207</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8774,12 +8926,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1631395937</t>
+          <t>1888898614</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1631395937</t>
+          <t>https://m.place.naver.com/place/1888898614</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -8796,29 +8948,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>솔하네일</t>
+          <t>풋케어 로미네일</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>feltbeats90@naver.com</t>
+          <t>kangsogood@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0507-1329-2315</t>
+          <t>0507-1301-6236</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 응암로1길 15 1층</t>
+          <t>서울특별시 서대문구 통일로 139 2층 좌측호</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>http://instagram.com/solhanail</t>
+          <t>https://www.instagram.com/footcare_romi_nail?igsh=cjVmanNvMWZ5OGRt</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8853,13 +9005,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>177</v>
+        <v>7</v>
       </c>
       <c r="Q92" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>216</v>
+        <v>7</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -8868,12 +9020,12 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1476338581</t>
+          <t>2080263501</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1476338581</t>
+          <t>https://m.place.naver.com/place/2080263501</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -8890,29 +9042,25 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>윈디네일 내성발톱 무좀 발각질 문제성발</t>
+          <t>모모네일</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>winner-d@naver.com</t>
+          <t>brenda70@naver.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>0507-1367-5855</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 응암로 43 두정빌딩 1층</t>
+          <t>서울특별시 서대문구 통일로36가길 13-2 1층 일부호</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/win_d_nail</t>
+          <t>https://www.instagram.com/_momo__nail</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8947,13 +9095,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>461</v>
+        <v>157</v>
       </c>
       <c r="Q93" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>522</v>
+        <v>157</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -8962,12 +9110,12 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>1287346768</t>
+          <t>1284552321</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1287346768</t>
+          <t>https://m.place.naver.com/place/1284552321</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -8984,25 +9132,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>한예진뷰티디자인</t>
+          <t>마레네일</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>bijou-artist@naver.com</t>
+          <t>mm940226@naver.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0507-1359-9204</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 189</t>
+          <t>서울특별시 서대문구 이화여대길 64 2층</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/mare.nail/</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9012,7 +9164,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -9033,17 +9185,17 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1491</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>453</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>1944</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9052,12 +9204,12 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>1388645750</t>
+          <t>32465293</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1388645750</t>
+          <t>https://m.place.naver.com/place/32465293</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -9074,25 +9226,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>네일마이데이</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
+          <t>소소람</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>sosoram-@naver.com</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0507-1325-2840</t>
+          <t>0507-1312-4806</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로15길 90 1층 차고 옆 출입문</t>
+          <t>서울특별시 서대문구 연희로28길 18 1층</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/_sosoram</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9102,7 +9258,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -9123,17 +9279,17 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="Q95" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R95" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9142,12 +9298,12 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>2027784358</t>
+          <t>2044971493</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2027784358</t>
+          <t>https://m.place.naver.com/place/2044971493</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -9164,35 +9320,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>네일뿐</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
+          <t>The서이</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>premier-music@naver.com</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0507-1487-1503</t>
+          <t>0507-1410-5589</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 127 2층 205호</t>
+          <t>서울특별시 서대문구 수색로 100 DMC레미안e편한세상 103동상가 2호</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Fhxemxj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -9208,22 +9368,22 @@
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="Q96" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="R96" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9232,12 +9392,12 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>1627245540</t>
+          <t>33928722</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1627245540</t>
+          <t>https://m.place.naver.com/place/33928722</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
@@ -9254,25 +9414,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>디디뷰티</t>
+          <t>수아라네일 가좌라운지점</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ddb0301@naver.com</t>
+          <t>matata4@naver.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>0507-1304-0817</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세무서8길 30 상가 B1(2층) 41호 디디뷰티</t>
+          <t>서울특별시 서대문구 수색로 56 6층 609호</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ddb0301</t>
+          <t>https://smartstore.naver.com/sooara0817</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -9287,7 +9451,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -9307,13 +9471,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>271</v>
+        <v>1640</v>
       </c>
       <c r="Q97" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="R97" t="n">
-        <v>288</v>
+        <v>1648</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9322,12 +9486,12 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>1056660215</t>
+          <t>1386960813</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1056660215</t>
+          <t>https://m.place.naver.com/place/1386960813</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -9344,35 +9508,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>네일올리브 신촌 연대캠퍼스점</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
+          <t>네일도Nail</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ksy3315@naver.com</t>
+        </is>
+      </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>02-2123-8273</t>
+          <t>0507-1444-2889</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로 50 연세대학교 내 국제학사 지하 2층</t>
+          <t>서울특별시 서대문구 신촌로 109 (신촌르메이에르타운)B109-1 네일도Nail</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>http://www.nailolive.com/</t>
+          <t>https://open.kakao.com/o/sIQTg2Uc</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -9388,22 +9556,22 @@
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="R98" t="n">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9412,12 +9580,12 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>13332586</t>
+          <t>1887906221</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13332586</t>
+          <t>https://m.place.naver.com/place/1887906221</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -9434,29 +9602,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>더블유네일</t>
+          <t>마디마다네일</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ybbbbinn@naver.com</t>
+          <t>z1004__@naver.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>02-335-4321</t>
+          <t>0507-1326-2539</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로4길 9 1충</t>
+          <t>서울특별시 서대문구 신촌로 149 206호</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>http://instagram.com/private_nailsalon_w</t>
+          <t>https://www.instagram.com/madi_mada_nail/</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9491,13 +9659,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>3</v>
+        <v>804</v>
       </c>
       <c r="Q99" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="R99" t="n">
-        <v>5</v>
+        <v>821</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9506,12 +9674,12 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>20322720</t>
+          <t>1156545059</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20322720</t>
+          <t>https://m.place.naver.com/place/1156545059</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -9528,29 +9696,25 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>곰지네일</t>
+          <t>네일홍</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>gom_gnail@naver.com</t>
+          <t>jjanga4774@naver.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>0507-1323-0257</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세무서길 73 2층 202호</t>
+          <t>서울특별시 서대문구 서소문로 21 충정타워빌딩 지하1층</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>http://instagram.com/gom_gnail</t>
+          <t>https://blog.naver.com/jjanga4774</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -9565,7 +9729,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -9576,22 +9740,22 @@
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>185</v>
+        <v>126</v>
       </c>
       <c r="Q100" t="n">
-        <v>135</v>
+        <v>25</v>
       </c>
       <c r="R100" t="n">
-        <v>320</v>
+        <v>151</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -9600,12 +9764,12 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>1468017488</t>
+          <t>35624131</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1468017488</t>
+          <t>https://m.place.naver.com/place/35624131</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
@@ -9622,29 +9786,25 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>제이네일</t>
+          <t>한예진뷰티디자인</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>rhkdmswl@naver.com</t>
+          <t>bijou-artist@naver.com</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>0507-1329-0346</t>
-        </is>
-      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 독립문공원길 13 독립문극동아파트</t>
+          <t>서울특별시 서대문구 신촌로 189</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/j_nail_2503</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9654,7 +9814,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -9675,17 +9835,17 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -9694,12 +9854,12 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>321319088</t>
+          <t>1388645750</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/321319088</t>
+          <t>https://m.place.naver.com/place/1388645750</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
@@ -9716,30 +9876,34 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>유네일</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
+          <t>네일어라모드 홍대점</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>icanbemyself@naver.com</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>0507-1412-2114</t>
+          <t>070-8844-3030</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로24마길 47 1층</t>
+          <t>서울특별시 서대문구 신촌로3가길 3-4 3층 301호</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_u_nail_</t>
+          <t>http://pf.kakao.com/_xfYVQj/chat</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -9760,7 +9924,7 @@
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -9769,13 +9933,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>231</v>
+        <v>572</v>
       </c>
       <c r="Q102" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="R102" t="n">
-        <v>267</v>
+        <v>612</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -9784,12 +9948,12 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>1610895712</t>
+          <t>1086898312</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1610895712</t>
+          <t>https://m.place.naver.com/place/1086898312</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -9806,21 +9970,29 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>네일뷰</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
+          <t>오네일드잇 신촌점</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>travelsudal@naver.com</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0507-1379-5740</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로32안길 82 1층 101호</t>
+          <t>서울특별시 서대문구 신촌로 123 2층</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailview__</t>
+          <t>https://www.instagram.com/oh_nailed_it</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9855,13 +10027,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>41</v>
+        <v>602</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R103" t="n">
-        <v>41</v>
+        <v>611</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -9870,12 +10042,12 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>2068137219</t>
+          <t>1930241791</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2068137219</t>
+          <t>https://m.place.naver.com/place/1930241791</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
@@ -9892,29 +10064,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>하미네일</t>
+          <t>네일오엔</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>p790512@naver.com</t>
+          <t>checkmate_out@naver.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>0507-1332-0103</t>
+          <t>0507-1362-3291</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로35길 3 2층 하미네일</t>
+          <t>서울특별시 서대문구 연세로7길 58 102호</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/p790512</t>
+          <t>https://www.instagram.com/nail.oen?igsh=c2poN3MxZG5kcmR1&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -9929,7 +10101,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -9940,7 +10112,7 @@
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -9949,13 +10121,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="R104" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -9964,12 +10136,12 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>1633156843</t>
+          <t>1478444590</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1633156843</t>
+          <t>https://m.place.naver.com/place/1478444590</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
@@ -9986,39 +10158,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>안씨네일</t>
+          <t>컬러라운지 네일&amp;태닝</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>an_c_nail@naver.com</t>
+          <t>brushlounge@naver.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0507-1352-3893</t>
+          <t>02-395-1196</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로35길 66 1층 103호</t>
+          <t>서울특별시 서대문구 통일로 461 2층</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_rxoxiqX</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -10034,22 +10206,22 @@
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>376</v>
+        <v>14</v>
       </c>
       <c r="Q105" t="n">
-        <v>247</v>
+        <v>1</v>
       </c>
       <c r="R105" t="n">
-        <v>623</v>
+        <v>15</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -10058,12 +10230,12 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>1657626219</t>
+          <t>13118581</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1657626219</t>
+          <t>https://m.place.naver.com/place/13118581</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
@@ -10080,30 +10252,30 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>안젤리크네일</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
+          <t>수네일</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>yjh1000j@naver.com</t>
+        </is>
+      </c>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>070-8648-3432</t>
-        </is>
-      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 북아현동 199-1 힐스테이트신촌상가 105호</t>
+          <t>서울특별시 서대문구 세검정로1길 50 1층 수네일</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_qZgeb</t>
+          <t>http://instagram.com/soonail_kim</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -10124,22 +10296,22 @@
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="Q106" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="R106" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -10148,12 +10320,12 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>1976256692</t>
+          <t>1835439095</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1976256692</t>
+          <t>https://m.place.naver.com/place/1835439095</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -10170,34 +10342,34 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>비포유</t>
+          <t>하미네일</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>hansse_db@naver.com</t>
+          <t>p790512@naver.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0507-1313-6448</t>
+          <t>0507-1332-0103</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 가재울미래로 2 203동 104-2호</t>
+          <t>서울특별시 서대문구 신촌로35길 3 2층 하미네일</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_IrLMG</t>
+          <t>https://blog.naver.com/p790512</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -10207,7 +10379,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -10218,7 +10390,7 @@
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -10227,13 +10399,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>264</v>
+        <v>15</v>
       </c>
       <c r="Q107" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="R107" t="n">
-        <v>280</v>
+        <v>42</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -10242,12 +10414,12 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>1150022642</t>
+          <t>1633156843</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1150022642</t>
+          <t>https://m.place.naver.com/place/1633156843</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
@@ -10264,30 +10436,34 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>원더네일</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
+          <t>위드네일</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>hahaha_1226@naver.com</t>
+        </is>
+      </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0507-1360-1515</t>
+          <t>0507-1308-2035</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 독립문로12길 2</t>
+          <t>서울특별시 서대문구 홍제천로 158 1층</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xczxmaj</t>
+          <t>https://www.instagram.com/with.nail_</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -10317,13 +10493,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="Q108" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -10332,12 +10508,12 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>37196672</t>
+          <t>2099359388</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37196672</t>
+          <t>https://m.place.naver.com/place/2099359388</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
@@ -10354,29 +10530,29 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>네일온</t>
+          <t>솔하네일</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>nailon22@naver.com</t>
+          <t>feltbeats90@naver.com</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0507-1331-5593</t>
+          <t>0507-1329-2315</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 충정로9길 4 2층(충정로2가)</t>
+          <t>서울특별시 서대문구 응암로1길 15 1층</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailon22</t>
+          <t>http://instagram.com/solhanail</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -10391,7 +10567,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -10411,13 +10587,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>447</v>
+        <v>177</v>
       </c>
       <c r="Q109" t="n">
-        <v>131</v>
+        <v>39</v>
       </c>
       <c r="R109" t="n">
-        <v>578</v>
+        <v>216</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -10426,12 +10602,12 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>1272307920</t>
+          <t>1476338581</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1272307920</t>
+          <t>https://m.place.naver.com/place/1476338581</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
@@ -10448,31 +10624,35 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>더네일</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
+          <t>썸네일</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>hackerstalk11@naver.com</t>
+        </is>
+      </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 서소문로 43-22 한흥빌딩 2층 더 네일</t>
+          <t>서울특별시 서대문구 이화여대길 58</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_mYaaxl</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -10488,22 +10668,22 @@
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P110" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="R110" t="n">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -10512,12 +10692,12 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>1800993616</t>
+          <t>1217647474</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1800993616</t>
+          <t>https://m.place.naver.com/place/1217647474</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -10534,25 +10714,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>네일살롱</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr"/>
+          <t>손에담다</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>kjy88990@naver.com</t>
+        </is>
+      </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>0507-1303-0241</t>
+          <t>0507-1307-7876</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희맛로 20 연희빌딩 1층 1호네일실롱</t>
+          <t>서울특별시 서대문구 통일로 153 손에담다</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>http://instagram.com/nailsalon7775</t>
+          <t>http://instagram.com/sonedamda</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -10587,13 +10771,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="Q111" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="R111" t="n">
-        <v>83</v>
+        <v>163</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -10602,12 +10786,12 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>1527535605</t>
+          <t>1681218410</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1527535605</t>
+          <t>https://m.place.naver.com/place/1681218410</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
@@ -10624,29 +10808,29 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>네일포시즌 풋풋한리쌤 신촌점</t>
+          <t>베이네일</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>nail4season@naver.com</t>
+          <t>4chi_27@naver.com</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>02-332-3239</t>
+          <t>0507-1337-7446</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로5나길 16 2층</t>
+          <t>서울특별시 서대문구 증가로 217</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail4season/ww.instagram.com/</t>
+          <t>https://www.instagram.com/baeynail</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10681,13 +10865,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>3936</v>
+        <v>138</v>
       </c>
       <c r="Q112" t="n">
-        <v>309</v>
+        <v>1</v>
       </c>
       <c r="R112" t="n">
-        <v>4245</v>
+        <v>139</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -10696,12 +10880,12 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>1902803079</t>
+          <t>1239283152</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1902803079</t>
+          <t>https://m.place.naver.com/place/1239283152</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
@@ -10718,25 +10902,29 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>네일뭐해</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
+          <t>코이네일</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>qwas1262@naver.com</t>
+        </is>
+      </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>0507-1340-8272</t>
+          <t>0507-1494-6711</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 가좌로 111 상가1층</t>
+          <t>서울특별시 서대문구 세검정로 46 1층 9호</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_mohe/</t>
+          <t>https://www.instagram.com/k.o.i.nail/</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10771,13 +10959,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>702</v>
+        <v>163</v>
       </c>
       <c r="Q113" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="R113" t="n">
-        <v>752</v>
+        <v>182</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -10786,12 +10974,12 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>533976950</t>
+          <t>1956411597</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/533976950</t>
+          <t>https://m.place.naver.com/place/1956411597</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
@@ -10808,29 +10996,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>손에담다</t>
+          <t>알지네일</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>kjy88990@naver.com</t>
+          <t>handsos@naver.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>0507-1307-7876</t>
+          <t>0507-1352-1908</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 153 손에담다</t>
+          <t>서울특별시 서대문구 연희로31길 9</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>http://instagram.com/sonedamda</t>
+          <t>http://instagram.com/r.g_nail</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -10865,13 +11053,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="Q114" t="n">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="R114" t="n">
-        <v>163</v>
+        <v>31</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -10880,12 +11068,12 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>1681218410</t>
+          <t>32528538</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1681218410</t>
+          <t>https://m.place.naver.com/place/32528538</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
@@ -10902,34 +11090,34 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>네일 소아나</t>
+          <t>네일소브 북가좌본점</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>missyou106@naver.com</t>
+          <t>hbs2002i@naver.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>0507-1363-1483</t>
+          <t>0507-1448-3319</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대5길 35 지하1층 104호</t>
+          <t>서울특별시 서대문구 거북골로 184 1층 좌측중앙(네일샵)</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_VExgxmn</t>
+          <t>https://www.instagram.com/nail_sove</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -10950,7 +11138,7 @@
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -10959,13 +11147,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="Q115" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="R115" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -10974,12 +11162,12 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>2057189903</t>
+          <t>1192995175</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2057189903</t>
+          <t>https://m.place.naver.com/place/1192995175</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
@@ -10996,29 +11184,29 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>토드네일</t>
+          <t>네일뭐해</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>0728helen@naver.com</t>
+          <t>mementomori-24@naver.com</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>0507-1486-0620</t>
+          <t>0507-1340-8272</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대5길 35 지하1층 114호</t>
+          <t>서울특별시 서대문구 가좌로 111 상가1층</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/todnail_</t>
+          <t>https://www.instagram.com/nail_mohe/</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -11044,7 +11232,7 @@
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -11053,13 +11241,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>436</v>
+        <v>702</v>
       </c>
       <c r="Q116" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="R116" t="n">
-        <v>466</v>
+        <v>752</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -11068,12 +11256,12 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>1674577867</t>
+          <t>533976950</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1674577867</t>
+          <t>https://m.place.naver.com/place/533976950</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
@@ -11090,25 +11278,29 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>소우네일</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>디에고푸스 연희점 네일바이은</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>kwonbinus@naver.com</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>0507-1328-7467</t>
+          <t>0507-1412-1747</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희맛로 7-17 1층 202호</t>
+          <t>서울특별시 서대문구 연희맛로 17-49</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sounail__</t>
+          <t>http://www.instagram.com/nailbyeun</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -11143,13 +11335,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="Q117" t="n">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="R117" t="n">
-        <v>1</v>
+        <v>208</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -11158,12 +11350,12 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>2021939074</t>
+          <t>37452801</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2021939074</t>
+          <t>https://m.place.naver.com/place/37452801</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
@@ -11180,30 +11372,34 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>보라다</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
+          <t>로렐네일</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>mchavzezy@naver.com</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>02-303-3188</t>
+          <t>0507-1436-9020</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로25길 11 1층 보라다</t>
+          <t>서울특별시 서대문구 이화여대3길 45 리브하임 B1층 로렐</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/iam.borada</t>
+          <t>http://pf.kakao.com/_xcXaxgn/friend</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -11224,7 +11420,7 @@
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -11233,13 +11429,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>41</v>
+        <v>233</v>
       </c>
       <c r="Q118" t="n">
-        <v>142</v>
+        <v>86</v>
       </c>
       <c r="R118" t="n">
-        <v>183</v>
+        <v>319</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -11248,12 +11444,12 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>34484907</t>
+          <t>1883098019</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34484907</t>
+          <t>https://m.place.naver.com/place/1883098019</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
@@ -11270,29 +11466,29 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>모뜨네일</t>
+          <t>윈디네일 내성발톱 무좀 발각질 문제성발</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>mott_nail@naver.com</t>
+          <t>winner-d@naver.com</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>0507-1385-6099</t>
+          <t>0507-1367-5855</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대1안길 25 2층 203호</t>
+          <t>서울특별시 서대문구 응암로 43 두정빌딩 1층</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mott.nail</t>
+          <t>https://www.instagram.com/win_d_nail</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -11327,13 +11523,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1330</v>
+        <v>461</v>
       </c>
       <c r="Q119" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="R119" t="n">
-        <v>1372</v>
+        <v>522</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -11342,12 +11538,12 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>1774073621</t>
+          <t>1287346768</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1774073621</t>
+          <t>https://m.place.naver.com/place/1287346768</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
@@ -11364,29 +11560,29 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>달달한네일</t>
+          <t>네일샘</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>nail0danji@naver.com</t>
+          <t>namyuri1004@naver.com</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>0507-1433-3262</t>
+          <t>02-312-0744</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세무서2길 16 1층 2호</t>
+          <t>서울특별시 서대문구 연세로 50</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/thedaldalnail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -11396,7 +11592,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -11417,17 +11613,17 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P120" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>323</v>
+        <v>0</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -11436,12 +11632,12 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>1257856428</t>
+          <t>813067384</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1257856428</t>
+          <t>https://m.place.naver.com/place/813067384</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
@@ -11458,29 +11654,29 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>온더네일스</t>
+          <t>루블리뷰티</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>k14150@naver.com</t>
+          <t>i_believe28@naver.com</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>0507-1330-5812</t>
+          <t>0507-1352-9350</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 400 2F</t>
+          <t>서울특별시 서대문구 연세로 27 3층</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_onthenails</t>
+          <t>https://www.instagram.com/lu_vely_beauty</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -11515,13 +11711,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R121" t="n">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -11530,12 +11726,12 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>1484695115</t>
+          <t>1078815275</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1484695115</t>
+          <t>https://m.place.naver.com/place/1078815275</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
@@ -11552,29 +11748,29 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>티파니네일</t>
+          <t>포쉬네일 하이푸스 신촌점</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>lovemw3@naver.com</t>
+          <t>freegirl11@naver.com</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>0507-1328-8847</t>
+          <t>0507-1335-4241</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 독립문로 34-1 티파니 네일</t>
+          <t>서울특별시 서대문구 신촌로 73 2층</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/sh_forsynail</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -11584,7 +11780,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -11605,17 +11801,17 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P122" t="n">
-        <v>11</v>
+        <v>3133</v>
       </c>
       <c r="Q122" t="n">
-        <v>1</v>
+        <v>337</v>
       </c>
       <c r="R122" t="n">
-        <v>12</v>
+        <v>3470</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -11624,12 +11820,12 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>1601161816</t>
+          <t>1944620503</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1601161816</t>
+          <t>https://m.place.naver.com/place/1944620503</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
@@ -11646,29 +11842,29 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>리본 네일</t>
+          <t>네일넘버8</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>feelringhair@naver.com</t>
+          <t>sjhfox2000@naver.com</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>0507-1445-1169</t>
+          <t>02-365-8008</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대길 33 2층 리본네일</t>
+          <t>서울특별시 서대문구 신촌역로 7</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/feelringhair</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -11678,12 +11874,12 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -11699,17 +11895,17 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P123" t="n">
-        <v>644</v>
+        <v>5</v>
       </c>
       <c r="Q123" t="n">
-        <v>439</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>1083</v>
+        <v>5</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -11718,12 +11914,12 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>1561804134</t>
+          <t>35751127</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1561804134</t>
+          <t>https://m.place.naver.com/place/35751127</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
@@ -11740,30 +11936,34 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>아모이네일스튜디오</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr"/>
+          <t>네일미야오</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>traveler_01@naver.com</t>
+        </is>
+      </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>0507-1439-5957</t>
+          <t>0507-1471-2420</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로27길 43 1층 102호</t>
+          <t>서울특별시 서대문구 신촌역로 17 203호</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_dxaVan/chat</t>
+          <t>https://www.instagram.com/nailmeow.2025?igsh=NDNhbmw0ZGgxN3d0</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -11784,7 +11984,7 @@
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -11793,13 +11993,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="Q124" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R124" t="n">
-        <v>22</v>
+        <v>148</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -11808,12 +12008,12 @@
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>2066634292</t>
+          <t>1516469775</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2066634292</t>
+          <t>https://m.place.naver.com/place/1516469775</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
@@ -11830,29 +12030,29 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>마레네일</t>
+          <t>네일, 여유</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>mm940226@naver.com</t>
+          <t>knl_95@naver.com</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>0507-1359-9204</t>
+          <t>0507-1433-1620</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대길 64 2층</t>
+          <t>서울특별시 서대문구 간호대로2길 9 1층</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mare.nail/</t>
+          <t>http://instagram.com/nail.healing_</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -11887,13 +12087,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1491</v>
+        <v>179</v>
       </c>
       <c r="Q125" t="n">
-        <v>453</v>
+        <v>32</v>
       </c>
       <c r="R125" t="n">
-        <v>1944</v>
+        <v>211</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -11902,12 +12102,12 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>32465293</t>
+          <t>1492064846</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32465293</t>
+          <t>https://m.place.naver.com/place/1492064846</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
@@ -11924,34 +12124,34 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>멜트네일</t>
+          <t>아모이네일스튜디오</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ckckcl1357@naver.com</t>
+          <t>morningarden@naver.com</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>0507-1323-6269</t>
+          <t>0507-1439-5957</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로 85 인사이드빌딩 1층 104호</t>
+          <t>서울특별시 서대문구 신촌로27길 43 1층 102호</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/melt_nail_/</t>
+          <t>http://pf.kakao.com/_dxaVan/chat</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -11981,13 +12181,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="Q126" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R126" t="n">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -11996,12 +12196,12 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>1591157927</t>
+          <t>2066634292</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1591157927</t>
+          <t>https://m.place.naver.com/place/2066634292</t>
         </is>
       </c>
       <c r="V126" t="inlineStr">
@@ -12021,7 +12221,11 @@
           <t>마브뷰티아카데미</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>omab_academy@naver.com</t>
+        </is>
+      </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>

--- a/naver-place-crawler/results_nail/서대문_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/서대문_네일샵.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>아임모어 신촌점</t>
+          <t>소소람</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iam_more@naver.com</t>
+          <t>sosoram-@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1451-3414</t>
+          <t>0507-1312-4806</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 명물길 6 9층</t>
+          <t>서울특별시 서대문구 연희로28길 18 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_tauxad</t>
+          <t>https://www.instagram.com/_sosoram</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1454</v>
+        <v>34</v>
       </c>
       <c r="Q2" t="n">
-        <v>892</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>2346</v>
+        <v>40</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>387024661</t>
+          <t>2044971493</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/387024661</t>
+          <t>https://m.place.naver.com/place/2044971493</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,24 +658,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>쏭뷰티샵</t>
+          <t>메리네일</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>aryangjiu@naver.com</t>
+          <t>qaqzqsaw2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>070-8248-9565</t>
+          <t>02-303-1194</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세검정로1길 48 1층</t>
+          <t>서울특별시 서대문구 증가로 143</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>32284905</t>
+          <t>13492671</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32284905</t>
+          <t>https://m.place.naver.com/place/13492671</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>미호네일</t>
+          <t>아모이네일스튜디오</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kikijj0206@naver.com</t>
+          <t>morningarden@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02-303-4117</t>
+          <t>0507-1439-5957</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 가재울미래로 2 205동상가 104-2 미호네일</t>
+          <t>서울특별시 서대문구 신촌로27길 43 1층 102호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_in_miho</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1494438581</t>
+          <t>2066634292</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1494438581</t>
+          <t>https://m.place.naver.com/place/2066634292</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,25 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>오늘네일</t>
+          <t>미호네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>barbie0903@naver.com</t>
+          <t>rain0979@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>02-303-4117</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대5길 9 2층</t>
+          <t>서울특별시 서대문구 가재울미래로 2 205동상가 104-2 미호네일</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ilovetan_oneulnail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -874,7 +878,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -890,7 +894,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -902,10 +906,10 @@
         <v>10</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1348096581</t>
+          <t>1494438581</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1348096581</t>
+          <t>https://m.place.naver.com/place/1494438581</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -936,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>토드네일</t>
+          <t>네일샘</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0728helen@naver.com</t>
+          <t>namyuri1004@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1486-0620</t>
+          <t>02-312-0744</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대5길 35 지하1층 114호</t>
+          <t>서울특별시 서대문구 연세로 50</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/todnail_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -968,7 +972,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -984,22 +988,22 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>436</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>466</v>
+        <v>0</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1674577867</t>
+          <t>813067384</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1674577867</t>
+          <t>https://m.place.naver.com/place/813067384</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1030,25 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>꾸밈</t>
+          <t>BK민방경네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hairccumim@naver.com</t>
+          <t>acquidigio7@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>02-393-7449</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 수색로2길 39 DMC금호리첸시아 상가 지하101호</t>
+          <t>서울특별시 서대문구 이화여대길 82 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/ggoomim</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1058,7 +1066,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1068,10 +1076,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc46s3</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1083,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>289</v>
+        <v>553</v>
       </c>
       <c r="Q7" t="n">
-        <v>113</v>
+        <v>1153</v>
       </c>
       <c r="R7" t="n">
-        <v>402</v>
+        <v>1706</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1649834362</t>
+          <t>38314950</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1649834362</t>
+          <t>https://m.place.naver.com/place/38314950</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1120,39 +1132,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>루미가넷 현대백화점 신촌점</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>nuroonge@naver.com</t>
-        </is>
-      </c>
+          <t>더네일</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1461-9296</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 83 현대백화점신촌점 3F</t>
+          <t>서울특별시 서대문구 서소문로 43-22 한흥빌딩 2층 더 네일</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_mYaaxl</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1168,22 +1172,22 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="Q8" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="R8" t="n">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,12 +1196,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>31229559</t>
+          <t>1800993616</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31229559</t>
+          <t>https://m.place.naver.com/place/1800993616</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1214,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>히카리 살롱 네일&amp;아이래쉬</t>
+          <t>보석</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>yeooonyummy@naver.com</t>
+          <t>marble1120@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1369-1853</t>
+          <t>02-322-1915</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 109 지하1층 비112 히카리살롱</t>
+          <t>서울특별시 서대문구 연희로15안길 6</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sY3GnTpg</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1246,7 +1250,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1262,22 +1266,22 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>433</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>460</v>
+        <v>12</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,12 +1290,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1696710543</t>
+          <t>992322635</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1696710543</t>
+          <t>https://m.place.naver.com/place/992322635</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1308,29 +1312,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>멜트네일</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ckckcl1357@naver.com</t>
-        </is>
-      </c>
+          <t>소우네일</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1323-6269</t>
+          <t>0507-1328-7467</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로 85 인사이드빌딩 1층 104호</t>
+          <t>서울특별시 서대문구 연희맛로 7-17 1층 202호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/melt_nail_/</t>
+          <t>https://www.instagram.com/sounail__</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1356,7 +1356,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>103</v>
+        <v>1</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1591157927</t>
+          <t>2021939074</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1591157927</t>
+          <t>https://m.place.naver.com/place/2021939074</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1402,29 +1402,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일살롱</t>
+          <t>네일온</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>wing3527@naver.com</t>
+          <t>nailon22@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1303-0241</t>
+          <t>0507-1331-5593</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희맛로 20 연희빌딩 1층 1호네일실롱</t>
+          <t>서울특별시 서대문구 충정로9길 4 2층(충정로2가)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://instagram.com/nailsalon7775</t>
+          <t>https://blog.naver.com/nailon22</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>38</v>
+        <v>447</v>
       </c>
       <c r="Q11" t="n">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="R11" t="n">
-        <v>83</v>
+        <v>578</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1527535605</t>
+          <t>1272307920</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1527535605</t>
+          <t>https://m.place.naver.com/place/1272307920</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1496,29 +1496,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>온더네일스</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>k14150@naver.com</t>
-        </is>
-      </c>
+          <t>릴리네일</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1330-5812</t>
+          <t>0507-1350-0862</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 400 2F</t>
+          <t>서울특별시 서대문구 통일로39가길 27</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_onthenails</t>
+          <t>https://www.instagram.com/lily.s_nail_studio</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1553,13 +1549,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>142</v>
+        <v>198</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>142</v>
+        <v>201</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,12 +1564,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1484695115</t>
+          <t>1863831189</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1484695115</t>
+          <t>https://m.place.naver.com/place/1863831189</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1590,34 +1586,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>네일뿐</t>
+          <t>곰지네일</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>cuiyushan20-19@naver.com</t>
+          <t>gom_gnail@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1487-1503</t>
+          <t>0507-1323-0257</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 127 2층 205호</t>
+          <t>서울특별시 서대문구 세무서길 73 2층 202호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Fhxemxj</t>
+          <t>http://instagram.com/gom_gnail</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1647,13 +1643,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>18</v>
+        <v>185</v>
       </c>
       <c r="Q13" t="n">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="R13" t="n">
-        <v>33</v>
+        <v>320</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,12 +1658,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1627245540</t>
+          <t>1468017488</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1627245540</t>
+          <t>https://m.place.naver.com/place/1468017488</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1684,34 +1680,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>제이앤제이네일</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>sallyhome_@naver.com</t>
-        </is>
-      </c>
+          <t>제이네일</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1342-8430</t>
+          <t>0507-1329-0346</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 402 1층 제이엔제이네일</t>
+          <t>서울특별시 서대문구 독립문공원길 13 독립문극동아파트</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_fMNYxj</t>
+          <t>https://www.instagram.com/j_nail_2503</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1732,7 +1724,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1741,13 +1733,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="Q14" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="R14" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,12 +1748,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1722436082</t>
+          <t>321319088</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722436082</t>
+          <t>https://m.place.naver.com/place/321319088</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1778,29 +1770,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>오드리네일</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ardusy@naver.com</t>
-        </is>
-      </c>
+          <t>연희동네일</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1407-8532</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 거북골로 84 상가2동 108호</t>
+          <t>서울특별시 서대문구 연희로11길 22</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/audreynail__</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1810,7 +1794,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1831,17 +1815,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,12 +1834,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1472183656</t>
+          <t>1631395937</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1472183656</t>
+          <t>https://m.place.naver.com/place/1631395937</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1872,29 +1856,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>리본 네일</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>feelringhair@naver.com</t>
-        </is>
-      </c>
+          <t>스윕네일</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1445-1169</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대길 33 2층 리본네일</t>
+          <t>서울특별시 서대문구 이화여대5길 35 지하1층 104호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/feelringhair</t>
+          <t>https://www.instagram.com/sweepnail/</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1909,7 +1885,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1929,13 +1905,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>644</v>
+        <v>178</v>
       </c>
       <c r="Q16" t="n">
-        <v>439</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>1083</v>
+        <v>181</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,12 +1920,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1561804134</t>
+          <t>1462276902</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1561804134</t>
+          <t>https://m.place.naver.com/place/1462276902</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1966,12 +1942,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>네일띵크</t>
+          <t>메이퀸네일살롱</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>goqlsl7895@naver.com</t>
+          <t>ogsohd@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1979,12 +1955,12 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로11가길 36 신관 1층</t>
+          <t>서울특별시 서대문구 신촌로 169-7 이대포레스트 1층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/snfSrVOh</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1994,7 +1970,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2010,22 +1986,22 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2034,12 +2010,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1472586988</t>
+          <t>82617755</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1472586988</t>
+          <t>https://m.place.naver.com/place/82617755</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2056,29 +2032,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>더 꼼네일</t>
+          <t>네일바이엔 이대역본점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>kjuuu0716@naver.com</t>
+          <t>makeup_byn@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1322-3992</t>
+          <t>0507-1316-9910</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 명지대길 56 1층</t>
+          <t>서울특별시 서대문구 신촌로 169-7 이대 포레스트 1층 105호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>http://instagram.com/the_kkom</t>
+          <t>http://instagram.com/arim_happy</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2113,13 +2089,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>81</v>
+        <v>665</v>
       </c>
       <c r="Q18" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="R18" t="n">
-        <v>146</v>
+        <v>695</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2128,12 +2104,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1616221232</t>
+          <t>1282451640</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1616221232</t>
+          <t>https://m.place.naver.com/place/1282451640</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2150,29 +2126,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>글리밍네일</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>hankyuldata@naver.com</t>
-        </is>
-      </c>
+          <t>로지네일</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>02-312-7769</t>
+          <t>0507-1387-0314</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로35길 10 e편한세상신촌상가 지하1층 글리밍네일</t>
+          <t>서울특별시 서대문구 연세로7안길 1 3층 로지네일</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/gleaming_nail</t>
+          <t>http://www.instagram.com/rosy___nail</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2207,13 +2179,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>61</v>
+        <v>292</v>
       </c>
       <c r="Q19" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="R19" t="n">
-        <v>104</v>
+        <v>320</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2222,12 +2194,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>302039845</t>
+          <t>1244771586</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/302039845</t>
+          <t>https://m.place.naver.com/place/1244771586</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2244,39 +2216,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>메리네일</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>qaqzqsaw2@naver.com</t>
-        </is>
-      </c>
+          <t>비포유</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>02-303-1194</t>
+          <t>0507-1313-6448</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로 143</t>
+          <t>서울특별시 서대문구 가재울미래로 2 203동 104-2호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_IrLMG</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2292,22 +2260,22 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>25</v>
+        <v>264</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="R20" t="n">
-        <v>27</v>
+        <v>280</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2316,12 +2284,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>13492671</t>
+          <t>1150022642</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13492671</t>
+          <t>https://m.place.naver.com/place/1150022642</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2338,29 +2306,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>제이네일</t>
+          <t>BK맨즈네일</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rhkdmswl@naver.com</t>
+          <t>bkmensnail@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1329-0346</t>
+          <t>02-365-7449</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 독립문공원길 13 독립문극동아파트</t>
+          <t>서울특별시 서대문구 이화여대길 82 3층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/j_nail_2503</t>
+          <t>https://blog.naver.com/bkmensnail</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2375,7 +2343,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2395,13 +2363,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>113</v>
+        <v>27</v>
       </c>
       <c r="Q21" t="n">
-        <v>9</v>
+        <v>310</v>
       </c>
       <c r="R21" t="n">
-        <v>122</v>
+        <v>337</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2410,12 +2378,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>321319088</t>
+          <t>1573880950</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/321319088</t>
+          <t>https://m.place.naver.com/place/1573880950</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2432,34 +2400,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>네일 아이보리</t>
+          <t>꽃물 네일 &amp; 속눈썹 &amp; 왁싱</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>052young@naver.com</t>
+          <t>ddalgy00@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1463-7021</t>
+          <t>02-394-4141</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대5길 35 신촌영타운지웰에스테이트 상가동 2층 네일, 아이보리</t>
+          <t>서울특별시 서대문구 통일로 420 2층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/770181/items/4634924</t>
+          <t>https://www.instagram.com/kina8843/</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2489,13 +2457,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>240</v>
+        <v>13</v>
       </c>
       <c r="Q22" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="R22" t="n">
-        <v>276</v>
+        <v>32</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2504,12 +2472,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1572186883</t>
+          <t>882778770</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1572186883</t>
+          <t>https://m.place.naver.com/place/882778770</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2526,29 +2494,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>달달한네일</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>nail0danji@naver.com</t>
-        </is>
-      </c>
+          <t>미뜨네일</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0507-1433-3262</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세무서2길 16 1층 2호</t>
+          <t>서울특별시 서대문구 증가로10길 16-6 미뜨네일</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/thedaldalnail</t>
+          <t>https://www.instagram.com/meett_nail</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2583,13 +2543,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>233</v>
+        <v>198</v>
       </c>
       <c r="Q23" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>323</v>
+        <v>199</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2598,12 +2558,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1257856428</t>
+          <t>1274572984</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1257856428</t>
+          <t>https://m.place.naver.com/place/1274572984</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2620,29 +2580,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BK맨즈네일</t>
+          <t>네일뭐해</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>bkmensnail@naver.com</t>
+          <t>mementomori-24@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>02-365-7449</t>
+          <t>0507-1340-8272</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대길 82 3층</t>
+          <t>서울특별시 서대문구 가좌로 111 상가1층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bkmensnail</t>
+          <t>https://www.instagram.com/nail_mohe/</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2657,7 +2617,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2677,13 +2637,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>27</v>
+        <v>702</v>
       </c>
       <c r="Q24" t="n">
-        <v>310</v>
+        <v>50</v>
       </c>
       <c r="R24" t="n">
-        <v>337</v>
+        <v>752</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2692,12 +2652,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1573880950</t>
+          <t>533976950</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1573880950</t>
+          <t>https://m.place.naver.com/place/533976950</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2714,29 +2674,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>프로젝트 앨리스</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>uer1130@naver.com</t>
-        </is>
-      </c>
+          <t>네일까사</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1383-3681</t>
+          <t>0507-1404-1654</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세검정로3길 38-2 1층</t>
+          <t>서울특별시 서대문구 연세로4길 28 2F</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/nailcasa</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2746,7 +2702,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2767,17 +2723,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>26</v>
+        <v>255</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="R25" t="n">
-        <v>27</v>
+        <v>304</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2786,12 +2742,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1788377896</t>
+          <t>38015918</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1788377896</t>
+          <t>https://m.place.naver.com/place/38015918</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2808,25 +2764,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>메이퀸네일살롱</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>ogsohd@naver.com</t>
-        </is>
-      </c>
+          <t>꾸밈</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 169-7 이대포레스트 1층</t>
+          <t>서울특별시 서대문구 수색로2길 39 DMC금호리첸시아 상가 지하101호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/ggoomim</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2836,7 +2788,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2857,17 +2809,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>13</v>
+        <v>289</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>113</v>
       </c>
       <c r="R26" t="n">
-        <v>15</v>
+        <v>402</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2876,12 +2828,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>82617755</t>
+          <t>1649834362</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/82617755</t>
+          <t>https://m.place.naver.com/place/1649834362</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2898,34 +2850,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BK민방경네일</t>
+          <t>네일뿐</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>acquidigio7@naver.com</t>
+          <t>cuiyushan20-19@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>02-393-7449</t>
+          <t>0507-1487-1503</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대길 82 2층</t>
+          <t>서울특별시 서대문구 신촌로 127 2층 205호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/acquidigio7</t>
+          <t>http://pf.kakao.com/_Fhxemxj</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2935,7 +2887,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2946,7 +2898,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2955,13 +2907,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>553</v>
+        <v>18</v>
       </c>
       <c r="Q27" t="n">
-        <v>1153</v>
+        <v>15</v>
       </c>
       <c r="R27" t="n">
-        <v>1706</v>
+        <v>33</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2970,12 +2922,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>38314950</t>
+          <t>1627245540</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38314950</t>
+          <t>https://m.place.naver.com/place/1627245540</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2992,34 +2944,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>더블유네일</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>ybbbbinn@naver.com</t>
-        </is>
-      </c>
+          <t>아르젠떼네일</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>02-335-4321</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로4길 9 1충</t>
+          <t>서울특별시 서대문구 이화여대8길 123 상가동 105호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://instagram.com/private_nailsalon_w</t>
+          <t>https://pf.kakao.com/_kqfCG</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3040,22 +2984,22 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3064,12 +3008,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>20322720</t>
+          <t>1142718935</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20322720</t>
+          <t>https://m.place.naver.com/place/1142718935</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3086,25 +3030,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>마요네일</t>
+          <t>더블유네일</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ynh3377@naver.com</t>
+          <t>ybbbbinn@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>02-335-4321</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로11가길 33-3 1층</t>
+          <t>서울특별시 서대문구 연희로4길 9 1충</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mayonail_official</t>
+          <t>http://instagram.com/private_nailsalon_w</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3139,13 +3087,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3154,12 +3102,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1434998291</t>
+          <t>20322720</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1434998291</t>
+          <t>https://m.place.naver.com/place/20322720</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3176,34 +3124,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>뮤즈네일</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>jiji012636@naver.com</t>
-        </is>
-      </c>
+          <t>네일 소아나</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1300-4636</t>
+          <t>0507-1363-1483</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 인왕시장길 18</t>
+          <t>서울특별시 서대문구 이화여대5길 35 지하1층 104호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jiji012636</t>
+          <t>http://pf.kakao.com/_VExgxmn</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3213,7 +3157,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3224,7 +3168,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3233,13 +3177,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="Q30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R30" t="n">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3248,12 +3192,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1179732435</t>
+          <t>2057189903</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1179732435</t>
+          <t>https://m.place.naver.com/place/2057189903</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3270,29 +3214,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>루나네일</t>
+          <t>네일뷰</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>lunamika@naver.com</t>
+          <t>darkyoon85@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0507-1329-7109</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 가재울미래로 15 1층 103호 루나네일</t>
+          <t>서울특별시 서대문구 증가로32안길 82 1층 101호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://instagram.com/lunarnail__</t>
+          <t>https://www.instagram.com/nailview__</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3327,13 +3267,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3342,12 +3282,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1427499799</t>
+          <t>2068137219</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1427499799</t>
+          <t>https://m.place.naver.com/place/2068137219</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3364,25 +3304,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>네일뷰</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>darkyoon85@naver.com</t>
-        </is>
-      </c>
+          <t>네일띵크</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로32안길 82 1층 101호</t>
+          <t>서울특별시 서대문구 연희로11가길 36 신관 1층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailview__</t>
+          <t>https://open.kakao.com/o/snfSrVOh</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3408,7 +3344,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3417,13 +3353,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3432,12 +3368,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2068137219</t>
+          <t>1472586988</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2068137219</t>
+          <t>https://m.place.naver.com/place/1472586988</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3454,25 +3390,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>행복한 네일</t>
+          <t>풋케어 로미네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>etbjj@naver.com</t>
+          <t>kangsogood@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1301-6236</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로 204 상가동 1층 105호</t>
+          <t>서울특별시 서대문구 통일로 139 2층 좌측호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/footcare_romi_nail?igsh=cjVmanNvMWZ5OGRt</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3482,7 +3422,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3503,17 +3443,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3522,12 +3462,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2064316137</t>
+          <t>2080263501</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2064316137</t>
+          <t>https://m.place.naver.com/place/2080263501</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3544,24 +3484,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>보석</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>marble1120@naver.com</t>
-        </is>
-      </c>
+          <t>굥뷰티</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>02-322-1915</t>
+          <t>0505-685-7683</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로15안길 6</t>
+          <t>서울특별시 서대문구 신촌역로 10</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3601,13 +3537,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3616,12 +3552,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>992322635</t>
+          <t>1137345145</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/992322635</t>
+          <t>https://m.place.naver.com/place/1137345145</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3638,39 +3574,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>네일 블라썸</t>
+          <t>행복한 네일</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>wilklove@naver.com</t>
+          <t>etbjj@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0507-1324-7644</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세검정로1길 39 풍림2차아파트 상가동 241호</t>
+          <t>서울특별시 서대문구 연희로 204 상가동 1층 105호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://naver.me/FRL0RGyl</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3695,13 +3627,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="Q35" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3710,12 +3642,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1423228794</t>
+          <t>2064316137</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1423228794</t>
+          <t>https://m.place.naver.com/place/2064316137</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3732,29 +3664,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>네일이끌림</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>nail_drag@naver.com</t>
-        </is>
-      </c>
+          <t>The서이</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>02-393-9948</t>
+          <t>0507-1410-5589</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로35길 10</t>
+          <t>서울특별시 서대문구 수색로 100 DMC레미안e편한세상 103동상가 2호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cong__vely</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3764,7 +3692,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3785,17 +3713,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="Q36" t="n">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>131</v>
+        <v>9</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3804,12 +3732,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1698891603</t>
+          <t>33928722</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1698891603</t>
+          <t>https://m.place.naver.com/place/33928722</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3826,29 +3754,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>네일온</t>
+          <t>리본 네일</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>nailon22@naver.com</t>
+          <t>feelringhair@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1331-5593</t>
+          <t>0507-1445-1169</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 충정로9길 4 2층(충정로2가)</t>
+          <t>서울특별시 서대문구 이화여대길 33 2층 리본네일</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailon22</t>
+          <t>https://blog.naver.com/feelringhair</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3883,13 +3811,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>447</v>
+        <v>644</v>
       </c>
       <c r="Q37" t="n">
-        <v>131</v>
+        <v>439</v>
       </c>
       <c r="R37" t="n">
-        <v>578</v>
+        <v>1083</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3898,12 +3826,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1272307920</t>
+          <t>1561804134</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1272307920</t>
+          <t>https://m.place.naver.com/place/1561804134</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3920,29 +3848,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>안젤리크네일</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>webmore@naver.com</t>
-        </is>
-      </c>
+          <t>리즈네일</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>070-8648-3432</t>
+          <t>0507-1491-2458</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 북아현동 199-1 힐스테이트신촌상가 105호</t>
+          <t>서울특별시 서대문구 연세로7안길 1 3층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_qZgeb</t>
+          <t>http://pf.kakao.com/_KQAFn</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3973,17 +3897,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R38" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3992,12 +3916,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1976256692</t>
+          <t>2007984773</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1976256692</t>
+          <t>https://m.place.naver.com/place/2007984773</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4014,25 +3938,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>아이원네일아트</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>fpwlsk8877@naver.com</t>
-        </is>
-      </c>
+          <t>오드리네일</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1407-8532</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로5길 38 1층</t>
+          <t>서울특별시 서대문구 거북골로 84 상가2동 108호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/audreynail__</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4042,7 +3966,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4063,17 +3987,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4082,12 +4006,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1544991635</t>
+          <t>1472183656</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1544991635</t>
+          <t>https://m.place.naver.com/place/1472183656</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4104,29 +4028,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일살롱무아</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>min_0_97@naver.com</t>
-        </is>
-      </c>
+          <t>네일도Nail</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1436-1705</t>
+          <t>0507-1444-2889</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 109 신촌르메이에르타운 5차 1층 110-1-2</t>
+          <t>서울특별시 서대문구 신촌로 109 (신촌르메이에르타운)B109-1 네일도Nail</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailmuah_</t>
+          <t>https://open.kakao.com/o/sIQTg2Uc</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4152,7 +4072,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4161,13 +4081,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="Q40" t="n">
-        <v>9</v>
+        <v>121</v>
       </c>
       <c r="R40" t="n">
-        <v>105</v>
+        <v>176</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4176,12 +4096,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1027772524</t>
+          <t>1887906221</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027772524</t>
+          <t>https://m.place.naver.com/place/1887906221</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4198,39 +4118,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일올리브 신촌 연대캠퍼스점</t>
+          <t>네일살롱무아</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>cxdbs@naver.com</t>
+          <t>min_0_97@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>02-2123-8273</t>
+          <t>0507-1436-1705</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로 50 연세대학교 내 국제학사 지하 2층</t>
+          <t>서울특별시 서대문구 신촌로 109 신촌르메이에르타운 5차 1층 110-1-2</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://www.nailolive.com/</t>
+          <t>https://www.instagram.com/nailmuah_</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4251,17 +4171,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R41" t="n">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4270,12 +4190,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>13332586</t>
+          <t>1027772524</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13332586</t>
+          <t>https://m.place.naver.com/place/1027772524</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4292,34 +4212,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>공간네일 신촌점</t>
+          <t>안씨네일</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>tomi6@naver.com</t>
+          <t>an_c_nail@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1367-0798</t>
+          <t>0507-1352-3893</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 명물길 49 3층</t>
+          <t>서울특별시 서대문구 통일로35길 66 1층 103호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://linktr.ee/gonggan_sc</t>
+          <t>http://pf.kakao.com/_rxoxiqX</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4329,7 +4249,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4345,17 +4265,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1760</v>
+        <v>376</v>
       </c>
       <c r="Q42" t="n">
-        <v>53</v>
+        <v>247</v>
       </c>
       <c r="R42" t="n">
-        <v>1813</v>
+        <v>623</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4364,12 +4284,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1412908076</t>
+          <t>1657626219</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1412908076</t>
+          <t>https://m.place.naver.com/place/1657626219</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4386,30 +4306,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>더네일</t>
+          <t>멜트네일</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>thenail_@naver.com</t>
+          <t>ckckcl1357@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1323-6269</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 서소문로 43-22 한흥빌딩 2층 더 네일</t>
+          <t>서울특별시 서대문구 연희로 85 인사이드빌딩 1층 104호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_mYaaxl</t>
+          <t>https://www.instagram.com/melt_nail_/</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4439,13 +4363,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="Q43" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="R43" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4454,12 +4378,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1800993616</t>
+          <t>1591157927</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1800993616</t>
+          <t>https://m.place.naver.com/place/1591157927</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4476,29 +4400,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>오늘도네일</t>
+          <t>세컨드네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>j2lang@naver.com</t>
+          <t>nail2nd@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>02-6364-4901</t>
+          <t>0507-1395-7369</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 충정로 7</t>
+          <t>서울특별시 서대문구 홍연길 69 1층 세컨드네일</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail2day</t>
+          <t>https://www.instagram.com/xecond_nail</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4533,13 +4457,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R44" t="n">
-        <v>20</v>
+        <v>211</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4548,12 +4472,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1277557209</t>
+          <t>1131608621</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1277557209</t>
+          <t>https://m.place.naver.com/place/1131608621</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4570,34 +4494,30 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>로지네일</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>wonderfuuul@naver.com</t>
-        </is>
-      </c>
+          <t>제이앤제이네일</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1387-0314</t>
+          <t>0507-1342-8430</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로7안길 1 3층 로지네일</t>
+          <t>서울특별시 서대문구 통일로 402 1층 제이엔제이네일</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/rosy___nail</t>
+          <t>http://pf.kakao.com/_fMNYxj</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4618,7 +4538,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4627,13 +4547,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>292</v>
+        <v>78</v>
       </c>
       <c r="Q45" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="R45" t="n">
-        <v>320</v>
+        <v>127</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4642,12 +4562,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1244771586</t>
+          <t>1722436082</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1244771586</t>
+          <t>https://m.place.naver.com/place/1722436082</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4664,29 +4584,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>위드앤네일</t>
+          <t>네일오엔</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jelly0355@naver.com</t>
+          <t>checkmate_out@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1322-3690</t>
+          <t>0507-1362-3291</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 510 상가212호 위드앤네일</t>
+          <t>서울특별시 서대문구 연세로7길 58 102호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/_with_n_nail_</t>
+          <t>https://www.instagram.com/nail.oen?igsh=c2poN3MxZG5kcmR1&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4712,7 +4632,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4721,13 +4641,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R46" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4736,12 +4656,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1070279609</t>
+          <t>1478444590</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1070279609</t>
+          <t>https://m.place.naver.com/place/1478444590</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4758,30 +4678,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>숨네일</t>
+          <t>네일 아이보리</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>traineran@naver.com</t>
+          <t>052young@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1463-7021</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 홍은중앙로 100-2 1층</t>
+          <t>서울특별시 서대문구 이화여대5길 35 신촌영타운지웰에스테이트 상가동 2층 네일, 아이보리</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sumnail9901</t>
+          <t>https://booking.naver.com/booking/13/bizes/770181/items/4634924</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4811,13 +4735,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>26</v>
+        <v>240</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="R47" t="n">
-        <v>27</v>
+        <v>276</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4826,12 +4750,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1326174975</t>
+          <t>1572186883</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1326174975</t>
+          <t>https://m.place.naver.com/place/1572186883</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4848,29 +4772,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>비포유</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>hansse_db@naver.com</t>
-        </is>
-      </c>
+          <t>지젤네일</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1313-6448</t>
+          <t>0507-1339-4329</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 가재울미래로 2 203동 104-2호</t>
+          <t>서울특별시 서대문구 신촌역로 16 1층 104-1호 지젤네일</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_IrLMG</t>
+          <t>https://booking.kakao.com/short/lBeB2nWTzo</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4896,7 +4816,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4905,13 +4825,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>264</v>
+        <v>32</v>
       </c>
       <c r="Q48" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>280</v>
+        <v>33</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4920,12 +4840,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1150022642</t>
+          <t>1215364308</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1150022642</t>
+          <t>https://m.place.naver.com/place/1215364308</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4942,29 +4862,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>옌그리다</t>
+          <t>네일마이데이</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>tmfddd@naver.com</t>
+          <t>b1xnk@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1358-6121</t>
+          <t>0507-1325-2840</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 홍제내길 118 1층</t>
+          <t>서울특별시 서대문구 연희로15길 90 1층 차고 옆 출입문</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCoLUjj2k9oeAU5y7IS50qOQ</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4974,7 +4894,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4995,17 +4915,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>228</v>
+        <v>28</v>
       </c>
       <c r="Q49" t="n">
-        <v>212</v>
+        <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>440</v>
+        <v>29</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5014,12 +4934,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1611348671</t>
+          <t>2027784358</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611348671</t>
+          <t>https://m.place.naver.com/place/2027784358</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5036,34 +4956,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>네일 소아나</t>
+          <t>루블리뷰티</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>missyou106@naver.com</t>
+          <t>i_believe28@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1363-1483</t>
+          <t>0507-1352-9350</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대5길 35 지하1층 104호</t>
+          <t>서울특별시 서대문구 연세로 27 3층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_VExgxmn</t>
+          <t>https://www.instagram.com/lu_vely_beauty</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5084,7 +5004,7 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5093,13 +5013,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q50" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="R50" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5108,12 +5028,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>2057189903</t>
+          <t>1078815275</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2057189903</t>
+          <t>https://m.place.naver.com/place/1078815275</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5130,29 +5050,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>빔빔네일</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>yznnim@naver.com</t>
-        </is>
-      </c>
+          <t>마요네일</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0507-1406-5642</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세무서길 77 1층</t>
+          <t>서울특별시 서대문구 연희로11가길 33-3 1층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/beam2nail</t>
+          <t>https://www.instagram.com/mayonail_official</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5187,13 +5099,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="Q51" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R51" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5202,12 +5114,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>84828356</t>
+          <t>1434998291</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/84828356</t>
+          <t>https://m.place.naver.com/place/1434998291</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5224,34 +5136,30 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>원더네일</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>noweunn@naver.com</t>
-        </is>
-      </c>
+          <t>마레네일</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1360-1515</t>
+          <t>0507-1359-9204</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 독립문로12길 2</t>
+          <t>서울특별시 서대문구 이화여대길 64 2층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xczxmaj</t>
+          <t>https://www.instagram.com/mare.nail/</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5272,7 +5180,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5281,13 +5189,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>38</v>
+        <v>1494</v>
       </c>
       <c r="Q52" t="n">
-        <v>7</v>
+        <v>453</v>
       </c>
       <c r="R52" t="n">
-        <v>45</v>
+        <v>1947</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5296,12 +5204,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>37196672</t>
+          <t>32465293</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37196672</t>
+          <t>https://m.place.naver.com/place/32465293</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5318,24 +5226,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>로뎀스킨케어</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>bealove0508@naver.com</t>
-        </is>
-      </c>
+          <t>쏭뷰티샵</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>02-303-9955</t>
+          <t>070-8248-9565</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 응암로 77</t>
+          <t>서울특별시 서대문구 세검정로1길 48 1층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5375,13 +5279,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5390,12 +5294,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1985190980</t>
+          <t>32284905</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1985190980</t>
+          <t>https://m.place.naver.com/place/32284905</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5412,39 +5316,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>안씨네일</t>
+          <t>티파니네일</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>an_c_nail@naver.com</t>
+          <t>lovemw3@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1352-3893</t>
+          <t>0507-1328-8847</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로35길 66 1층 103호</t>
+          <t>서울특별시 서대문구 독립문로 34-1 티파니 네일</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_rxoxiqX</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5460,22 +5364,22 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>376</v>
+        <v>11</v>
       </c>
       <c r="Q54" t="n">
-        <v>247</v>
+        <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>623</v>
+        <v>12</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5484,12 +5388,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1657626219</t>
+          <t>1601161816</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1657626219</t>
+          <t>https://m.place.naver.com/place/1601161816</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5511,7 +5415,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>dyk6614@naver.com</t>
+          <t>junghalee1004@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -5600,29 +5504,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>유네일</t>
+          <t>히카리 살롱 네일&amp;아이래쉬</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>luvu1016@naver.com</t>
+          <t>yeooonyummy@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1412-2114</t>
+          <t>0507-1369-1853</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로24마길 47 1층</t>
+          <t>서울특별시 서대문구 신촌로 109 지하1층 비112 히카리살롱</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_u_nail_</t>
+          <t>https://open.kakao.com/o/sY3GnTpg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5648,7 +5552,7 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5657,13 +5561,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>231</v>
+        <v>433</v>
       </c>
       <c r="Q56" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="R56" t="n">
-        <v>267</v>
+        <v>460</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5672,12 +5576,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1610895712</t>
+          <t>1696710543</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1610895712</t>
+          <t>https://m.place.naver.com/place/1696710543</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5694,12 +5598,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>미뜨네일</t>
+          <t>코알라네일</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>annykoh@naver.com</t>
+          <t>zhdkffkekfekfo@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -5707,12 +5611,12 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로10길 16-6 미뜨네일</t>
+          <t>서울특별시 서대문구 홍제원3길 17 1층 가운데호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/meett_nail</t>
+          <t>https://www.instagram.com/___nail.by.koala?igsh=MWpjaDB0MjIyNHBzcw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5738,7 +5642,7 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5747,13 +5651,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>198</v>
+        <v>25</v>
       </c>
       <c r="Q57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R57" t="n">
-        <v>199</v>
+        <v>27</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5762,12 +5666,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1274572984</t>
+          <t>1997616944</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1274572984</t>
+          <t>https://m.place.naver.com/place/1997616944</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5784,34 +5688,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>굥뷰티</t>
+          <t>네일올리브 신촌 연대캠퍼스점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>sunday020@naver.com</t>
+          <t>cxdbs@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0505-685-7683</t>
+          <t>02-2123-8273</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌역로 10</t>
+          <t>서울특별시 서대문구 연세로 50 연세대학교 내 국제학사 지하 2층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.nailolive.com/</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5841,13 +5745,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5856,12 +5760,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1137345145</t>
+          <t>13332586</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1137345145</t>
+          <t>https://m.place.naver.com/place/13332586</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5878,29 +5782,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>세컨드네일</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>nail2nd@naver.com</t>
-        </is>
-      </c>
+          <t>옌그리다</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1395-7369</t>
+          <t>0507-1358-6121</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 홍연길 69 1층 세컨드네일</t>
+          <t>서울특별시 서대문구 홍제내길 118 1층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/xecond_nail</t>
+          <t>https://youtube.com/channel/UCoLUjj2k9oeAU5y7IS50qOQ</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5935,13 +5835,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="Q59" t="n">
-        <v>5</v>
+        <v>212</v>
       </c>
       <c r="R59" t="n">
-        <v>211</v>
+        <v>440</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5950,12 +5850,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1131608621</t>
+          <t>1611348671</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1131608621</t>
+          <t>https://m.place.naver.com/place/1611348671</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -5972,25 +5872,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>동네살롱</t>
+          <t>시즈닝네일</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>hoteltt@naver.com</t>
+          <t>blue991013@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1362-1065</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 가재울로6길 53-55 1층</t>
+          <t>서울특별시 서대문구 통일로40길 28</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://instagram.com/dn.salon</t>
+          <t>https://blog.naver.com/blue991013</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6005,7 +5909,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6025,13 +5929,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>49</v>
+        <v>155</v>
       </c>
       <c r="Q60" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="R60" t="n">
-        <v>62</v>
+        <v>207</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6040,12 +5944,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1209907072</t>
+          <t>1888898614</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1209907072</t>
+          <t>https://m.place.naver.com/place/1888898614</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6062,29 +5966,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>아띠네일</t>
+          <t>베이네일</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>attinail_@naver.com</t>
+          <t>4chi_27@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1322-6612</t>
+          <t>0507-1337-7446</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 193 2층 아띠네일</t>
+          <t>서울특별시 서대문구 증가로 217</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/addi_nail_/</t>
+          <t>https://www.instagram.com/baeynail</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6119,13 +6023,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>345</v>
+        <v>138</v>
       </c>
       <c r="Q61" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>386</v>
+        <v>139</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6134,12 +6038,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1631947370</t>
+          <t>1239283152</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1631947370</t>
+          <t>https://m.place.naver.com/place/1239283152</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6156,29 +6060,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>꽃물 네일 &amp; 속눈썹 &amp; 왁싱</t>
+          <t>위드네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ddalgy00@naver.com</t>
+          <t>hahaha_1226@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>02-394-4141</t>
+          <t>0507-1308-2035</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 420 2층</t>
+          <t>서울특별시 서대문구 홍제천로 158 1층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kina8843/</t>
+          <t>https://www.instagram.com/with.nail_</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6204,7 +6108,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6213,13 +6117,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="Q62" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6228,12 +6132,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>882778770</t>
+          <t>2099359388</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/882778770</t>
+          <t>https://m.place.naver.com/place/2099359388</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6250,29 +6154,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>살롱드선네일</t>
+          <t>디에고푸스 연희점 네일바이은</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jam_d@naver.com</t>
+          <t>kwonbinus@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1338-2605</t>
+          <t>0507-1412-1747</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 북아현로1가길 20 이편한세상신촌 1단지상가 110호</t>
+          <t>서울특별시 서대문구 연희맛로 17-49</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://instagram.com/salonde_seon</t>
+          <t>http://www.instagram.com/nailbyeun</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6307,13 +6211,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>426</v>
+        <v>99</v>
       </c>
       <c r="Q63" t="n">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="R63" t="n">
-        <v>438</v>
+        <v>208</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6322,12 +6226,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1688455455</t>
+          <t>37452801</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1688455455</t>
+          <t>https://m.place.naver.com/place/37452801</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6344,25 +6248,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>디디뷰티</t>
+          <t>포쉬네일 하이푸스 신촌점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ddb0301@naver.com</t>
+          <t>freegirl11@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1335-4241</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세무서8길 30 상가 B1(2층) 41호 디디뷰티</t>
+          <t>서울특별시 서대문구 신촌로 73 2층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ddb0301</t>
+          <t>https://www.instagram.com/sh_forsynail</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6377,7 +6285,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6397,13 +6305,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>271</v>
+        <v>3133</v>
       </c>
       <c r="Q64" t="n">
-        <v>17</v>
+        <v>337</v>
       </c>
       <c r="R64" t="n">
-        <v>288</v>
+        <v>3470</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6412,12 +6320,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1056660215</t>
+          <t>1944620503</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1056660215</t>
+          <t>https://m.place.naver.com/place/1944620503</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6434,25 +6342,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>네일, 온미</t>
+          <t>네일포시즌 풋풋한리쌤 신촌점</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>cjsdks518@naver.com</t>
+          <t>nail4season@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>02-332-3239</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세검정로 93 . 1층 네일샵</t>
+          <t>서울특별시 서대문구 연세로5나길 16 2층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_onme_/</t>
+          <t>https://www.instagram.com/nail4season/ww.instagram.com/</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6487,13 +6399,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>10</v>
+        <v>3936</v>
       </c>
       <c r="Q65" t="n">
-        <v>3</v>
+        <v>308</v>
       </c>
       <c r="R65" t="n">
-        <v>13</v>
+        <v>4244</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6502,12 +6414,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1881659470</t>
+          <t>1902803079</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1881659470</t>
+          <t>https://m.place.naver.com/place/1902803079</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6524,29 +6436,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>네일마이데이</t>
+          <t>오늘도네일</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ohmyhotelnco@naver.com</t>
+          <t>j2lang@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1325-2840</t>
+          <t>02-6364-4901</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로15길 90 1층 차고 옆 출입문</t>
+          <t>서울특별시 서대문구 충정로 7</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/nail2day</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6556,7 +6468,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6577,17 +6489,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6596,12 +6508,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>2027784358</t>
+          <t>1277557209</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2027784358</t>
+          <t>https://m.place.naver.com/place/1277557209</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6618,29 +6530,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>소우네일</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>snflcjswo54@naver.com</t>
-        </is>
-      </c>
+          <t>네일넘버8</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1328-7467</t>
+          <t>02-365-8008</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희맛로 7-17 1층 202호</t>
+          <t>서울특별시 서대문구 신촌역로 7</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sounail__</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6650,7 +6558,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6671,17 +6579,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P67" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>1</v>
-      </c>
       <c r="R67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6690,12 +6598,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>2021939074</t>
+          <t>35751127</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2021939074</t>
+          <t>https://m.place.naver.com/place/35751127</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6712,34 +6620,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>에스뷰티</t>
+          <t>수아라네일 가좌라운지점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ssooke114@naver.com</t>
+          <t>matata4@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1478-9939</t>
+          <t>0507-1304-0817</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로4길 58-11 1층</t>
+          <t>서울특별시 서대문구 수색로 56 6층 609호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/936347</t>
+          <t>https://smartstore.naver.com/sooara0817</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6765,17 +6673,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1640</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1648</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6784,12 +6692,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1456809966</t>
+          <t>1386960813</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1456809966</t>
+          <t>https://m.place.naver.com/place/1386960813</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6806,39 +6714,35 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>리즈네일</t>
+          <t>한예진뷰티디자인</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>jozzin@naver.com</t>
+          <t>bijou-artist@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>0507-1491-2458</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로7안길 1 3층</t>
+          <t>서울특별시 서대문구 신촌로 189</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_KQAFn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6854,22 +6758,22 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6878,12 +6782,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>2007984773</t>
+          <t>1388645750</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2007984773</t>
+          <t>https://m.place.naver.com/place/1388645750</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6900,29 +6804,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>영네일</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>youngnail423@naver.com</t>
-        </is>
-      </c>
+          <t>온더네일스</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1368-4230</t>
+          <t>0507-1330-5812</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 109 르메이에르타운5 B103-3</t>
+          <t>서울특별시 서대문구 통일로 400 2F</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/youngnail423</t>
+          <t>https://www.instagram.com/_onthenails</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6937,7 +6837,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6957,13 +6857,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="Q70" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6972,12 +6872,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>36505109</t>
+          <t>1484695115</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36505109</t>
+          <t>https://m.place.naver.com/place/1484695115</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -6994,29 +6894,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>네일온</t>
+          <t>네일써니데이</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>dlgksmf3595@naver.com</t>
+          <t>songhs1226@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1412-0791</t>
+          <t>0507-1403-0327</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 불광천길 264 1층좌측</t>
+          <t>서울특별시 서대문구 증가로10길 48-6 101호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailon_0790</t>
+          <t>https://www.instagram.com/nail_s.day</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7051,13 +6951,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>35</v>
+        <v>220</v>
       </c>
       <c r="Q71" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R71" t="n">
-        <v>37</v>
+        <v>228</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7066,12 +6966,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1376233513</t>
+          <t>1324725520</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1376233513</t>
+          <t>https://m.place.naver.com/place/1324725520</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7088,29 +6988,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>네일포시즌 풋풋한리쌤 신촌점</t>
+          <t>네일, 여유</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>nail4season@naver.com</t>
+          <t>knl_95@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>02-332-3239</t>
+          <t>0507-1433-1620</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로5나길 16 2층</t>
+          <t>서울특별시 서대문구 간호대로2길 9 1층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail4season/ww.instagram.com/</t>
+          <t>http://instagram.com/nail.healing_</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7145,13 +7045,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3936</v>
+        <v>179</v>
       </c>
       <c r="Q72" t="n">
-        <v>308</v>
+        <v>32</v>
       </c>
       <c r="R72" t="n">
-        <v>4244</v>
+        <v>211</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7160,12 +7060,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1902803079</t>
+          <t>1492064846</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1902803079</t>
+          <t>https://m.place.naver.com/place/1492064846</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7182,29 +7082,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>보라다</t>
+          <t>영네일</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>kordipr@naver.com</t>
+          <t>youngnail423@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>02-303-3188</t>
+          <t>0507-1368-4230</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로25길 11 1층 보라다</t>
+          <t>서울특별시 서대문구 신촌로 109 르메이에르타운5 B103-3</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/iam.borada</t>
+          <t>https://blog.naver.com/youngnail423</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7219,7 +7119,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7239,13 +7139,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="Q73" t="n">
-        <v>142</v>
+        <v>67</v>
       </c>
       <c r="R73" t="n">
-        <v>183</v>
+        <v>126</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7254,12 +7154,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>34484907</t>
+          <t>36505109</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34484907</t>
+          <t>https://m.place.naver.com/place/36505109</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7276,34 +7176,30 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>네일에피소드</t>
+          <t>네일, 온미</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>daonnail0305@naver.com</t>
+          <t>cjsdks518@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>0507-1370-4811</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세무서길 55 1층</t>
+          <t>서울특별시 서대문구 세검정로 93 . 1층 네일샵</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhbrZn</t>
+          <t>https://www.instagram.com/nail_onme_/</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7324,7 +7220,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7333,13 +7229,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R74" t="n">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7348,12 +7244,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1897148944</t>
+          <t>1881659470</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1897148944</t>
+          <t>https://m.place.naver.com/place/1881659470</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7370,34 +7266,34 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>모뜨네일</t>
+          <t>네일 블라썸</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>mott_nail@naver.com</t>
+          <t>wilklove@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1385-6099</t>
+          <t>0507-1324-7644</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대1안길 25 2층 203호</t>
+          <t>서울특별시 서대문구 세검정로1길 39 풍림2차아파트 상가동 241호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mott.nail</t>
+          <t>https://naver.me/FRL0RGyl</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7423,17 +7319,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1330</v>
+        <v>74</v>
       </c>
       <c r="Q75" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="R75" t="n">
-        <v>1372</v>
+        <v>111</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7442,12 +7338,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1774073621</t>
+          <t>1423228794</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1774073621</t>
+          <t>https://m.place.naver.com/place/1423228794</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7464,34 +7360,30 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>지젤네일</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>shinesparis@naver.com</t>
-        </is>
-      </c>
+          <t>메리제이네일</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1339-4329</t>
+          <t>0507-1424-8411</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌역로 16 1층 104-1호 지젤네일</t>
+          <t>서울특별시 서대문구 거북골로 120 제상가 2동 2층 13호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://booking.kakao.com/short/lBeB2nWTzo</t>
+          <t>http://instagram.com/merry_j_nail</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7521,13 +7413,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>32</v>
+        <v>109</v>
       </c>
       <c r="Q76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R76" t="n">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7536,12 +7428,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1215364308</t>
+          <t>42246094</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1215364308</t>
+          <t>https://m.place.naver.com/place/42246094</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7558,29 +7450,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>네일까사</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>ptypoohpooh0820@naver.com</t>
-        </is>
-      </c>
+          <t>동네살롱</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>0507-1404-1654</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로4길 28 2F</t>
+          <t>서울특별시 서대문구 가재울로6길 53-55 1층</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nailcasa</t>
+          <t>http://instagram.com/dn.salon</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7615,13 +7499,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>255</v>
+        <v>49</v>
       </c>
       <c r="Q77" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="R77" t="n">
-        <v>304</v>
+        <v>62</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7630,12 +7514,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>38015918</t>
+          <t>1209907072</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38015918</t>
+          <t>https://m.place.naver.com/place/1209907072</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7652,29 +7536,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>네일바이엔 이대역본점</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>makeup_byn@naver.com</t>
-        </is>
-      </c>
+          <t>네일소솜</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0507-1316-9910</t>
+          <t>0507-1430-3550</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 169-7 이대 포레스트 1층 105호</t>
+          <t>서울특별시 서대문구 이화여대길 88-15 1층 왼편점포호</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>http://instagram.com/arim_happy</t>
+          <t>https://www.instagram.com/nailsosom</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7709,13 +7589,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>665</v>
+        <v>218</v>
       </c>
       <c r="Q78" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="R78" t="n">
-        <v>695</v>
+        <v>220</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7724,12 +7604,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1282451640</t>
+          <t>1529665185</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1282451640</t>
+          <t>https://m.place.naver.com/place/1529665185</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7746,25 +7626,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>스윕네일</t>
+          <t>네일소브 북가좌본점</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>tong2star@naver.com</t>
+          <t>hbs2002i@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0507-1448-3319</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대5길 35 지하1층 104호</t>
+          <t>서울특별시 서대문구 거북골로 184 1층 좌측중앙(네일샵)</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sweepnail/</t>
+          <t>https://www.instagram.com/nail_sove</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7799,13 +7683,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>178</v>
+        <v>105</v>
       </c>
       <c r="Q79" t="n">
         <v>3</v>
       </c>
       <c r="R79" t="n">
-        <v>181</v>
+        <v>108</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7814,12 +7698,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1462276902</t>
+          <t>1192995175</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1462276902</t>
+          <t>https://m.place.naver.com/place/1192995175</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7836,35 +7720,35 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>연희동네일</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>love1nlove@naver.com</t>
-        </is>
-      </c>
+          <t>네일에피소드</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1370-4811</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로11길 22</t>
+          <t>서울특별시 서대문구 세무서길 55 1층</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xhbrZn</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -7880,22 +7764,22 @@
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7904,12 +7788,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1631395937</t>
+          <t>1897148944</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1631395937</t>
+          <t>https://m.place.naver.com/place/1897148944</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -7926,29 +7810,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>곰지네일</t>
+          <t>보라다</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>gom_gnail@naver.com</t>
+          <t>kordipr@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1323-0257</t>
+          <t>02-303-3188</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세무서길 73 2층 202호</t>
+          <t>서울특별시 서대문구 증가로25길 11 1층 보라다</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>http://instagram.com/gom_gnail</t>
+          <t>http://www.instagram.com/iam.borada</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7974,7 +7858,7 @@
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -7983,13 +7867,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>185</v>
+        <v>41</v>
       </c>
       <c r="Q81" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="R81" t="n">
-        <v>320</v>
+        <v>183</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -7998,12 +7882,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1468017488</t>
+          <t>34484907</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1468017488</t>
+          <t>https://m.place.naver.com/place/34484907</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8020,35 +7904,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>아르젠떼네일</t>
+          <t>루미가넷 현대백화점 신촌점</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>dmswnrjsl213@naver.com</t>
+          <t>nuroonge@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0507-1461-9296</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대8길 123 상가동 105호</t>
+          <t>서울특별시 서대문구 신촌로 83 현대백화점신촌점 3F</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_kqfCG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -8064,7 +7952,7 @@
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -8073,13 +7961,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="Q82" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="R82" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8088,12 +7976,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1142718935</t>
+          <t>31229559</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1142718935</t>
+          <t>https://m.place.naver.com/place/31229559</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -8110,34 +7998,34 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>릴리네일</t>
+          <t>네일어라모드 홍대점</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>jain_im_@naver.com</t>
+          <t>icanbemyself@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0507-1350-0862</t>
+          <t>070-8844-3030</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로39가길 27</t>
+          <t>서울특별시 서대문구 신촌로3가길 3-4 3층 301호</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lily.s_nail_studio</t>
+          <t>http://pf.kakao.com/_xfYVQj/chat</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8158,7 +8046,7 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8167,13 +8055,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>198</v>
+        <v>572</v>
       </c>
       <c r="Q83" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="R83" t="n">
-        <v>201</v>
+        <v>612</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8182,12 +8070,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1863831189</t>
+          <t>1086898312</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1863831189</t>
+          <t>https://m.place.naver.com/place/1086898312</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8204,29 +8092,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>메리제이네일</t>
+          <t>마디마다네일</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>tnsend3020@naver.com</t>
+          <t>z1004__@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0507-1424-8411</t>
+          <t>0507-1326-2539</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 거북골로 120 제상가 2동 2층 13호</t>
+          <t>서울특별시 서대문구 신촌로 149 206호</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>http://instagram.com/merry_j_nail</t>
+          <t>https://www.instagram.com/madi_mada_nail/</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8261,13 +8149,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>109</v>
+        <v>804</v>
       </c>
       <c r="Q84" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="R84" t="n">
-        <v>112</v>
+        <v>821</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8276,12 +8164,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>42246094</t>
+          <t>1156545059</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/42246094</t>
+          <t>https://m.place.naver.com/place/1156545059</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -8298,34 +8186,34 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>네일소솜</t>
+          <t>아임모어 신촌점</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>wnzhd1203@naver.com</t>
+          <t>iam_more@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0507-1430-3550</t>
+          <t>0507-1451-3414</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대길 88-15 1층 왼편점포호</t>
+          <t>서울특별시 서대문구 명물길 6 9층</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailsosom</t>
+          <t>https://pf.kakao.com/_tauxad</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -8346,7 +8234,7 @@
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -8355,13 +8243,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>218</v>
+        <v>1454</v>
       </c>
       <c r="Q85" t="n">
-        <v>2</v>
+        <v>892</v>
       </c>
       <c r="R85" t="n">
-        <v>220</v>
+        <v>2346</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8370,12 +8258,12 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1529665185</t>
+          <t>387024661</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1529665185</t>
+          <t>https://m.place.naver.com/place/387024661</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -8392,39 +8280,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>티파니네일</t>
+          <t>에스뷰티</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>lovemw3@naver.com</t>
+          <t>ssooke114@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0507-1328-8847</t>
+          <t>0507-1478-9939</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 독립문로 34-1 티파니 네일</t>
+          <t>서울특별시 서대문구 증가로4길 58-11 1층</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://booking.naver.com/booking/13/bizes/936347</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -8449,13 +8337,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8464,12 +8352,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1601161816</t>
+          <t>1456809966</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1601161816</t>
+          <t>https://m.place.naver.com/place/1456809966</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -8486,29 +8374,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>수네일</t>
+          <t>알지네일</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>yjh1000j@naver.com</t>
+          <t>handsos@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1332-4612</t>
+          <t>0507-1352-1908</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로10길 16-20 1층</t>
+          <t>서울특별시 서대문구 연희로31길 9</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lovely.sunail</t>
+          <t>http://instagram.com/r.g_nail</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8543,13 +8431,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>334</v>
+        <v>20</v>
       </c>
       <c r="Q87" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="R87" t="n">
-        <v>341</v>
+        <v>31</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8558,12 +8446,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1027173445</t>
+          <t>32528538</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027173445</t>
+          <t>https://m.place.naver.com/place/32528538</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -8580,25 +8468,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>네일도행운</t>
+          <t>하미네일</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>stellacafe@naver.com</t>
+          <t>p790512@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1332-0103</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 모래내로 245 2층 더미뷰티 내부</t>
+          <t>서울특별시 서대문구 신촌로35길 3 2층 하미네일</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luck__with_nail?igsh=aWltam43aTkwdDJu&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/p790512</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8613,7 +8505,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -8624,7 +8516,7 @@
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -8633,13 +8525,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>131</v>
+        <v>15</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="R88" t="n">
-        <v>131</v>
+        <v>42</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8648,12 +8540,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>2049561266</t>
+          <t>1633156843</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2049561266</t>
+          <t>https://m.place.naver.com/place/1633156843</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -8670,30 +8562,30 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>코알라네일</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>zhdkffkekfekfo@naver.com</t>
-        </is>
-      </c>
+          <t>로렐네일</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1436-9020</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 홍제원3길 17 1층 가운데호</t>
+          <t>서울특별시 서대문구 이화여대3길 45 리브하임 B1층 로렐</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/___nail.by.koala?igsh=MWpjaDB0MjIyNHBzcw%3D%3D&amp;utm_source=qr</t>
+          <t>http://pf.kakao.com/_xcXaxgn/friend</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -8723,13 +8615,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>25</v>
+        <v>233</v>
       </c>
       <c r="Q89" t="n">
-        <v>2</v>
+        <v>86</v>
       </c>
       <c r="R89" t="n">
-        <v>27</v>
+        <v>319</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8738,12 +8630,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1997616944</t>
+          <t>1883098019</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1997616944</t>
+          <t>https://m.place.naver.com/place/1883098019</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8760,29 +8652,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>네일써니데이</t>
+          <t>루나네일</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>songhs1226@naver.com</t>
+          <t>lunamika@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0507-1403-0327</t>
+          <t>0507-1329-7109</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로10길 48-6 101호</t>
+          <t>서울특별시 서대문구 가재울미래로 15 1층 103호 루나네일</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_s.day</t>
+          <t>http://instagram.com/lunarnail__</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8817,13 +8709,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>220</v>
+        <v>10</v>
       </c>
       <c r="Q90" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>228</v>
+        <v>10</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8832,12 +8724,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1324725520</t>
+          <t>1427499799</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324725520</t>
+          <t>https://m.place.naver.com/place/1427499799</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -8854,29 +8746,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>시즈닝네일</t>
+          <t>컬러라운지 네일&amp;태닝</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>blue991013@naver.com</t>
+          <t>brushlounge@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0507-1362-1065</t>
+          <t>02-395-1196</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로40길 28</t>
+          <t>서울특별시 서대문구 통일로 461 2층</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/blue991013</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8886,12 +8778,12 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -8907,17 +8799,17 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>155</v>
+        <v>14</v>
       </c>
       <c r="Q91" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="R91" t="n">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8926,12 +8818,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1888898614</t>
+          <t>13118581</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1888898614</t>
+          <t>https://m.place.naver.com/place/13118581</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -8948,29 +8840,25 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>풋케어 로미네일</t>
+          <t>오늘네일</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>kangsogood@naver.com</t>
+          <t>barbie0903@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>0507-1301-6236</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 139 2층 좌측호</t>
+          <t>서울특별시 서대문구 이화여대5길 9 2층</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/footcare_romi_nail?igsh=cjVmanNvMWZ5OGRt</t>
+          <t>https://www.instagram.com/ilovetan_oneulnail</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9005,13 +8893,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9020,12 +8908,12 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>2080263501</t>
+          <t>1348096581</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2080263501</t>
+          <t>https://m.place.naver.com/place/1348096581</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -9042,25 +8930,25 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>모모네일</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>brenda70@naver.com</t>
-        </is>
-      </c>
+          <t>글리밍네일</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>02-312-7769</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로36가길 13-2 1층 일부호</t>
+          <t>서울특별시 서대문구 신촌로35길 10 e편한세상신촌상가 지하1층 글리밍네일</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_momo__nail</t>
+          <t>http://www.instagram.com/gleaming_nail</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9095,13 +8983,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="R93" t="n">
-        <v>157</v>
+        <v>104</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9110,12 +8998,12 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>1284552321</t>
+          <t>302039845</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284552321</t>
+          <t>https://m.place.naver.com/place/302039845</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -9132,29 +9020,25 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>마레네일</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>mm940226@naver.com</t>
-        </is>
-      </c>
+          <t>수네일</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0507-1359-9204</t>
+          <t>0507-1332-4612</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대길 64 2층</t>
+          <t>서울특별시 서대문구 증가로10길 16-20 1층</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mare.nail/</t>
+          <t>https://www.instagram.com/lovely.sunail</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9189,13 +9073,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1491</v>
+        <v>334</v>
       </c>
       <c r="Q94" t="n">
-        <v>453</v>
+        <v>7</v>
       </c>
       <c r="R94" t="n">
-        <v>1944</v>
+        <v>341</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9204,12 +9088,12 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>32465293</t>
+          <t>1027173445</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32465293</t>
+          <t>https://m.place.naver.com/place/1027173445</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -9226,29 +9110,25 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>소소람</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>sosoram-@naver.com</t>
-        </is>
-      </c>
+          <t>네일온</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0507-1312-4806</t>
+          <t>0507-1412-0791</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로28길 18 1층</t>
+          <t>서울특별시 서대문구 불광천길 264 1층좌측</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_sosoram</t>
+          <t>https://www.instagram.com/nailon_0790</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9283,13 +9163,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q95" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R95" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9298,12 +9178,12 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>2044971493</t>
+          <t>1376233513</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2044971493</t>
+          <t>https://m.place.naver.com/place/1376233513</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -9320,24 +9200,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>The서이</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>premier-music@naver.com</t>
-        </is>
-      </c>
+          <t>로뎀스킨케어</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0507-1410-5589</t>
+          <t>02-303-9955</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 수색로 100 DMC레미안e편한세상 103동상가 2호</t>
+          <t>서울특별시 서대문구 응암로 77</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9377,13 +9253,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9392,12 +9268,12 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>33928722</t>
+          <t>1985190980</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33928722</t>
+          <t>https://m.place.naver.com/place/1985190980</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
@@ -9414,29 +9290,25 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>수아라네일 가좌라운지점</t>
+          <t>모모네일</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>matata4@naver.com</t>
+          <t>brenda70@naver.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>0507-1304-0817</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 수색로 56 6층 609호</t>
+          <t>서울특별시 서대문구 통일로36가길 13-2 1층 일부호</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/sooara0817</t>
+          <t>https://www.instagram.com/_momo__nail</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -9471,13 +9343,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1640</v>
+        <v>157</v>
       </c>
       <c r="Q97" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>1648</v>
+        <v>157</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9486,12 +9358,12 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>1386960813</t>
+          <t>1284552321</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1386960813</t>
+          <t>https://m.place.naver.com/place/1284552321</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -9508,34 +9380,30 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>네일도Nail</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>ksy3315@naver.com</t>
-        </is>
-      </c>
+          <t>원더네일</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0507-1444-2889</t>
+          <t>0507-1360-1515</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 109 (신촌르메이에르타운)B109-1 네일도Nail</t>
+          <t>서울특별시 서대문구 독립문로12길 2</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sIQTg2Uc</t>
+          <t>http://pf.kakao.com/_xczxmaj</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -9565,13 +9433,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="Q98" t="n">
-        <v>121</v>
+        <v>7</v>
       </c>
       <c r="R98" t="n">
-        <v>176</v>
+        <v>45</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9580,12 +9448,12 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>1887906221</t>
+          <t>37196672</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1887906221</t>
+          <t>https://m.place.naver.com/place/37196672</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -9602,29 +9470,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>마디마다네일</t>
+          <t>더 꼼네일</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>z1004__@naver.com</t>
+          <t>kjuuu0716@naver.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0507-1326-2539</t>
+          <t>0507-1322-3992</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 149 206호</t>
+          <t>서울특별시 서대문구 명지대길 56 1층</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/madi_mada_nail/</t>
+          <t>http://instagram.com/the_kkom</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9659,13 +9527,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>804</v>
+        <v>81</v>
       </c>
       <c r="Q99" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="R99" t="n">
-        <v>821</v>
+        <v>146</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9674,12 +9542,12 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>1156545059</t>
+          <t>1616221232</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156545059</t>
+          <t>https://m.place.naver.com/place/1616221232</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -9696,12 +9564,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>네일홍</t>
+          <t>숨네일</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>jjanga4774@naver.com</t>
+          <t>traineran@naver.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -9709,12 +9577,12 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 서소문로 21 충정타워빌딩 지하1층</t>
+          <t>서울특별시 서대문구 홍은중앙로 100-2 1층</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jjanga4774</t>
+          <t>https://www.instagram.com/sumnail9901</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -9729,7 +9597,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -9745,17 +9613,17 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>126</v>
+        <v>26</v>
       </c>
       <c r="Q100" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="R100" t="n">
-        <v>151</v>
+        <v>27</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -9764,12 +9632,12 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>35624131</t>
+          <t>1326174975</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35624131</t>
+          <t>https://m.place.naver.com/place/1326174975</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
@@ -9786,25 +9654,25 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>한예진뷰티디자인</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>bijou-artist@naver.com</t>
-        </is>
-      </c>
+          <t>오네일드잇 신촌점</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>0507-1379-5740</t>
+        </is>
+      </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 189</t>
+          <t>서울특별시 서대문구 신촌로 123 2층</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/oh_nailed_it</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9814,7 +9682,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -9835,17 +9703,17 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>603</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -9854,12 +9722,12 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>1388645750</t>
+          <t>1930241791</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1388645750</t>
+          <t>https://m.place.naver.com/place/1930241791</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
@@ -9876,34 +9744,30 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>네일어라모드 홍대점</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>icanbemyself@naver.com</t>
-        </is>
-      </c>
+          <t>달달한네일</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>070-8844-3030</t>
+          <t>0507-1433-3262</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로3가길 3-4 3층 301호</t>
+          <t>서울특별시 서대문구 세무서2길 16 1층 2호</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xfYVQj/chat</t>
+          <t>https://www.instagram.com/thedaldalnail</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -9924,7 +9788,7 @@
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -9933,13 +9797,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>572</v>
+        <v>233</v>
       </c>
       <c r="Q102" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="R102" t="n">
-        <v>612</v>
+        <v>323</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -9948,12 +9812,12 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>1086898312</t>
+          <t>1257856428</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1086898312</t>
+          <t>https://m.place.naver.com/place/1257856428</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -9970,29 +9834,25 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>오네일드잇 신촌점</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>travelsudal@naver.com</t>
-        </is>
-      </c>
+          <t>모뜨네일</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>0507-1379-5740</t>
+          <t>0507-1385-6099</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 123 2층</t>
+          <t>서울특별시 서대문구 이화여대1안길 25 2층 203호</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oh_nailed_it</t>
+          <t>https://www.instagram.com/mott.nail</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -10027,13 +9887,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>602</v>
+        <v>1331</v>
       </c>
       <c r="Q103" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="R103" t="n">
-        <v>611</v>
+        <v>1373</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -10042,12 +9902,12 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>1930241791</t>
+          <t>1774073621</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1930241791</t>
+          <t>https://m.place.naver.com/place/1774073621</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
@@ -10064,29 +9924,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>네일오엔</t>
+          <t>살롱드선네일</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>checkmate_out@naver.com</t>
+          <t>jam_d@naver.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>0507-1362-3291</t>
+          <t>0507-1338-2605</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로7길 58 102호</t>
+          <t>서울특별시 서대문구 북아현로1가길 20 이편한세상신촌 1단지상가 110호</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.oen?igsh=c2poN3MxZG5kcmR1&amp;utm_source=qr</t>
+          <t>http://instagram.com/salonde_seon</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -10112,7 +9972,7 @@
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -10121,13 +9981,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="Q104" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R104" t="n">
-        <v>3</v>
+        <v>438</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -10136,12 +9996,12 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>1478444590</t>
+          <t>1688455455</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1478444590</t>
+          <t>https://m.place.naver.com/place/1688455455</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
@@ -10158,29 +10018,25 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>컬러라운지 네일&amp;태닝</t>
+          <t>디디뷰티</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>brushlounge@naver.com</t>
+          <t>ddb0301@naver.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>02-395-1196</t>
-        </is>
-      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 461 2층</t>
+          <t>서울특별시 서대문구 세무서8길 30 상가 B1(2층) 41호 디디뷰티</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ddb0301</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10190,12 +10046,12 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -10211,17 +10067,17 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>14</v>
+        <v>271</v>
       </c>
       <c r="Q105" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="R105" t="n">
-        <v>15</v>
+        <v>288</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -10230,12 +10086,12 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>13118581</t>
+          <t>1056660215</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13118581</t>
+          <t>https://m.place.naver.com/place/1056660215</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
@@ -10252,25 +10108,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>수네일</t>
+          <t>네일살롱</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>yjh1000j@naver.com</t>
+          <t>wing3527@naver.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>0507-1303-0241</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세검정로1길 50 1층 수네일</t>
+          <t>서울특별시 서대문구 연희맛로 20 연희빌딩 1층 1호네일실롱</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>http://instagram.com/soonail_kim</t>
+          <t>http://instagram.com/nailsalon7775</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -10305,13 +10165,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="Q106" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="R106" t="n">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -10320,12 +10180,12 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>1835439095</t>
+          <t>1527535605</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835439095</t>
+          <t>https://m.place.naver.com/place/1527535605</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -10342,29 +10202,29 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>하미네일</t>
+          <t>프로젝트 앨리스</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>p790512@naver.com</t>
+          <t>uer1130@naver.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0507-1332-0103</t>
+          <t>0507-1383-3681</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로35길 3 2층 하미네일</t>
+          <t>서울특별시 서대문구 세검정로3길 38-2 1층</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/p790512</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -10374,12 +10234,12 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -10395,18 +10255,18 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P107" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="Q107" t="n">
+        <v>1</v>
+      </c>
+      <c r="R107" t="n">
         <v>27</v>
       </c>
-      <c r="R107" t="n">
-        <v>42</v>
-      </c>
       <c r="S107" t="inlineStr">
         <is>
           <t>X</t>
@@ -10414,12 +10274,12 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>1633156843</t>
+          <t>1788377896</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1633156843</t>
+          <t>https://m.place.naver.com/place/1788377896</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
@@ -10436,29 +10296,25 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>위드네일</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>hahaha_1226@naver.com</t>
-        </is>
-      </c>
+          <t>토드네일</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0507-1308-2035</t>
+          <t>0507-1486-0620</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 홍제천로 158 1층</t>
+          <t>서울특별시 서대문구 이화여대5길 35 지하1층 114호</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/with.nail_</t>
+          <t>https://www.instagram.com/todnail_</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -10493,13 +10349,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>27</v>
+        <v>436</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R108" t="n">
-        <v>27</v>
+        <v>466</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -10508,12 +10364,12 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>2099359388</t>
+          <t>1674577867</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099359388</t>
+          <t>https://m.place.naver.com/place/1674577867</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
@@ -10530,29 +10386,29 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>솔하네일</t>
+          <t>손에담다</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>feltbeats90@naver.com</t>
+          <t>kjy88990@naver.com</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0507-1329-2315</t>
+          <t>0507-1307-7876</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 응암로1길 15 1층</t>
+          <t>서울특별시 서대문구 통일로 153 손에담다</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>http://instagram.com/solhanail</t>
+          <t>http://instagram.com/sonedamda</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -10587,13 +10443,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="Q109" t="n">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="R109" t="n">
-        <v>216</v>
+        <v>163</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -10602,12 +10458,12 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>1476338581</t>
+          <t>1681218410</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1476338581</t>
+          <t>https://m.place.naver.com/place/1681218410</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
@@ -10624,25 +10480,29 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>썸네일</t>
+          <t>네일이끌림</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>hackerstalk11@naver.com</t>
+          <t>nail_drag@naver.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>02-393-9948</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대길 58</t>
+          <t>서울특별시 서대문구 신촌로35길 10</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/cong__vely</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -10652,7 +10512,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -10673,17 +10533,17 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="Q110" t="n">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="R110" t="n">
-        <v>2</v>
+        <v>131</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -10692,12 +10552,12 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>1217647474</t>
+          <t>1698891603</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1217647474</t>
+          <t>https://m.place.naver.com/place/1698891603</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -10714,29 +10574,25 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>손에담다</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>kjy88990@naver.com</t>
-        </is>
-      </c>
+          <t>빔빔네일</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>0507-1307-7876</t>
+          <t>0507-1406-5642</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 153 손에담다</t>
+          <t>서울특별시 서대문구 세무서길 77 1층</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>http://instagram.com/sonedamda</t>
+          <t>http://www.instagram.com/beam2nail</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -10771,13 +10627,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="Q111" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="R111" t="n">
-        <v>163</v>
+        <v>21</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -10786,12 +10642,12 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>1681218410</t>
+          <t>84828356</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1681218410</t>
+          <t>https://m.place.naver.com/place/84828356</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
@@ -10808,29 +10664,29 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>베이네일</t>
+          <t>코이네일</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>4chi_27@naver.com</t>
+          <t>qwas1262@naver.com</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>0507-1337-7446</t>
+          <t>0507-1494-6711</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로 217</t>
+          <t>서울특별시 서대문구 세검정로 46 1층 9호</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/baeynail</t>
+          <t>https://www.instagram.com/k.o.i.nail/</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10865,13 +10721,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="Q112" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="R112" t="n">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -10880,12 +10736,12 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>1239283152</t>
+          <t>1956411597</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1239283152</t>
+          <t>https://m.place.naver.com/place/1956411597</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
@@ -10902,29 +10758,25 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>코이네일</t>
+          <t>네일홍</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>qwas1262@naver.com</t>
+          <t>jjanga4774@naver.com</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>0507-1494-6711</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세검정로 46 1층 9호</t>
+          <t>서울특별시 서대문구 서소문로 21 충정타워빌딩 지하1층</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/k.o.i.nail/</t>
+          <t>https://blog.naver.com/jjanga4774</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10939,7 +10791,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -10955,17 +10807,17 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P113" t="n">
-        <v>163</v>
+        <v>126</v>
       </c>
       <c r="Q113" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="R113" t="n">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -10974,12 +10826,12 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>1956411597</t>
+          <t>35624131</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1956411597</t>
+          <t>https://m.place.naver.com/place/35624131</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
@@ -10996,29 +10848,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>알지네일</t>
+          <t>아띠네일</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>handsos@naver.com</t>
+          <t>attinail_@naver.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>0507-1352-1908</t>
+          <t>0507-1322-6612</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로31길 9</t>
+          <t>서울특별시 서대문구 통일로 193 2층 아띠네일</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>http://instagram.com/r.g_nail</t>
+          <t>http://www.instagram.com/addi_nail_/</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -11053,13 +10905,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>20</v>
+        <v>345</v>
       </c>
       <c r="Q114" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="R114" t="n">
-        <v>31</v>
+        <v>386</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -11068,12 +10920,12 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>32528538</t>
+          <t>1631947370</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32528538</t>
+          <t>https://m.place.naver.com/place/1631947370</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
@@ -11090,29 +10942,29 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>네일소브 북가좌본점</t>
+          <t>뮤즈네일</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>hbs2002i@naver.com</t>
+          <t>jiji012636@naver.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>0507-1448-3319</t>
+          <t>0507-1300-4636</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 거북골로 184 1층 좌측중앙(네일샵)</t>
+          <t>서울특별시 서대문구 인왕시장길 18</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_sove</t>
+          <t>https://blog.naver.com/jiji012636</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -11127,7 +10979,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -11147,13 +10999,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>105</v>
+        <v>3</v>
       </c>
       <c r="Q115" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="R115" t="n">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -11162,12 +11014,12 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>1192995175</t>
+          <t>1179732435</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1192995175</t>
+          <t>https://m.place.naver.com/place/1179732435</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
@@ -11184,29 +11036,29 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>네일뭐해</t>
+          <t>솔하네일</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>mementomori-24@naver.com</t>
+          <t>feltbeats90@naver.com</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>0507-1340-8272</t>
+          <t>0507-1329-2315</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 가좌로 111 상가1층</t>
+          <t>서울특별시 서대문구 응암로1길 15 1층</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_mohe/</t>
+          <t>http://instagram.com/solhanail</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -11241,13 +11093,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>702</v>
+        <v>177</v>
       </c>
       <c r="Q116" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="R116" t="n">
-        <v>752</v>
+        <v>216</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -11256,12 +11108,12 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>533976950</t>
+          <t>1476338581</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/533976950</t>
+          <t>https://m.place.naver.com/place/1476338581</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
@@ -11278,29 +11130,25 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>디에고푸스 연희점 네일바이은</t>
+          <t>썸네일</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>kwonbinus@naver.com</t>
+          <t>hackerstalk11@naver.com</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>0507-1412-1747</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희맛로 17-49</t>
+          <t>서울특별시 서대문구 이화여대길 58</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nailbyeun</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -11310,7 +11158,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -11331,17 +11179,17 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P117" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>109</v>
+        <v>2</v>
       </c>
       <c r="R117" t="n">
-        <v>208</v>
+        <v>2</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -11350,12 +11198,12 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>37452801</t>
+          <t>1217647474</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37452801</t>
+          <t>https://m.place.naver.com/place/1217647474</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
@@ -11372,34 +11220,34 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>로렐네일</t>
+          <t>위드앤네일</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>mchavzezy@naver.com</t>
+          <t>jelly0355@naver.com</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>0507-1436-9020</t>
+          <t>0507-1322-3690</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대3길 45 리브하임 B1층 로렐</t>
+          <t>서울특별시 서대문구 통일로 510 상가212호 위드앤네일</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xcXaxgn/friend</t>
+          <t>http://www.instagram.com/_with_n_nail_</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -11420,7 +11268,7 @@
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -11429,13 +11277,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>233</v>
+        <v>22</v>
       </c>
       <c r="Q118" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>319</v>
+        <v>22</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -11444,12 +11292,12 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>1883098019</t>
+          <t>1070279609</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1883098019</t>
+          <t>https://m.place.naver.com/place/1070279609</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
@@ -11466,29 +11314,29 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>윈디네일 내성발톱 무좀 발각질 문제성발</t>
+          <t>공간네일 신촌점</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>winner-d@naver.com</t>
+          <t>tomi6@naver.com</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>0507-1367-5855</t>
+          <t>0507-1367-0798</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 응암로 43 두정빌딩 1층</t>
+          <t>서울특별시 서대문구 명물길 49 3층</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/win_d_nail</t>
+          <t>https://linktr.ee/gonggan_sc</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -11503,7 +11351,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -11514,22 +11362,22 @@
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P119" t="n">
-        <v>461</v>
+        <v>1760</v>
       </c>
       <c r="Q119" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="R119" t="n">
-        <v>522</v>
+        <v>1813</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -11538,12 +11386,12 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>1287346768</t>
+          <t>1412908076</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1287346768</t>
+          <t>https://m.place.naver.com/place/1412908076</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
@@ -11560,29 +11408,25 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>네일샘</t>
+          <t>수네일</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>namyuri1004@naver.com</t>
+          <t>yjh1000j@naver.com</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>02-312-0744</t>
-        </is>
-      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로 50</t>
+          <t>서울특별시 서대문구 세검정로1길 50 1층 수네일</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/soonail_kim</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -11592,7 +11436,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -11613,17 +11457,17 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -11632,12 +11476,12 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>813067384</t>
+          <t>1835439095</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/813067384</t>
+          <t>https://m.place.naver.com/place/1835439095</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
@@ -11654,29 +11498,29 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>루블리뷰티</t>
+          <t>네일미야오</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>i_believe28@naver.com</t>
+          <t>traveler_01@naver.com</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>0507-1352-9350</t>
+          <t>0507-1471-2420</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로 27 3층</t>
+          <t>서울특별시 서대문구 신촌역로 17 203호</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lu_vely_beauty</t>
+          <t>https://www.instagram.com/nailmeow.2025?igsh=NDNhbmw0ZGgxN3d0</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -11711,13 +11555,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="Q121" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="R121" t="n">
-        <v>96</v>
+        <v>148</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -11726,12 +11570,12 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>1078815275</t>
+          <t>1516469775</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1078815275</t>
+          <t>https://m.place.naver.com/place/1516469775</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
@@ -11748,29 +11592,25 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>포쉬네일 하이푸스 신촌점</t>
+          <t>네일도행운</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>freegirl11@naver.com</t>
+          <t>stellacafe@naver.com</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>0507-1335-4241</t>
-        </is>
-      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 73 2층</t>
+          <t>서울특별시 서대문구 모래내로 245 2층 더미뷰티 내부</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sh_forsynail</t>
+          <t>https://www.instagram.com/luck__with_nail?igsh=aWltam43aTkwdDJu&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -11796,7 +11636,7 @@
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -11805,13 +11645,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>3133</v>
+        <v>131</v>
       </c>
       <c r="Q122" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>3470</v>
+        <v>131</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -11820,12 +11660,12 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>1944620503</t>
+          <t>2049561266</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1944620503</t>
+          <t>https://m.place.naver.com/place/2049561266</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
@@ -11842,29 +11682,29 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>네일넘버8</t>
+          <t>윈디네일 내성발톱 무좀 발각질 문제성발</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>sjhfox2000@naver.com</t>
+          <t>winner-d@naver.com</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>02-365-8008</t>
+          <t>0507-1367-5855</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌역로 7</t>
+          <t>서울특별시 서대문구 응암로 43 두정빌딩 1층</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/win_d_nail</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -11874,7 +11714,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -11895,17 +11735,17 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P123" t="n">
-        <v>5</v>
+        <v>461</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="R123" t="n">
-        <v>5</v>
+        <v>522</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -11914,12 +11754,12 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>35751127</t>
+          <t>1287346768</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35751127</t>
+          <t>https://m.place.naver.com/place/1287346768</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
@@ -11936,29 +11776,25 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>네일미야오</t>
+          <t>아이원네일아트</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>traveler_01@naver.com</t>
+          <t>fpwlsk8877@naver.com</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>0507-1471-2420</t>
-        </is>
-      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌역로 17 203호</t>
+          <t>서울특별시 서대문구 연세로5길 38 1층</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailmeow.2025?igsh=NDNhbmw0ZGgxN3d0</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -11968,7 +11804,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -11989,17 +11825,17 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P124" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="Q124" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R124" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -12008,12 +11844,12 @@
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>1516469775</t>
+          <t>1544991635</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1516469775</t>
+          <t>https://m.place.naver.com/place/1544991635</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
@@ -12030,29 +11866,29 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>네일, 여유</t>
+          <t>유네일</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>knl_95@naver.com</t>
+          <t>luvu1016@naver.com</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>0507-1433-1620</t>
+          <t>0507-1412-2114</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 간호대로2길 9 1층</t>
+          <t>서울특별시 서대문구 증가로24마길 47 1층</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail.healing_</t>
+          <t>https://www.instagram.com/_u_nail_</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -12087,13 +11923,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>179</v>
+        <v>231</v>
       </c>
       <c r="Q125" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="R125" t="n">
-        <v>211</v>
+        <v>267</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -12102,12 +11938,12 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>1492064846</t>
+          <t>1610895712</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1492064846</t>
+          <t>https://m.place.naver.com/place/1610895712</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
@@ -12124,29 +11960,25 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>아모이네일스튜디오</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>morningarden@naver.com</t>
-        </is>
-      </c>
+          <t>안젤리크네일</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>0507-1439-5957</t>
+          <t>070-8648-3432</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로27길 43 1층 102호</t>
+          <t>서울특별시 서대문구 북아현동 199-1 힐스테이트신촌상가 105호</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_dxaVan/chat</t>
+          <t>http://pf.kakao.com/_qZgeb</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -12177,17 +12009,17 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P126" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="Q126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R126" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -12196,12 +12028,12 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>2066634292</t>
+          <t>1976256692</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2066634292</t>
+          <t>https://m.place.naver.com/place/1976256692</t>
         </is>
       </c>
       <c r="V126" t="inlineStr">
@@ -12221,11 +12053,7 @@
           <t>마브뷰티아카데미</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>omab_academy@naver.com</t>
-        </is>
-      </c>
+      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>

--- a/naver-place-crawler/results_nail/서대문_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/서대문_네일샵.xlsx
@@ -564,29 +564,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>멜트네일</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ckckcl1357@naver.com</t>
-        </is>
-      </c>
+          <t>메이퀸네일살롱</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0507-1323-6269</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로 85 인사이드빌딩 1층 104호</t>
+          <t>서울특별시 서대문구 신촌로 169-7 이대포레스트 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/melt_nail_/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +588,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -612,22 +604,22 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +628,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1591157927</t>
+          <t>82617755</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1591157927</t>
+          <t>https://m.place.naver.com/place/82617755</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,24 +650,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>네일샘</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>namyuri1004@naver.com</t>
-        </is>
-      </c>
+          <t>연희동네일</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>02-312-0744</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로 50</t>
+          <t>서울특별시 서대문구 연희로11길 22</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -715,13 +699,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +714,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>813067384</t>
+          <t>1631395937</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/813067384</t>
+          <t>https://m.place.naver.com/place/1631395937</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +736,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>네일온</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>nailon22@naver.com</t>
-        </is>
-      </c>
+          <t>네일도Nail</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1331-5593</t>
+          <t>0507-1444-2889</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 충정로9길 4 2층(충정로2가)</t>
+          <t>서울특별시 서대문구 신촌로 109 (신촌르메이에르타운)B109-1 네일도Nail</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailon22</t>
+          <t>https://open.kakao.com/o/sIQTg2Uc</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +769,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -800,7 +780,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +789,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>447</v>
+        <v>55</v>
       </c>
       <c r="Q4" t="n">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="R4" t="n">
-        <v>578</v>
+        <v>176</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +804,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1272307920</t>
+          <t>1887906221</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1272307920</t>
+          <t>https://m.place.naver.com/place/1887906221</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,34 +826,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일 아이보리</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>052young@naver.com</t>
-        </is>
-      </c>
+          <t>네일살롱</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1463-7021</t>
+          <t>0507-1303-0241</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대5길 35 신촌영타운지웰에스테이트 상가동 2층 네일, 아이보리</t>
+          <t>서울특별시 서대문구 연희맛로 20 연희빌딩 1층 1호네일실롱</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/770181/items/4634924</t>
+          <t>http://instagram.com/nailsalon7775</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -903,13 +879,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>240</v>
+        <v>38</v>
       </c>
       <c r="Q5" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="R5" t="n">
-        <v>276</v>
+        <v>83</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +894,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1572186883</t>
+          <t>1527535605</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1572186883</t>
+          <t>https://m.place.naver.com/place/1527535605</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,25 +916,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>모모네일</t>
+          <t>멜트네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>brenda70@naver.com</t>
+          <t>ckckcl1357@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1323-6269</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로36가길 13-2 1층 일부호</t>
+          <t>서울특별시 서대문구 연희로 85 인사이드빌딩 1층 104호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_momo__nail</t>
+          <t>https://www.instagram.com/melt_nail_/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -984,7 +964,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -993,13 +973,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>157</v>
+        <v>93</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R6" t="n">
-        <v>157</v>
+        <v>103</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,12 +988,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1284552321</t>
+          <t>1591157927</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284552321</t>
+          <t>https://m.place.naver.com/place/1591157927</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1030,29 +1010,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>유네일</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>luvu1016@naver.com</t>
-        </is>
-      </c>
+          <t>손에담다</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1412-2114</t>
+          <t>0507-1307-7876</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로24마길 47 1층</t>
+          <t>서울특별시 서대문구 통일로 153 손에담다</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_u_nail_</t>
+          <t>http://instagram.com/sonedamda</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,13 +1063,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>231</v>
+        <v>83</v>
       </c>
       <c r="Q7" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="R7" t="n">
-        <v>267</v>
+        <v>163</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,12 +1078,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1610895712</t>
+          <t>1681218410</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1610895712</t>
+          <t>https://m.place.naver.com/place/1681218410</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1124,35 +1100,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>행복한 네일</t>
+          <t>네일뿐</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>etbjj@naver.com</t>
+          <t>cuiyushan20-19@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1487-1503</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로 204 상가동 1층 105호</t>
+          <t>서울특별시 서대문구 신촌로 127 2층 205호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_Fhxemxj</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1168,22 +1148,22 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R8" t="n">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,12 +1172,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2064316137</t>
+          <t>1627245540</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2064316137</t>
+          <t>https://m.place.naver.com/place/1627245540</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1214,29 +1194,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>메리제이네일</t>
+          <t>동네살롱</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>tnsend3020@naver.com</t>
+          <t>naverofficial@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1424-8411</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 거북골로 120 제상가 2동 2층 13호</t>
+          <t>서울특별시 서대문구 가재울로6길 53-55 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://instagram.com/merry_j_nail</t>
+          <t>http://instagram.com/dn.salon</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1271,13 +1247,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="R9" t="n">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,12 +1262,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>42246094</t>
+          <t>1209907072</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/42246094</t>
+          <t>https://m.place.naver.com/place/1209907072</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1308,34 +1284,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>루블리뷰티</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>i_believe28@naver.com</t>
-        </is>
-      </c>
+          <t>안젤리크네일</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1352-9350</t>
+          <t>070-8648-3432</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로 27 3층</t>
+          <t>서울특별시 서대문구 북아현동 199-1 힐스테이트신촌상가 105호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lu_vely_beauty</t>
+          <t>http://pf.kakao.com/_qZgeb</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1356,22 +1328,22 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="Q10" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,12 +1352,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1078815275</t>
+          <t>1976256692</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1078815275</t>
+          <t>https://m.place.naver.com/place/1976256692</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1402,29 +1374,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>영네일</t>
+          <t>베이네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>youngnail423@naver.com</t>
+          <t>4chi_27@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1368-4230</t>
+          <t>0507-1337-7446</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 109 르메이에르타운5 B103-3</t>
+          <t>서울특별시 서대문구 증가로 217</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/youngnail423</t>
+          <t>https://www.instagram.com/baeynail</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1439,7 +1411,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1459,13 +1431,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="Q11" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,12 +1446,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>36505109</t>
+          <t>1239283152</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36505109</t>
+          <t>https://m.place.naver.com/place/1239283152</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1496,29 +1468,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>마레네일</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>mm940226@naver.com</t>
-        </is>
-      </c>
+          <t>풋케어 로미네일</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1359-9204</t>
+          <t>0507-1301-6236</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대길 64 2층</t>
+          <t>서울특별시 서대문구 통일로 139 2층 좌측호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mare.nail/</t>
+          <t>https://www.instagram.com/footcare_romi_nail?igsh=cjVmanNvMWZ5OGRt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1553,13 +1521,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1494</v>
+        <v>8</v>
       </c>
       <c r="Q12" t="n">
-        <v>453</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1947</v>
+        <v>8</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,12 +1536,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>32465293</t>
+          <t>2080263501</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32465293</t>
+          <t>https://m.place.naver.com/place/2080263501</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1590,29 +1558,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>시즈닝네일</t>
+          <t>네일에비뉴_연세대</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>blue991013@naver.com</t>
+          <t>dyk6614@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1362-1065</t>
+          <t>0507-1377-0744</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로40길 28</t>
+          <t>서울특별시 서대문구 연세로 50 학생회관 지하1층 헤어에비뉴 內 네일에비뉴</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/blue991013</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1622,12 +1590,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1643,17 +1611,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>155</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>207</v>
+        <v>2</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,12 +1630,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1888898614</t>
+          <t>1303420092</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1888898614</t>
+          <t>https://m.place.naver.com/place/1303420092</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1684,29 +1652,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>미호네일</t>
+          <t>마디마다네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>kikijj0206@naver.com</t>
+          <t>z1004__@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>02-303-4117</t>
+          <t>0507-1326-2539</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 가재울미래로 2 205동상가 104-2 미호네일</t>
+          <t>서울특별시 서대문구 신촌로 149 206호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_in_miho</t>
+          <t>https://www.instagram.com/madi_mada_nail/</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1732,7 +1700,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1741,13 +1709,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>10</v>
+        <v>804</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="R14" t="n">
-        <v>12</v>
+        <v>821</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,12 +1724,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1494438581</t>
+          <t>1156545059</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1494438581</t>
+          <t>https://m.place.naver.com/place/1156545059</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1778,29 +1746,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>토드네일</t>
+          <t>알지네일</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0728helen@naver.com</t>
+          <t>handsos@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1486-0620</t>
+          <t>0507-1352-1908</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대5길 35 지하1층 114호</t>
+          <t>서울특별시 서대문구 연희로31길 9</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/todnail_</t>
+          <t>http://instagram.com/r.g_nail</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1826,7 +1794,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1835,13 +1803,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>438</v>
+        <v>20</v>
       </c>
       <c r="Q15" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="R15" t="n">
-        <v>468</v>
+        <v>31</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,12 +1818,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1674577867</t>
+          <t>32528538</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1674577867</t>
+          <t>https://m.place.naver.com/place/32528538</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1872,29 +1840,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>프로젝트 앨리스</t>
+          <t>네일, 여유</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>uer1130@naver.com</t>
+          <t>knl_95@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1383-3681</t>
+          <t>0507-1433-1620</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세검정로3길 38-2 1층</t>
+          <t>서울특별시 서대문구 간호대로2길 9 1층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/nail.healing_</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1904,7 +1872,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1925,17 +1893,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>26</v>
+        <v>179</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>27</v>
+        <v>211</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,12 +1912,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1788377896</t>
+          <t>1492064846</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1788377896</t>
+          <t>https://m.place.naver.com/place/1492064846</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1966,29 +1934,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>네일넘버8</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>bcysfinder@naver.com</t>
-        </is>
-      </c>
+          <t>스윕네일</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>02-365-8008</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌역로 7</t>
+          <t>서울특별시 서대문구 이화여대5길 35 지하1층 104호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/sweepnail/</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1998,7 +1958,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2019,17 +1979,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5</v>
+        <v>178</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>5</v>
+        <v>181</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2038,12 +1998,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>35751127</t>
+          <t>1462276902</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35751127</t>
+          <t>https://m.place.naver.com/place/1462276902</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2060,24 +2020,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>네일에비뉴_연세대</t>
+          <t>아이원네일아트</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dyk6614@naver.com</t>
+          <t>fpwlsk8877@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1377-0744</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로 50 학생회관 지하1층 헤어에비뉴 內 네일에비뉴</t>
+          <t>서울특별시 서대문구 연세로5길 38 1층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2117,13 +2073,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>148</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>152</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2132,12 +2088,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1303420092</t>
+          <t>1544991635</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1303420092</t>
+          <t>https://m.place.naver.com/place/1544991635</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2154,39 +2110,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>네일올리브 신촌 연대캠퍼스점</t>
+          <t>네일까사</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>megu03@naver.com</t>
+          <t>ptypoohpooh0820@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>02-2123-8273</t>
+          <t>0507-1404-1654</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로 50 연세대학교 내 국제학사 지하 2층</t>
+          <t>서울특별시 서대문구 연세로4길 28 2F</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>http://www.nailolive.com/</t>
+          <t>http://www.instagram.com/nailcasa</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2207,17 +2163,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>144</v>
+        <v>255</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="R19" t="n">
-        <v>144</v>
+        <v>304</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2226,12 +2182,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>13332586</t>
+          <t>38015918</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13332586</t>
+          <t>https://m.place.naver.com/place/38015918</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2248,29 +2204,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>하미네일</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>p790512@naver.com</t>
-        </is>
-      </c>
+          <t>프로젝트 앨리스</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1332-0103</t>
+          <t>0507-1383-3681</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로35길 3 2층 하미네일</t>
+          <t>서울특별시 서대문구 세검정로3길 38-2 1층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/p790512</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2280,12 +2232,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2301,18 +2253,18 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
         <v>27</v>
       </c>
-      <c r="R20" t="n">
-        <v>42</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>X</t>
@@ -2320,12 +2272,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1633156843</t>
+          <t>1788377896</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1633156843</t>
+          <t>https://m.place.naver.com/place/1788377896</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2342,30 +2294,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>더네일</t>
+          <t>소소람</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>thenail7282@naver.com</t>
+          <t>theokh@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1312-4806</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 서소문로 43-22 한흥빌딩 2층 더 네일</t>
+          <t>서울특별시 서대문구 연희로28길 18 1층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_mYaaxl</t>
+          <t>https://www.instagram.com/_sosoram</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2386,7 +2342,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2395,13 +2351,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="Q21" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="R21" t="n">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2410,12 +2366,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1800993616</t>
+          <t>2044971493</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1800993616</t>
+          <t>https://m.place.naver.com/place/2044971493</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2432,25 +2388,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>동네살롱</t>
+          <t>메리제이네일</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>naverofficial@naver.com</t>
+          <t>tnsend3020@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1424-8411</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 가재울로6길 53-55 1층</t>
+          <t>서울특별시 서대문구 거북골로 120 제상가 2동 2층 13호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>http://instagram.com/dn.salon</t>
+          <t>http://instagram.com/merry_j_nail</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2485,13 +2445,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="Q22" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2500,12 +2460,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1209907072</t>
+          <t>42246094</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1209907072</t>
+          <t>https://m.place.naver.com/place/42246094</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2522,29 +2482,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>제이앤제이네일</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>sallyhome_@naver.com</t>
-        </is>
-      </c>
+          <t>리즈네일</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1342-8430</t>
+          <t>0507-1491-2458</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 402 1층 제이엔제이네일</t>
+          <t>서울특별시 서대문구 연세로7안길 1 3층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_fMNYxj</t>
+          <t>http://pf.kakao.com/_KQAFn</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2579,13 +2535,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>78</v>
+        <v>6</v>
       </c>
       <c r="Q23" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>127</v>
+        <v>8</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2594,12 +2550,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1722436082</t>
+          <t>2007984773</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722436082</t>
+          <t>https://m.place.naver.com/place/2007984773</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2616,29 +2572,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>티파니네일</t>
+          <t>뮤즈네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>lovemw3@naver.com</t>
+          <t>jiji012636@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1328-8847</t>
+          <t>0507-1300-4636</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 독립문로 34-1 티파니 네일</t>
+          <t>서울특별시 서대문구 인왕시장길 18</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/jiji012636</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2648,12 +2604,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2669,17 +2625,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="R24" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2688,12 +2644,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1601161816</t>
+          <t>1179732435</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1601161816</t>
+          <t>https://m.place.naver.com/place/1179732435</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2710,29 +2666,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>네일오엔</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>checkmate_out@naver.com</t>
-        </is>
-      </c>
+          <t>썸네일</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0507-1362-3291</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로7길 58 102호</t>
+          <t>서울특별시 서대문구 이화여대길 58</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.oen?igsh=c2poN3MxZG5kcmR1&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2742,7 +2690,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2758,22 +2706,22 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2782,12 +2730,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1478444590</t>
+          <t>1217647474</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1478444590</t>
+          <t>https://m.place.naver.com/place/1217647474</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2804,34 +2752,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>위드앤네일</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>jelly0355@naver.com</t>
-        </is>
-      </c>
+          <t>에스뷰티</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1322-3690</t>
+          <t>0507-1478-9939</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 510 상가212호 위드앤네일</t>
+          <t>서울특별시 서대문구 증가로4길 58-11 1층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/_with_n_nail_</t>
+          <t>https://booking.naver.com/booking/13/bizes/936347</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2857,17 +2801,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2876,12 +2820,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1070279609</t>
+          <t>1456809966</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1070279609</t>
+          <t>https://m.place.naver.com/place/1456809966</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2898,29 +2842,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>아띠네일</t>
+          <t>루미가넷 현대백화점 신촌점</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>attinail_@naver.com</t>
+          <t>nuroonge@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1322-6612</t>
+          <t>0507-1461-9296</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 193 2층 아띠네일</t>
+          <t>서울특별시 서대문구 신촌로 83 현대백화점신촌점 3F</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/addi_nail_/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2930,7 +2874,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2951,17 +2895,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>345</v>
+        <v>67</v>
       </c>
       <c r="Q27" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="R27" t="n">
-        <v>386</v>
+        <v>81</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2970,12 +2914,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1631947370</t>
+          <t>31229559</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1631947370</t>
+          <t>https://m.place.naver.com/place/31229559</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2992,29 +2936,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네일소솜</t>
+          <t>디에고푸스 연희점 네일바이은</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>wnzhd1203@naver.com</t>
+          <t>kwonbinus@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1430-3550</t>
+          <t>0507-1412-1747</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대길 88-15 1층 왼편점포호</t>
+          <t>서울특별시 서대문구 연희맛로 17-49</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailsosom</t>
+          <t>http://www.instagram.com/nailbyeun</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3049,13 +2993,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>218</v>
+        <v>99</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>109</v>
       </c>
       <c r="R28" t="n">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3064,12 +3008,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1529665185</t>
+          <t>37452801</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1529665185</t>
+          <t>https://m.place.naver.com/place/37452801</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3086,29 +3030,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>루미가넷 현대백화점 신촌점</t>
+          <t>아띠네일</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>nuroonge@naver.com</t>
+          <t>attinail_@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1461-9296</t>
+          <t>0507-1322-6612</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 83 현대백화점신촌점 3F</t>
+          <t>서울특별시 서대문구 통일로 193 2층 아띠네일</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/addi_nail_/</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3118,7 +3062,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3139,17 +3083,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>67</v>
+        <v>345</v>
       </c>
       <c r="Q29" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="R29" t="n">
-        <v>81</v>
+        <v>386</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3158,12 +3102,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>31229559</t>
+          <t>1631947370</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31229559</t>
+          <t>https://m.place.naver.com/place/1631947370</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3180,25 +3124,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>코알라네일</t>
+          <t>네일미야오</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>zhdkffkekfekfo@naver.com</t>
+          <t>traveler_01@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1471-2420</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 홍제원3길 17 1층 가운데호</t>
+          <t>서울특별시 서대문구 신촌역로 17 203호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/___nail.by.koala?igsh=MWpjaDB0MjIyNHBzcw%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/nailmeow.2025?igsh=NDNhbmw0ZGgxN3d0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3224,7 +3172,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3233,13 +3181,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>25</v>
+        <v>141</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R30" t="n">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3248,12 +3196,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1997616944</t>
+          <t>1516469775</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1997616944</t>
+          <t>https://m.place.naver.com/place/1516469775</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3270,25 +3218,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>수네일</t>
+          <t>더블유네일</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>yjh1000j@naver.com</t>
+          <t>ybbbbinn@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>02-335-4321</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세검정로1길 50 1층 수네일</t>
+          <t>서울특별시 서대문구 연희로4길 9 1충</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://instagram.com/soonail_kim</t>
+          <t>http://instagram.com/private_nailsalon_w</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3323,13 +3275,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3338,12 +3290,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1835439095</t>
+          <t>20322720</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835439095</t>
+          <t>https://m.place.naver.com/place/20322720</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3360,29 +3312,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>네일, 여유</t>
+          <t>네일샘</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>knl_95@naver.com</t>
+          <t>namyuri1004@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1433-1620</t>
+          <t>02-312-0744</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 간호대로2길 9 1층</t>
+          <t>서울특별시 서대문구 연세로 50</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail.healing_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3392,7 +3344,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3413,17 +3365,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3432,12 +3384,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1492064846</t>
+          <t>813067384</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1492064846</t>
+          <t>https://m.place.naver.com/place/813067384</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3454,29 +3406,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>풋케어 로미네일</t>
+          <t>하미네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>kangsogood@naver.com</t>
+          <t>p790512@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1301-6236</t>
+          <t>0507-1332-0103</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 139 2층 좌측호</t>
+          <t>서울특별시 서대문구 신촌로35길 3 2층 하미네일</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/footcare_romi_nail?igsh=cjVmanNvMWZ5OGRt</t>
+          <t>https://blog.naver.com/p790512</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3491,7 +3443,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3511,13 +3463,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="R33" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3526,12 +3478,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2080263501</t>
+          <t>1633156843</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2080263501</t>
+          <t>https://m.place.naver.com/place/1633156843</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3548,29 +3500,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>오늘도네일</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>j2lang@naver.com</t>
-        </is>
-      </c>
+          <t>행복한 네일</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>02-6364-4901</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 충정로 7</t>
+          <t>서울특별시 서대문구 연희로 204 상가동 1층 105호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail2day</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3580,7 +3524,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3601,17 +3545,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3620,12 +3564,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1277557209</t>
+          <t>2064316137</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1277557209</t>
+          <t>https://m.place.naver.com/place/2064316137</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3642,29 +3586,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>비포유</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>hansse_db@naver.com</t>
-        </is>
-      </c>
+          <t>제이앤제이네일</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1313-6448</t>
+          <t>0507-1342-8430</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 가재울미래로 2 203동 104-2호</t>
+          <t>서울특별시 서대문구 통일로 402 1층 제이엔제이네일</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_IrLMG</t>
+          <t>http://pf.kakao.com/_fMNYxj</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3699,13 +3639,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>264</v>
+        <v>78</v>
       </c>
       <c r="Q35" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="R35" t="n">
-        <v>280</v>
+        <v>127</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3714,12 +3654,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1150022642</t>
+          <t>1722436082</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1150022642</t>
+          <t>https://m.place.naver.com/place/1722436082</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3830,34 +3770,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>원더네일</t>
+          <t>루나네일</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>noweunn@naver.com</t>
+          <t>lunamika@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1360-1515</t>
+          <t>0507-1329-7109</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 독립문로12길 2</t>
+          <t>서울특별시 서대문구 가재울미래로 15 1층 103호 루나네일</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xczxmaj</t>
+          <t>http://instagram.com/lunarnail__</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3878,7 +3818,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3887,13 +3827,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="Q37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3902,12 +3842,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>37196672</t>
+          <t>1427499799</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37196672</t>
+          <t>https://m.place.naver.com/place/1427499799</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3924,12 +3864,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>아이원네일아트</t>
+          <t>네일, 온미</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>fpwlsk8877@naver.com</t>
+          <t>cjsdks518@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -3937,12 +3877,12 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로5길 38 1층</t>
+          <t>서울특별시 서대문구 세검정로 93 . 1층 네일샵</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_onme_/</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3952,7 +3892,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3973,17 +3913,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>148</v>
+        <v>10</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>152</v>
+        <v>13</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3992,12 +3932,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1544991635</t>
+          <t>1881659470</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1544991635</t>
+          <t>https://m.place.naver.com/place/1881659470</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4014,29 +3954,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>소우네일</t>
+          <t>디디뷰티</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>snflcjswo54@naver.com</t>
+          <t>ddb0301@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0507-1328-7467</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희맛로 7-17 1층 202호</t>
+          <t>서울특별시 서대문구 세무서8길 30 상가 B1(2층) 41호 디디뷰티</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sounail__</t>
+          <t>https://blog.naver.com/ddb0301</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4051,7 +3987,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4071,13 +4007,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>271</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>288</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4086,12 +4022,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2021939074</t>
+          <t>1056660215</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2021939074</t>
+          <t>https://m.place.naver.com/place/1056660215</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4108,39 +4044,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>안씨네일</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>an_c_nail@naver.com</t>
-        </is>
-      </c>
+          <t>메리네일</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1352-3893</t>
+          <t>02-303-1194</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로35길 66 1층 103호</t>
+          <t>서울특별시 서대문구 증가로 143</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_rxoxiqX</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4156,22 +4088,22 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>376</v>
+        <v>25</v>
       </c>
       <c r="Q40" t="n">
-        <v>247</v>
+        <v>2</v>
       </c>
       <c r="R40" t="n">
-        <v>623</v>
+        <v>27</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4180,12 +4112,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1657626219</t>
+          <t>13492671</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1657626219</t>
+          <t>https://m.place.naver.com/place/13492671</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4202,29 +4134,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일도Nail</t>
+          <t>The서이</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ksy3315@naver.com</t>
+          <t>premier-music@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1444-2889</t>
+          <t>0507-1410-5589</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 109 (신촌르메이에르타운)B109-1 네일도Nail</t>
+          <t>서울특별시 서대문구 수색로 100 DMC레미안e편한세상 103동상가 2호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sIQTg2Uc</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4234,7 +4166,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4250,22 +4182,22 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="Q41" t="n">
-        <v>121</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>176</v>
+        <v>9</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4274,12 +4206,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1887906221</t>
+          <t>33928722</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1887906221</t>
+          <t>https://m.place.naver.com/place/33928722</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4296,29 +4228,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>네일온</t>
+          <t>제이네일</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>dlgksmf3595@naver.com</t>
+          <t>morningapple6@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1412-0791</t>
+          <t>0507-1329-0346</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 불광천길 264 1층좌측</t>
+          <t>서울특별시 서대문구 독립문공원길 13 독립문극동아파트</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailon_0790</t>
+          <t>https://www.instagram.com/j_nail_2503</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4353,13 +4285,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>35</v>
+        <v>113</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="R42" t="n">
-        <v>37</v>
+        <v>122</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4368,12 +4300,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1376233513</t>
+          <t>321319088</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1376233513</t>
+          <t>https://m.place.naver.com/place/321319088</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4390,25 +4322,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>꾸밈</t>
+          <t>마레네일</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>hairccumim@naver.com</t>
+          <t>mm940226@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1359-9204</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 수색로2길 39 DMC금호리첸시아 상가 지하101호</t>
+          <t>서울특별시 서대문구 이화여대길 64 2층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/ggoomim</t>
+          <t>https://www.instagram.com/mare.nail/</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4443,13 +4379,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>289</v>
+        <v>1494</v>
       </c>
       <c r="Q43" t="n">
-        <v>113</v>
+        <v>453</v>
       </c>
       <c r="R43" t="n">
-        <v>402</v>
+        <v>1947</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4458,12 +4394,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1649834362</t>
+          <t>32465293</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1649834362</t>
+          <t>https://m.place.naver.com/place/32465293</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4480,30 +4416,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>스윕네일</t>
+          <t>안씨네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>tong2star@naver.com</t>
+          <t>an_c_nail@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1352-3893</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대5길 35 지하1층 104호</t>
+          <t>서울특별시 서대문구 통일로35길 66 1층 103호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sweepnail/</t>
+          <t>http://pf.kakao.com/_rxoxiqX</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4524,7 +4464,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4533,13 +4473,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>178</v>
+        <v>376</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>247</v>
       </c>
       <c r="R44" t="n">
-        <v>181</v>
+        <v>623</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4548,12 +4488,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1462276902</t>
+          <t>1657626219</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1462276902</t>
+          <t>https://m.place.naver.com/place/1657626219</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4570,29 +4510,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>네일바이엔 이대역본점</t>
+          <t>네일이끌림</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>makeup_byn@naver.com</t>
+          <t>nail_drag@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1316-9910</t>
+          <t>02-393-9948</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 169-7 이대 포레스트 1층 105호</t>
+          <t>서울특별시 서대문구 신촌로35길 10</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://instagram.com/arim_happy</t>
+          <t>https://www.instagram.com/cong__vely</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4627,13 +4567,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>665</v>
+        <v>49</v>
       </c>
       <c r="Q45" t="n">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="R45" t="n">
-        <v>695</v>
+        <v>131</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4642,12 +4582,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1282451640</t>
+          <t>1698891603</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1282451640</t>
+          <t>https://m.place.naver.com/place/1698891603</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4664,29 +4604,25 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>더 꼼네일</t>
+          <t>미뜨네일</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>kjuuu0716@naver.com</t>
+          <t>annykoh@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0507-1322-3992</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 명지대길 56 1층</t>
+          <t>서울특별시 서대문구 증가로10길 16-6 미뜨네일</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>http://instagram.com/the_kkom</t>
+          <t>https://www.instagram.com/meett_nail</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4721,13 +4657,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>81</v>
+        <v>198</v>
       </c>
       <c r="Q46" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>146</v>
+        <v>199</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4736,12 +4672,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1616221232</t>
+          <t>1274572984</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1616221232</t>
+          <t>https://m.place.naver.com/place/1274572984</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4758,34 +4694,30 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>보라다</t>
+          <t>더네일</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>kordipr@naver.com</t>
+          <t>thenail_@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>02-303-3188</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로25길 11 1층 보라다</t>
+          <t>서울특별시 서대문구 서소문로 43-22 한흥빌딩 2층 더 네일</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/iam.borada</t>
+          <t>https://pf.kakao.com/_mYaaxl</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4806,7 +4738,7 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4815,13 +4747,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="Q47" t="n">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="R47" t="n">
-        <v>183</v>
+        <v>102</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4830,12 +4762,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>34484907</t>
+          <t>1800993616</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34484907</t>
+          <t>https://m.place.naver.com/place/1800993616</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4852,29 +4784,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>솔하네일</t>
+          <t>토드네일</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>feltbeats90@naver.com</t>
+          <t>0728helen@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1329-2315</t>
+          <t>0507-1486-0620</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 응암로1길 15 1층</t>
+          <t>서울특별시 서대문구 이화여대5길 35 지하1층 114호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>http://instagram.com/solhanail</t>
+          <t>https://www.instagram.com/todnail_</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4900,7 +4832,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4909,13 +4841,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>177</v>
+        <v>438</v>
       </c>
       <c r="Q48" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="R48" t="n">
-        <v>216</v>
+        <v>468</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4924,12 +4856,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1476338581</t>
+          <t>1674577867</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1476338581</t>
+          <t>https://m.place.naver.com/place/1674577867</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4946,29 +4878,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>모뜨네일</t>
+          <t>위드네일</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>mott_nail@naver.com</t>
+          <t>hahaha_1226@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1385-6099</t>
+          <t>0507-1308-2035</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대1안길 25 2층 203호</t>
+          <t>서울특별시 서대문구 홍제천로 158 1층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mott.nail</t>
+          <t>https://www.instagram.com/with.nail_</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4994,7 +4926,7 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -5003,13 +4935,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1331</v>
+        <v>28</v>
       </c>
       <c r="Q49" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1373</v>
+        <v>28</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5018,12 +4950,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1774073621</t>
+          <t>2099359388</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1774073621</t>
+          <t>https://m.place.naver.com/place/2099359388</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5040,34 +4972,30 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>수아라네일 가좌라운지점</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>matata4@naver.com</t>
-        </is>
-      </c>
+          <t>아모이네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1304-0817</t>
+          <t>0507-1439-5957</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 수색로 56 6층 609호</t>
+          <t>서울특별시 서대문구 신촌로27길 43 1층 102호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/sooara0817</t>
+          <t>http://pf.kakao.com/_dxaVan/chat</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5088,7 +5016,7 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5097,13 +5025,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1640</v>
+        <v>21</v>
       </c>
       <c r="Q50" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>1648</v>
+        <v>22</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5112,12 +5040,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1386960813</t>
+          <t>2066634292</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1386960813</t>
+          <t>https://m.place.naver.com/place/2066634292</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5134,29 +5062,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>소소람</t>
+          <t>굥뷰티</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>theokh@naver.com</t>
+          <t>sunday020@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1312-4806</t>
+          <t>0505-685-7683</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로28길 18 1층</t>
+          <t>서울특별시 서대문구 신촌역로 10</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_sosoram</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5166,7 +5094,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5187,17 +5115,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5206,12 +5134,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2044971493</t>
+          <t>1137345145</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2044971493</t>
+          <t>https://m.place.naver.com/place/1137345145</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5228,25 +5156,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>네일띵크</t>
+          <t>로지네일</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>goqlsl7895@naver.com</t>
+          <t>wonderfuuul@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1387-0314</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로11가길 36 신관 1층</t>
+          <t>서울특별시 서대문구 연세로7안길 1 3층 로지네일</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/snfSrVOh</t>
+          <t>http://www.instagram.com/rosy___nail</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5272,7 +5204,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5281,13 +5213,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>69</v>
+        <v>291</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="R52" t="n">
-        <v>70</v>
+        <v>319</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5296,12 +5228,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1472586988</t>
+          <t>1244771586</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1472586988</t>
+          <t>https://m.place.naver.com/place/1244771586</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5318,30 +5250,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>오늘네일</t>
+          <t>아임모어 신촌점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>barbie0903@naver.com</t>
+          <t>iam_more@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1451-3414</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대5길 9 2층</t>
+          <t>서울특별시 서대문구 명물길 6 9층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ilovetan_oneulnail</t>
+          <t>https://pf.kakao.com/_tauxad</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5362,7 +5298,7 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5371,13 +5307,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>10</v>
+        <v>1455</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>892</v>
       </c>
       <c r="R53" t="n">
-        <v>10</v>
+        <v>2347</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5386,12 +5322,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1348096581</t>
+          <t>387024661</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1348096581</t>
+          <t>https://m.place.naver.com/place/387024661</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5408,29 +5344,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>네일포시즌 풋풋한리쌤 신촌점</t>
+          <t>미호네일</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>nail4season@naver.com</t>
+          <t>kikijj0206@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>02-332-3239</t>
+          <t>02-303-4117</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로5나길 16 2층</t>
+          <t>서울특별시 서대문구 가재울미래로 2 205동상가 104-2 미호네일</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail4season/ww.instagram.com/</t>
+          <t>http://www.instagram.com/nail_in_miho</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5456,7 +5392,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5465,13 +5401,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>3938</v>
+        <v>10</v>
       </c>
       <c r="Q54" t="n">
-        <v>308</v>
+        <v>2</v>
       </c>
       <c r="R54" t="n">
-        <v>4246</v>
+        <v>12</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5480,12 +5416,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1902803079</t>
+          <t>1494438581</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1902803079</t>
+          <t>https://m.place.naver.com/place/1494438581</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5502,29 +5438,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>옌그리다</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>tmfddd@naver.com</t>
-        </is>
-      </c>
+          <t>네일마이데이</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1358-6121</t>
+          <t>0507-1325-2840</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 홍제내길 118 1층</t>
+          <t>서울특별시 서대문구 연희로15길 90 1층 차고 옆 출입문</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCoLUjj2k9oeAU5y7IS50qOQ</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5534,7 +5466,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5555,17 +5487,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>228</v>
+        <v>29</v>
       </c>
       <c r="Q55" t="n">
-        <v>212</v>
+        <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>440</v>
+        <v>30</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5574,12 +5506,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1611348671</t>
+          <t>2027784358</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611348671</t>
+          <t>https://m.place.naver.com/place/2027784358</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5596,29 +5528,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>로지네일</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>wonderfuuul@naver.com</t>
-        </is>
-      </c>
+          <t>포쉬네일 하이푸스 신촌점</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1387-0314</t>
+          <t>0507-1335-4241</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로7안길 1 3층 로지네일</t>
+          <t>서울특별시 서대문구 신촌로 73 2층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/rosy___nail</t>
+          <t>https://www.instagram.com/sh_forsynail</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5653,13 +5581,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>291</v>
+        <v>3133</v>
       </c>
       <c r="Q56" t="n">
-        <v>28</v>
+        <v>338</v>
       </c>
       <c r="R56" t="n">
-        <v>319</v>
+        <v>3471</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5668,12 +5596,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1244771586</t>
+          <t>1944620503</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1244771586</t>
+          <t>https://m.place.naver.com/place/1944620503</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5690,34 +5618,34 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>네일어라모드 홍대점</t>
+          <t>오드리네일</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>icanbemyself@naver.com</t>
+          <t>ardusy@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>070-8844-3030</t>
+          <t>0507-1407-8532</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로3가길 3-4 3층 301호</t>
+          <t>서울특별시 서대문구 거북골로 84 상가2동 108호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xfYVQj/chat</t>
+          <t>https://www.instagram.com/audreynail__</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5738,7 +5666,7 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5747,13 +5675,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>572</v>
+        <v>77</v>
       </c>
       <c r="Q57" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="R57" t="n">
-        <v>612</v>
+        <v>79</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5762,12 +5690,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1086898312</t>
+          <t>1472183656</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1086898312</t>
+          <t>https://m.place.naver.com/place/1472183656</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5784,39 +5712,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>보석</t>
+          <t>원더네일</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>marble1120@naver.com</t>
+          <t>noweunn@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>02-322-1915</t>
+          <t>0507-1360-1515</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로15안길 6</t>
+          <t>서울특별시 서대문구 독립문로12길 2</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xczxmaj</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5832,22 +5760,22 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="Q58" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R58" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5856,12 +5784,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>992322635</t>
+          <t>37196672</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/992322635</t>
+          <t>https://m.place.naver.com/place/37196672</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5878,34 +5806,30 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>리본 네일</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>feelringhair@naver.com</t>
-        </is>
-      </c>
+          <t>네일 아이보리</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1445-1169</t>
+          <t>0507-1463-7021</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대길 33 2층 리본네일</t>
+          <t>서울특별시 서대문구 이화여대5길 35 신촌영타운지웰에스테이트 상가동 2층 네일, 아이보리</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/feelringhair</t>
+          <t>https://booking.naver.com/booking/13/bizes/770181/items/4634924</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5915,7 +5839,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5935,13 +5859,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>644</v>
+        <v>240</v>
       </c>
       <c r="Q59" t="n">
-        <v>439</v>
+        <v>36</v>
       </c>
       <c r="R59" t="n">
-        <v>1083</v>
+        <v>276</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5950,12 +5874,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1561804134</t>
+          <t>1572186883</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1561804134</t>
+          <t>https://m.place.naver.com/place/1572186883</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -5972,25 +5896,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>네일뷰</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>darkyoon85@naver.com</t>
-        </is>
-      </c>
+          <t>수네일</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1332-4612</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로32안길 82 1층 101호</t>
+          <t>서울특별시 서대문구 증가로10길 16-20 1층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailview__</t>
+          <t>https://www.instagram.com/lovely.sunail</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6025,13 +5949,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>40</v>
+        <v>334</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R60" t="n">
-        <v>40</v>
+        <v>341</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6040,12 +5964,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>2068137219</t>
+          <t>1027173445</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2068137219</t>
+          <t>https://m.place.naver.com/place/1027173445</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6062,30 +5986,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>아르젠떼네일</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>dmswnrjsl213@naver.com</t>
-        </is>
-      </c>
+          <t>달달한네일</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1433-3262</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대8길 123 상가동 105호</t>
+          <t>서울특별시 서대문구 세무서2길 16 1층 2호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_kqfCG</t>
+          <t>https://www.instagram.com/thedaldalnail</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6106,22 +6030,22 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>21</v>
+        <v>233</v>
       </c>
       <c r="Q61" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="R61" t="n">
-        <v>22</v>
+        <v>323</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6130,12 +6054,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1142718935</t>
+          <t>1257856428</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1142718935</t>
+          <t>https://m.place.naver.com/place/1257856428</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6152,34 +6076,26 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>네일뭐해</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>mementomori-24@naver.com</t>
-        </is>
-      </c>
+          <t>아르젠떼네일</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>0507-1340-8272</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 가좌로 111 상가1층</t>
+          <t>서울특별시 서대문구 이화여대8길 123 상가동 105호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_mohe/</t>
+          <t>https://pf.kakao.com/_kqfCG</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6200,22 +6116,22 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>702</v>
+        <v>21</v>
       </c>
       <c r="Q62" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="R62" t="n">
-        <v>752</v>
+        <v>22</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6224,12 +6140,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>533976950</t>
+          <t>1142718935</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/533976950</t>
+          <t>https://m.place.naver.com/place/1142718935</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6246,34 +6162,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>네일 블라썸</t>
+          <t>옌그리다</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>wilklove@naver.com</t>
+          <t>l-jungeun@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1324-7644</t>
+          <t>0507-1358-6121</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세검정로1길 39 풍림2차아파트 상가동 241호</t>
+          <t>서울특별시 서대문구 홍제내길 118 1층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://naver.me/FRL0RGyl</t>
+          <t>https://youtube.com/channel/UCoLUjj2k9oeAU5y7IS50qOQ</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6299,17 +6215,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>74</v>
+        <v>227</v>
       </c>
       <c r="Q63" t="n">
-        <v>37</v>
+        <v>212</v>
       </c>
       <c r="R63" t="n">
-        <v>111</v>
+        <v>439</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6318,12 +6234,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1423228794</t>
+          <t>1611348671</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1423228794</t>
+          <t>https://m.place.naver.com/place/1611348671</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6340,29 +6256,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>포쉬네일 하이푸스 신촌점</t>
+          <t>네일써니데이</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>freegirl11@naver.com</t>
+          <t>songhs1226@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1335-4241</t>
+          <t>0507-1403-0327</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 73 2층</t>
+          <t>서울특별시 서대문구 증가로10길 48-6 101호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sh_forsynail</t>
+          <t>https://www.instagram.com/nail_s.day</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6397,13 +6313,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>3133</v>
+        <v>220</v>
       </c>
       <c r="Q64" t="n">
-        <v>338</v>
+        <v>8</v>
       </c>
       <c r="R64" t="n">
-        <v>3471</v>
+        <v>228</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6412,12 +6328,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1944620503</t>
+          <t>1324725520</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1944620503</t>
+          <t>https://m.place.naver.com/place/1324725520</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6434,29 +6350,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BK민방경네일</t>
+          <t>온더네일스</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>acquidigio7@naver.com</t>
+          <t>k14150@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>02-393-7449</t>
+          <t>0507-1330-5812</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대길 82 2층</t>
+          <t>서울특별시 서대문구 통일로 400 2F</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/acquidigio7</t>
+          <t>https://www.instagram.com/_onthenails</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6471,7 +6387,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6491,13 +6407,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>552</v>
+        <v>142</v>
       </c>
       <c r="Q65" t="n">
-        <v>1153</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1705</v>
+        <v>142</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6506,12 +6422,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>38314950</t>
+          <t>1484695115</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38314950</t>
+          <t>https://m.place.naver.com/place/1484695115</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6528,29 +6444,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>네일살롱무아</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>min_0_97@naver.com</t>
-        </is>
-      </c>
+          <t>숨네일</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>0507-1436-1705</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 109 신촌르메이에르타운 5차 1층 110-1-2</t>
+          <t>서울특별시 서대문구 홍은중앙로 100-2 1층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailmuah_</t>
+          <t>https://www.instagram.com/sumnail9901</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6585,13 +6493,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="Q66" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="R66" t="n">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6600,12 +6508,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1027772524</t>
+          <t>1326174975</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027772524</t>
+          <t>https://m.place.naver.com/place/1326174975</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6622,29 +6530,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일살롱</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>wing3527@naver.com</t>
-        </is>
-      </c>
+          <t>네일뭐해</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1303-0241</t>
+          <t>0507-1340-8272</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희맛로 20 연희빌딩 1층 1호네일실롱</t>
+          <t>서울특별시 서대문구 가좌로 111 상가1층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>http://instagram.com/nailsalon7775</t>
+          <t>https://www.instagram.com/nail_mohe/</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6679,13 +6583,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>38</v>
+        <v>702</v>
       </c>
       <c r="Q67" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="R67" t="n">
-        <v>83</v>
+        <v>752</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6694,12 +6598,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1527535605</t>
+          <t>533976950</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1527535605</t>
+          <t>https://m.place.naver.com/place/533976950</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6716,34 +6620,30 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>네일소브 북가좌본점</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>hbs2002i@naver.com</t>
-        </is>
-      </c>
+          <t>네일 블라썸</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1448-3319</t>
+          <t>0507-1324-7644</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 거북골로 184 1층 좌측중앙(네일샵)</t>
+          <t>서울특별시 서대문구 세검정로1길 39 풍림2차아파트 상가동 241호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_sove</t>
+          <t>https://naver.me/FRL0RGyl</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6769,17 +6669,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="Q68" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="R68" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6788,12 +6688,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1192995175</t>
+          <t>1423228794</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1192995175</t>
+          <t>https://m.place.naver.com/place/1423228794</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6810,34 +6710,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>아임모어 신촌점</t>
+          <t>빔빔네일</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>iam_more@naver.com</t>
+          <t>yznnim@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1451-3414</t>
+          <t>0507-1406-5642</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 명물길 6 9층</t>
+          <t>서울특별시 서대문구 세무서길 77 1층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_tauxad</t>
+          <t>http://www.instagram.com/beam2nail</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6858,7 +6758,7 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6867,13 +6767,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1454</v>
+        <v>20</v>
       </c>
       <c r="Q69" t="n">
-        <v>892</v>
+        <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>2346</v>
+        <v>21</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6882,12 +6782,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>387024661</t>
+          <t>84828356</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/387024661</t>
+          <t>https://m.place.naver.com/place/84828356</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6904,29 +6804,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>제이네일</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>morningapple6@naver.com</t>
-        </is>
-      </c>
+          <t>쏭뷰티샵</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1329-0346</t>
+          <t>070-8248-9565</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 독립문공원길 13 독립문극동아파트</t>
+          <t>서울특별시 서대문구 세검정로1길 48 1층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/j_nail_2503</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6936,7 +6832,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6957,17 +6853,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6976,12 +6872,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>321319088</t>
+          <t>32284905</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/321319088</t>
+          <t>https://m.place.naver.com/place/32284905</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -6998,29 +6894,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>네일이끌림</t>
+          <t>네일뷰</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>nail_drag@naver.com</t>
+          <t>darkyoon85@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>02-393-9948</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로35길 10</t>
+          <t>서울특별시 서대문구 증가로32안길 82 1층 101호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cong__vely</t>
+          <t>https://www.instagram.com/nailview__</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7055,13 +6947,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="Q71" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>131</v>
+        <v>40</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7070,12 +6962,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1698891603</t>
+          <t>2068137219</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1698891603</t>
+          <t>https://m.place.naver.com/place/2068137219</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7092,29 +6984,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>더블유네일</t>
+          <t>모뜨네일</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ybbbbinn@naver.com</t>
+          <t>mott_nail@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>02-335-4321</t>
+          <t>0507-1385-6099</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로4길 9 1충</t>
+          <t>서울특별시 서대문구 이화여대1안길 25 2층 203호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>http://instagram.com/private_nailsalon_w</t>
+          <t>https://www.instagram.com/mott.nail</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7149,13 +7041,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3</v>
+        <v>1331</v>
       </c>
       <c r="Q72" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="R72" t="n">
-        <v>5</v>
+        <v>1373</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7164,12 +7056,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>20322720</t>
+          <t>1774073621</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20322720</t>
+          <t>https://m.place.naver.com/place/1774073621</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7186,29 +7078,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>디에고푸스 연희점 네일바이은</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>kwonbinus@naver.com</t>
-        </is>
-      </c>
+          <t>유네일</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1412-1747</t>
+          <t>0507-1412-2114</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희맛로 17-49</t>
+          <t>서울특별시 서대문구 증가로24마길 47 1층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nailbyeun</t>
+          <t>https://www.instagram.com/_u_nail_</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7243,13 +7131,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>99</v>
+        <v>231</v>
       </c>
       <c r="Q73" t="n">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="R73" t="n">
-        <v>208</v>
+        <v>267</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7258,12 +7146,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>37452801</t>
+          <t>1610895712</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37452801</t>
+          <t>https://m.place.naver.com/place/1610895712</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7280,25 +7168,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>숨네일</t>
+          <t>리본 네일</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>traineran@naver.com</t>
+          <t>feelringhair@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1445-1169</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 홍은중앙로 100-2 1층</t>
+          <t>서울특별시 서대문구 이화여대길 33 2층 리본네일</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sumnail9901</t>
+          <t>https://blog.naver.com/feelringhair</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7313,7 +7205,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7333,13 +7225,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>26</v>
+        <v>644</v>
       </c>
       <c r="Q74" t="n">
-        <v>1</v>
+        <v>439</v>
       </c>
       <c r="R74" t="n">
-        <v>27</v>
+        <v>1083</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7348,12 +7240,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1326174975</t>
+          <t>1561804134</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1326174975</t>
+          <t>https://m.place.naver.com/place/1561804134</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7370,29 +7262,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>네일미야오</t>
+          <t>솔하네일</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>traveler_01@naver.com</t>
+          <t>feltbeats90@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1471-2420</t>
+          <t>0507-1329-2315</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌역로 17 203호</t>
+          <t>서울특별시 서대문구 응암로1길 15 1층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailmeow.2025?igsh=NDNhbmw0ZGgxN3d0</t>
+          <t>http://instagram.com/solhanail</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7427,13 +7319,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="Q75" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="R75" t="n">
-        <v>149</v>
+        <v>216</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7442,12 +7334,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1516469775</t>
+          <t>1476338581</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1516469775</t>
+          <t>https://m.place.naver.com/place/1476338581</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7464,34 +7356,34 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>네일에피소드</t>
+          <t>시즈닝네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>daonnail0305@naver.com</t>
+          <t>blue991013@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1370-4811</t>
+          <t>0507-1362-1065</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세무서길 55 1층</t>
+          <t>서울특별시 서대문구 통일로40길 28</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhbrZn</t>
+          <t>https://blog.naver.com/blue991013</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7501,7 +7393,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7512,7 +7404,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7521,13 +7413,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="R76" t="n">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7536,12 +7428,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1897148944</t>
+          <t>1888898614</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1897148944</t>
+          <t>https://m.place.naver.com/place/1888898614</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7558,29 +7450,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>오드리네일</t>
+          <t>BK맨즈네일</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ardusy@naver.com</t>
+          <t>bkmensnail@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1407-8532</t>
+          <t>02-365-7449</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 거북골로 84 상가2동 108호</t>
+          <t>서울특별시 서대문구 이화여대길 82 3층</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/audreynail__</t>
+          <t>https://blog.naver.com/bkmensnail</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7595,7 +7487,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7615,13 +7507,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="Q77" t="n">
-        <v>2</v>
+        <v>310</v>
       </c>
       <c r="R77" t="n">
-        <v>79</v>
+        <v>337</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7630,12 +7522,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1472183656</t>
+          <t>1573880950</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1472183656</t>
+          <t>https://m.place.naver.com/place/1573880950</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7652,29 +7544,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>뮤즈네일</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>jiji012636@naver.com</t>
-        </is>
-      </c>
+          <t>코이네일</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0507-1300-4636</t>
+          <t>0507-1494-6711</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 인왕시장길 18</t>
+          <t>서울특별시 서대문구 세검정로 46 1층 9호</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jiji012636</t>
+          <t>https://www.instagram.com/k.o.i.nail/</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7689,7 +7577,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -7709,13 +7597,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>3</v>
+        <v>163</v>
       </c>
       <c r="Q78" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="R78" t="n">
-        <v>17</v>
+        <v>182</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7724,12 +7612,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1179732435</t>
+          <t>1956411597</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1179732435</t>
+          <t>https://m.place.naver.com/place/1956411597</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7746,29 +7634,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>릴리네일</t>
+          <t>네일온</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>jain_im_@naver.com</t>
+          <t>dlgksmf3595@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0507-1350-0862</t>
+          <t>0507-1412-0791</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로39가길 27</t>
+          <t>서울특별시 서대문구 불광천길 264 1층좌측</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lily.s_nail_studio</t>
+          <t>https://www.instagram.com/nailon_0790</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7803,13 +7691,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>199</v>
+        <v>35</v>
       </c>
       <c r="Q79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R79" t="n">
-        <v>202</v>
+        <v>37</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7818,12 +7706,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1863831189</t>
+          <t>1376233513</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1863831189</t>
+          <t>https://m.place.naver.com/place/1376233513</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7840,29 +7728,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>빔빔네일</t>
+          <t>수아라네일 가좌라운지점</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>yznnim@naver.com</t>
+          <t>matata4@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1406-5642</t>
+          <t>0507-1304-0817</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세무서길 77 1층</t>
+          <t>서울특별시 서대문구 수색로 56 6층 609호</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/beam2nail</t>
+          <t>https://smartstore.naver.com/sooara0817</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7897,13 +7785,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>20</v>
+        <v>1640</v>
       </c>
       <c r="Q80" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R80" t="n">
-        <v>21</v>
+        <v>1648</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7912,12 +7800,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>84828356</t>
+          <t>1386960813</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/84828356</t>
+          <t>https://m.place.naver.com/place/1386960813</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -7934,29 +7822,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>달달한네일</t>
+          <t>네일포시즌 풋풋한리쌤 신촌점</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>nail0danji@naver.com</t>
+          <t>nail4season@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1433-3262</t>
+          <t>02-332-3239</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세무서2길 16 1층 2호</t>
+          <t>서울특별시 서대문구 연세로5나길 16 2층</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/thedaldalnail</t>
+          <t>https://www.instagram.com/nail4season/ww.instagram.com/</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7991,13 +7879,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>233</v>
+        <v>3939</v>
       </c>
       <c r="Q81" t="n">
-        <v>90</v>
+        <v>308</v>
       </c>
       <c r="R81" t="n">
-        <v>323</v>
+        <v>4247</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8006,12 +7894,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1257856428</t>
+          <t>1902803079</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1257856428</t>
+          <t>https://m.place.naver.com/place/1902803079</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8028,29 +7916,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BK맨즈네일</t>
+          <t>살롱드선네일</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>bkmensnail@naver.com</t>
+          <t>jam_d@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>02-365-7449</t>
+          <t>0507-1338-2605</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대길 82 3층</t>
+          <t>서울특별시 서대문구 북아현로1가길 20 이편한세상신촌 1단지상가 110호</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bkmensnail</t>
+          <t>http://instagram.com/salonde_seon</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8065,7 +7953,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8085,13 +7973,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>27</v>
+        <v>426</v>
       </c>
       <c r="Q82" t="n">
-        <v>310</v>
+        <v>12</v>
       </c>
       <c r="R82" t="n">
-        <v>337</v>
+        <v>438</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8100,12 +7988,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1573880950</t>
+          <t>1688455455</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1573880950</t>
+          <t>https://m.place.naver.com/place/1688455455</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -8122,25 +8010,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>네일도행운</t>
+          <t>윈디네일 내성발톱 무좀 발각질 문제성발</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>stellacafe@naver.com</t>
+          <t>winner-d@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1367-5855</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 모래내로 245 2층 더미뷰티 내부</t>
+          <t>서울특별시 서대문구 응암로 43 두정빌딩 1층</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luck__with_nail?igsh=aWltam43aTkwdDJu&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/win_d_nail</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8166,7 +8058,7 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8175,13 +8067,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>131</v>
+        <v>461</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="R83" t="n">
-        <v>131</v>
+        <v>522</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8190,12 +8082,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>2049561266</t>
+          <t>1287346768</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2049561266</t>
+          <t>https://m.place.naver.com/place/1287346768</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8212,29 +8104,25 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>오네일드잇 신촌점</t>
+          <t>꾸밈</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>travelsudal@naver.com</t>
+          <t>hairccumim@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>0507-1379-5740</t>
-        </is>
-      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 123 2층</t>
+          <t>서울특별시 서대문구 수색로2길 39 DMC금호리첸시아 상가 지하101호</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oh_nailed_it</t>
+          <t>http://www.instagram.com/ggoomim</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8269,13 +8157,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>603</v>
+        <v>289</v>
       </c>
       <c r="Q84" t="n">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="R84" t="n">
-        <v>612</v>
+        <v>402</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8284,12 +8172,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1930241791</t>
+          <t>1649834362</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1930241791</t>
+          <t>https://m.place.naver.com/place/1649834362</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -8306,25 +8194,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>미뜨네일</t>
+          <t>네일넘버8</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>annykoh@naver.com</t>
+          <t>bcysfinder@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>02-365-8008</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로10길 16-6 미뜨네일</t>
+          <t>서울특별시 서대문구 신촌역로 7</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/meett_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8334,7 +8226,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -8355,17 +8247,17 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>198</v>
+        <v>5</v>
       </c>
       <c r="Q85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>199</v>
+        <v>5</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8374,12 +8266,12 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1274572984</t>
+          <t>35751127</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1274572984</t>
+          <t>https://m.place.naver.com/place/35751127</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -8396,29 +8288,25 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>알지네일</t>
+          <t>한예진뷰티디자인</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>handsos@naver.com</t>
+          <t>bijou-artist@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>0507-1352-1908</t>
-        </is>
-      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로31길 9</t>
+          <t>서울특별시 서대문구 신촌로 189</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>http://instagram.com/r.g_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8428,7 +8316,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -8449,17 +8337,17 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8468,12 +8356,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>32528538</t>
+          <t>1388645750</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32528538</t>
+          <t>https://m.place.naver.com/place/1388645750</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -8490,25 +8378,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>메이퀸네일살롱</t>
+          <t>네일바이엔 이대역본점</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ogsohd@naver.com</t>
+          <t>makeup_byn@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0507-1316-9910</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 169-7 이대포레스트 1층</t>
+          <t>서울특별시 서대문구 신촌로 169-7 이대 포레스트 1층 105호</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/arim_happy</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8518,7 +8410,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -8539,17 +8431,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>13</v>
+        <v>666</v>
       </c>
       <c r="Q87" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="R87" t="n">
-        <v>15</v>
+        <v>696</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8558,12 +8450,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>82617755</t>
+          <t>1282451640</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/82617755</t>
+          <t>https://m.place.naver.com/place/1282451640</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -8580,29 +8472,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>에스뷰티</t>
+          <t>네일올리브 신촌 연대캠퍼스점</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ssooke114@naver.com</t>
+          <t>megu03@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0507-1478-9939</t>
+          <t>02-2123-8273</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로4길 58-11 1층</t>
+          <t>서울특별시 서대문구 연세로 50 연세대학교 내 국제학사 지하 2층</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/936347</t>
+          <t>http://www.nailolive.com/</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8612,7 +8504,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -8637,13 +8529,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8652,12 +8544,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1456809966</t>
+          <t>13332586</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1456809966</t>
+          <t>https://m.place.naver.com/place/13332586</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -8674,25 +8566,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>연희동네일</t>
+          <t>네일소브 북가좌본점</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>love1nlove@naver.com</t>
+          <t>hbs2002i@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1448-3319</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로11길 22</t>
+          <t>서울특별시 서대문구 거북골로 184 1층 좌측중앙(네일샵)</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_sove</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8702,7 +8598,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -8723,17 +8619,17 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R89" t="n">
-        <v>9</v>
+        <v>108</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8742,12 +8638,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1631395937</t>
+          <t>1192995175</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1631395937</t>
+          <t>https://m.place.naver.com/place/1192995175</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8764,29 +8660,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>네일마이데이</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>ohmyhotelnco@naver.com</t>
-        </is>
-      </c>
+          <t>히카리 살롱 네일&amp;아이래쉬</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0507-1325-2840</t>
+          <t>0507-1369-1853</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로15길 90 1층 차고 옆 출입문</t>
+          <t>서울특별시 서대문구 신촌로 109 지하1층 비112 히카리살롱</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/sY3GnTpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8796,7 +8688,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -8812,22 +8704,22 @@
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>28</v>
+        <v>434</v>
       </c>
       <c r="Q90" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="R90" t="n">
-        <v>29</v>
+        <v>461</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8836,12 +8728,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>2027784358</t>
+          <t>1696710543</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2027784358</t>
+          <t>https://m.place.naver.com/place/1696710543</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -8858,34 +8750,34 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>윈디네일 내성발톱 무좀 발각질 문제성발</t>
+          <t>네일어라모드 홍대점</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>winner-d@naver.com</t>
+          <t>icanbemyself@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0507-1367-5855</t>
+          <t>070-8844-3030</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 응암로 43 두정빌딩 1층</t>
+          <t>서울특별시 서대문구 신촌로3가길 3-4 3층 301호</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/win_d_nail</t>
+          <t>http://pf.kakao.com/_xfYVQj/chat</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -8906,7 +8798,7 @@
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -8915,13 +8807,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>461</v>
+        <v>572</v>
       </c>
       <c r="Q91" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="R91" t="n">
-        <v>522</v>
+        <v>612</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8930,12 +8822,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1287346768</t>
+          <t>1086898312</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1287346768</t>
+          <t>https://m.place.naver.com/place/1086898312</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -8952,29 +8844,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>히카리 살롱 네일&amp;아이래쉬</t>
+          <t>오늘도네일</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>yeooonyummy@naver.com</t>
+          <t>j2lang@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0507-1369-1853</t>
+          <t>02-6364-4901</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 109 지하1층 비112 히카리살롱</t>
+          <t>서울특별시 서대문구 충정로 7</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sY3GnTpg</t>
+          <t>http://www.instagram.com/nail2day</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9000,7 +8892,7 @@
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -9009,13 +8901,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>433</v>
+        <v>20</v>
       </c>
       <c r="Q92" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>460</v>
+        <v>20</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9024,12 +8916,12 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1696710543</t>
+          <t>1277557209</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1696710543</t>
+          <t>https://m.place.naver.com/place/1277557209</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -9046,29 +8938,25 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>네일까사</t>
+          <t>수네일</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ptypoohpooh0820@naver.com</t>
+          <t>yjh1000j@naver.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>0507-1404-1654</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로4길 28 2F</t>
+          <t>서울특별시 서대문구 세검정로1길 50 1층 수네일</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nailcasa</t>
+          <t>http://instagram.com/soonail_kim</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9103,13 +8991,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>255</v>
+        <v>1</v>
       </c>
       <c r="Q93" t="n">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="R93" t="n">
-        <v>304</v>
+        <v>17</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9118,12 +9006,12 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>38015918</t>
+          <t>1835439095</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38015918</t>
+          <t>https://m.place.naver.com/place/1835439095</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -9140,25 +9028,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>디디뷰티</t>
+          <t>영네일</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ddb0301@naver.com</t>
+          <t>youngnail423@naver.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0507-1368-4230</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세무서8길 30 상가 B1(2층) 41호 디디뷰티</t>
+          <t>서울특별시 서대문구 신촌로 109 르메이에르타운5 B103-3</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ddb0301</t>
+          <t>https://blog.naver.com/youngnail423</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9193,13 +9085,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>271</v>
+        <v>59</v>
       </c>
       <c r="Q94" t="n">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="R94" t="n">
-        <v>288</v>
+        <v>126</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9208,12 +9100,12 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>1056660215</t>
+          <t>36505109</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1056660215</t>
+          <t>https://m.place.naver.com/place/36505109</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -9230,25 +9122,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>마요네일</t>
+          <t>위드앤네일</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ynh3377@naver.com</t>
+          <t>jelly0355@naver.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0507-1322-3690</t>
+        </is>
+      </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로11가길 33-3 1층</t>
+          <t>서울특별시 서대문구 통일로 510 상가212호 위드앤네일</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mayonail_official</t>
+          <t>http://www.instagram.com/_with_n_nail_</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9283,13 +9179,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="Q95" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9298,12 +9194,12 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>1434998291</t>
+          <t>1070279609</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1434998291</t>
+          <t>https://m.place.naver.com/place/1070279609</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -9320,29 +9216,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>꽃물 네일 &amp; 속눈썹 &amp; 왁싱</t>
+          <t>보석</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ddalgy00@naver.com</t>
+          <t>marble1120@naver.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>02-394-4141</t>
+          <t>02-322-1915</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 420 2층</t>
+          <t>서울특별시 서대문구 연희로15안길 6</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kina8843/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9352,7 +9248,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -9373,17 +9269,17 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q96" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="R96" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9392,12 +9288,12 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>882778770</t>
+          <t>992322635</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/882778770</t>
+          <t>https://m.place.naver.com/place/992322635</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
@@ -9414,34 +9310,26 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>지젤네일</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>shinesparis@naver.com</t>
-        </is>
-      </c>
+          <t>네일띵크</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>0507-1339-4329</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌역로 16 1층 104-1호 지젤네일</t>
+          <t>서울특별시 서대문구 연희로11가길 36 신관 1층</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://booking.kakao.com/short/lBeB2nWTzo</t>
+          <t>https://open.kakao.com/o/snfSrVOh</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -9462,7 +9350,7 @@
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -9471,13 +9359,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="Q97" t="n">
         <v>1</v>
       </c>
       <c r="R97" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9486,12 +9374,12 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>1215364308</t>
+          <t>1472586988</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1215364308</t>
+          <t>https://m.place.naver.com/place/1472586988</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -9508,29 +9396,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>쏭뷰티샵</t>
+          <t>릴리네일</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>aryangjiu@naver.com</t>
+          <t>jain_im_@naver.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>070-8248-9565</t>
+          <t>0507-1350-0862</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세검정로1길 48 1층</t>
+          <t>서울특별시 서대문구 통일로39가길 27</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lily.s_nail_studio</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -9540,7 +9428,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -9561,17 +9449,17 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9580,12 +9468,12 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>32284905</t>
+          <t>1863831189</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32284905</t>
+          <t>https://m.place.naver.com/place/1863831189</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -9602,39 +9490,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>메리네일</t>
+          <t>비포유</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>qaqzqsaw2@naver.com</t>
+          <t>hansse_db@naver.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>02-303-1194</t>
+          <t>0507-1313-6448</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로 143</t>
+          <t>서울특별시 서대문구 가재울미래로 2 203동 104-2호</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_IrLMG</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -9650,22 +9538,22 @@
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P99" t="n">
-        <v>25</v>
+        <v>264</v>
       </c>
       <c r="Q99" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="R99" t="n">
-        <v>27</v>
+        <v>280</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9674,12 +9562,12 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>13492671</t>
+          <t>1150022642</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13492671</t>
+          <t>https://m.place.naver.com/place/1150022642</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -9696,29 +9584,25 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>로렐네일</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>mchavzezy@naver.com</t>
-        </is>
-      </c>
+          <t>네일 소아나</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0507-1436-9020</t>
+          <t>0507-1363-1483</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대3길 45 리브하임 B1층 로렐</t>
+          <t>서울특별시 서대문구 이화여대5길 35 지하1층 104호</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xcXaxgn/friend</t>
+          <t>http://pf.kakao.com/_VExgxmn</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -9753,13 +9637,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>233</v>
+        <v>101</v>
       </c>
       <c r="Q100" t="n">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="R100" t="n">
-        <v>319</v>
+        <v>114</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -9768,12 +9652,12 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>1883098019</t>
+          <t>2057189903</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1883098019</t>
+          <t>https://m.place.naver.com/place/2057189903</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
@@ -9790,34 +9674,34 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>네일써니데이</t>
+          <t>네일에피소드</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>songhs1226@naver.com</t>
+          <t>daonnail0305@naver.com</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0507-1403-0327</t>
+          <t>0507-1370-4811</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로10길 48-6 101호</t>
+          <t>서울특별시 서대문구 세무서길 55 1층</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_s.day</t>
+          <t>http://pf.kakao.com/_xhbrZn</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -9838,7 +9722,7 @@
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -9847,13 +9731,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>220</v>
+        <v>78</v>
       </c>
       <c r="Q101" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -9862,12 +9746,12 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>1324725520</t>
+          <t>1897148944</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324725520</t>
+          <t>https://m.place.naver.com/place/1897148944</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
@@ -9884,12 +9768,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>썸네일</t>
+          <t>네일도행운</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>hackerstalk11@naver.com</t>
+          <t>bongbong323@naver.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -9897,12 +9781,12 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대길 58</t>
+          <t>서울특별시 서대문구 모래내로 245 2층 더미뷰티 내부</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/luck__with_nail?igsh=aWltam43aTkwdDJu&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9912,7 +9796,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -9928,22 +9812,22 @@
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P102" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>2</v>
-      </c>
       <c r="R102" t="n">
-        <v>2</v>
+        <v>131</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -9952,12 +9836,12 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>1217647474</t>
+          <t>2049561266</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1217647474</t>
+          <t>https://m.place.naver.com/place/2049561266</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -9974,25 +9858,29 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>네일, 온미</t>
+          <t>네일온</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>cjsdks518@naver.com</t>
+          <t>nailon22@naver.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0507-1331-5593</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세검정로 93 . 1층 네일샵</t>
+          <t>서울특별시 서대문구 충정로9길 4 2층(충정로2가)</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_onme_/</t>
+          <t>https://blog.naver.com/nailon22</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -10007,7 +9895,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -10027,13 +9915,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>10</v>
+        <v>447</v>
       </c>
       <c r="Q103" t="n">
-        <v>3</v>
+        <v>131</v>
       </c>
       <c r="R103" t="n">
-        <v>13</v>
+        <v>578</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -10042,12 +9930,12 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>1881659470</t>
+          <t>1272307920</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1881659470</t>
+          <t>https://m.place.naver.com/place/1272307920</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
@@ -10064,34 +9952,34 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>수네일</t>
+          <t>지젤네일</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>yjh1000j@naver.com</t>
+          <t>shinesparis@naver.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>0507-1332-4612</t>
+          <t>0507-1339-4329</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로10길 16-20 1층</t>
+          <t>서울특별시 서대문구 신촌역로 16 1층 104-1호 지젤네일</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lovely.sunail</t>
+          <t>https://booking.kakao.com/short/lBeB2nWTzo</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -10121,13 +10009,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>334</v>
+        <v>32</v>
       </c>
       <c r="Q104" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R104" t="n">
-        <v>341</v>
+        <v>33</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -10136,12 +10024,12 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>1027173445</t>
+          <t>1215364308</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027173445</t>
+          <t>https://m.place.naver.com/place/1215364308</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
@@ -10158,29 +10046,29 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>온더네일스</t>
+          <t>네일소솜</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>k14150@naver.com</t>
+          <t>wnzhd1203@naver.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0507-1330-5812</t>
+          <t>0507-1430-3550</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 400 2F</t>
+          <t>서울특별시 서대문구 이화여대길 88-15 1층 왼편점포호</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_onthenails</t>
+          <t>https://www.instagram.com/nailsosom</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10215,13 +10103,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>142</v>
+        <v>218</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R105" t="n">
-        <v>142</v>
+        <v>220</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -10230,12 +10118,12 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>1484695115</t>
+          <t>1529665185</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1484695115</t>
+          <t>https://m.place.naver.com/place/1529665185</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
@@ -10252,29 +10140,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>네일뿐</t>
+          <t>로렐네일</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>cuiyushan20-19@naver.com</t>
+          <t>mchavzezy@naver.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0507-1487-1503</t>
+          <t>0507-1436-9020</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 127 2층 205호</t>
+          <t>서울특별시 서대문구 이화여대3길 45 리브하임 B1층 로렐</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Fhxemxj</t>
+          <t>http://pf.kakao.com/_xcXaxgn/friend</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -10309,13 +10197,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>18</v>
+        <v>233</v>
       </c>
       <c r="Q106" t="n">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="R106" t="n">
-        <v>33</v>
+        <v>319</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -10324,12 +10212,12 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>1627245540</t>
+          <t>1883098019</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1627245540</t>
+          <t>https://m.place.naver.com/place/1883098019</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -10346,29 +10234,29 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>살롱드선네일</t>
+          <t>곰지네일</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>salonde_seon@naver.com</t>
+          <t>gom_gnail@naver.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0507-1338-2605</t>
+          <t>0507-1323-0257</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 북아현로1가길 20 이편한세상신촌 1단지상가 110호</t>
+          <t>서울특별시 서대문구 세무서길 73 2층 202호</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/gom_gnail</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -10378,7 +10266,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -10394,7 +10282,7 @@
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -10403,13 +10291,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>426</v>
+        <v>185</v>
       </c>
       <c r="Q107" t="n">
-        <v>12</v>
+        <v>136</v>
       </c>
       <c r="R107" t="n">
-        <v>438</v>
+        <v>321</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -10418,12 +10306,12 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>1688455455</t>
+          <t>1468017488</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1688455455</t>
+          <t>https://m.place.naver.com/place/1468017488</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
@@ -10440,29 +10328,25 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>아모이네일스튜디오</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>soom_mi@naver.com</t>
-        </is>
-      </c>
+          <t>네일살롱무아</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0507-1439-5957</t>
+          <t>0507-1436-1705</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로27길 43 1층 102호</t>
+          <t>서울특별시 서대문구 신촌로 109 신촌르메이에르타운 5차 1층 110-1-2</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailmuah_</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -10472,7 +10356,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -10488,7 +10372,7 @@
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -10497,13 +10381,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="Q108" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R108" t="n">
-        <v>22</v>
+        <v>105</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -10512,12 +10396,12 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>2066634292</t>
+          <t>1027772524</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2066634292</t>
+          <t>https://m.place.naver.com/place/1027772524</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
@@ -10534,29 +10418,29 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>세컨드네일</t>
+          <t>루블리뷰티</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>nail2nd@naver.com</t>
+          <t>i_believe28@naver.com</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0507-1395-7369</t>
+          <t>0507-1352-9350</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 홍연길 69 1층 세컨드네일</t>
+          <t>서울특별시 서대문구 연세로 27 3층</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lu_vely_beauty</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -10566,7 +10450,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -10576,14 +10460,10 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4s321</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr">
         <is>
           <t>X</t>
@@ -10595,13 +10475,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>206</v>
+        <v>80</v>
       </c>
       <c r="Q109" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="R109" t="n">
-        <v>211</v>
+        <v>96</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -10610,12 +10490,12 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>1131608621</t>
+          <t>1078815275</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1131608621</t>
+          <t>https://m.place.naver.com/place/1078815275</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
@@ -10632,29 +10512,25 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>곰지네일</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>gom_gnail@naver.com</t>
-        </is>
-      </c>
+          <t>컬러라운지 네일&amp;태닝</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>0507-1323-0257</t>
+          <t>02-395-1196</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세무서길 73 2층 202호</t>
+          <t>서울특별시 서대문구 통일로 461 2층</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>http://instagram.com/gom_gnail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -10664,7 +10540,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -10680,22 +10556,22 @@
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P110" t="n">
-        <v>185</v>
+        <v>14</v>
       </c>
       <c r="Q110" t="n">
-        <v>136</v>
+        <v>1</v>
       </c>
       <c r="R110" t="n">
-        <v>321</v>
+        <v>15</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -10704,12 +10580,12 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>1468017488</t>
+          <t>13118581</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1468017488</t>
+          <t>https://m.place.naver.com/place/13118581</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -10726,34 +10602,34 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>리즈네일</t>
+          <t>꽃물 네일 &amp; 속눈썹 &amp; 왁싱</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>jozzin@naver.com</t>
+          <t>ddalgy00@naver.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>0507-1491-2458</t>
+          <t>02-394-4141</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로7안길 1 3층</t>
+          <t>서울특별시 서대문구 통일로 420 2층</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_KQAFn</t>
+          <t>https://www.instagram.com/kina8843/</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -10774,7 +10650,7 @@
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -10783,13 +10659,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Q111" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R111" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -10798,12 +10674,12 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>2007984773</t>
+          <t>882778770</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2007984773</t>
+          <t>https://m.place.naver.com/place/882778770</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
@@ -10820,20 +10696,20 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>네일홍</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>jjanga4774@naver.com</t>
-        </is>
-      </c>
+          <t>티파니네일</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>0507-1328-8847</t>
+        </is>
+      </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 서소문로 21 충정타워빌딩 지하1층</t>
+          <t>서울특별시 서대문구 독립문로 34-1 티파니 네일</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -10873,13 +10749,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>126</v>
+        <v>11</v>
       </c>
       <c r="Q112" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="R112" t="n">
-        <v>151</v>
+        <v>12</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -10888,12 +10764,12 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>35624131</t>
+          <t>1601161816</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35624131</t>
+          <t>https://m.place.naver.com/place/1601161816</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
@@ -10910,29 +10786,25 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>코이네일</t>
+          <t>오늘네일</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>rladbal0548@naver.com</t>
+          <t>barbie0903@naver.com</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>0507-1494-6711</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 세검정로 46 1층 9호</t>
+          <t>서울특별시 서대문구 이화여대5길 9 2층</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/ilovetan_oneulnail</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10942,7 +10814,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -10952,17 +10824,13 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5imkv</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -10971,13 +10839,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>163</v>
+        <v>10</v>
       </c>
       <c r="Q113" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>182</v>
+        <v>10</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -10986,12 +10854,12 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>1956411597</t>
+          <t>1348096581</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1956411597</t>
+          <t>https://m.place.naver.com/place/1348096581</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
@@ -11008,29 +10876,25 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>위드네일</t>
+          <t>모모네일</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>hahaha_1226@naver.com</t>
+          <t>brenda70@naver.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>0507-1308-2035</t>
-        </is>
-      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 홍제천로 158 1층</t>
+          <t>서울특별시 서대문구 통일로36가길 13-2 1층 일부호</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/_momo__nail</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -11040,7 +10904,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -11050,17 +10914,13 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wlqexlj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -11069,13 +10929,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>27</v>
+        <v>157</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>27</v>
+        <v>157</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -11084,12 +10944,12 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>2099359388</t>
+          <t>1284552321</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099359388</t>
+          <t>https://m.place.naver.com/place/1284552321</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
@@ -11106,29 +10966,25 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>컬러라운지 네일&amp;태닝</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>brushlounge@naver.com</t>
-        </is>
-      </c>
+          <t>보라다</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>02-395-1196</t>
+          <t>02-303-3188</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 461 2층</t>
+          <t>서울특별시 서대문구 증가로25길 11 1층 보라다</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/iam.borada</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -11138,7 +10994,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -11159,17 +11015,17 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P115" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="Q115" t="n">
-        <v>1</v>
+        <v>142</v>
       </c>
       <c r="R115" t="n">
-        <v>15</v>
+        <v>183</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -11178,12 +11034,12 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>13118581</t>
+          <t>34484907</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13118581</t>
+          <t>https://m.place.naver.com/place/34484907</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
@@ -11200,29 +11056,25 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>네일 소아나</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>yooree890@naver.com</t>
-        </is>
-      </c>
+          <t>글리밍네일</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>0507-1363-1483</t>
+          <t>02-312-7769</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대5길 35 지하1층 104호</t>
+          <t>서울특별시 서대문구 신촌로35길 10 e편한세상신촌상가 지하1층 글리밍네일</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/gleaming_nail</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -11232,7 +11084,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -11242,17 +11094,13 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wu266kp</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -11261,13 +11109,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="Q116" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="R116" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -11276,12 +11124,12 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>2057189903</t>
+          <t>302039845</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2057189903</t>
+          <t>https://m.place.naver.com/place/302039845</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
@@ -11298,29 +11146,29 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>글리밍네일</t>
+          <t>공간네일 신촌점</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>tomi6@naver.com</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>02-312-7769</t>
+          <t>0507-1367-0798</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로35길 10 e편한세상신촌상가 지하1층 글리밍네일</t>
+          <t>서울특별시 서대문구 명물길 49 3층</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/gleaming_nail</t>
+          <t>https://linktr.ee/gonggan_sc</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -11335,7 +11183,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -11346,22 +11194,22 @@
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P117" t="n">
-        <v>61</v>
+        <v>1760</v>
       </c>
       <c r="Q117" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="R117" t="n">
-        <v>104</v>
+        <v>1813</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -11370,12 +11218,12 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>302039845</t>
+          <t>1412908076</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/302039845</t>
+          <t>https://m.place.naver.com/place/1412908076</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
@@ -11392,29 +11240,25 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>안젤리크네일</t>
+          <t>네일홍</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>webmore@naver.com</t>
+          <t>jjanga4774@naver.com</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>070-8648-3432</t>
-        </is>
-      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 북아현동 199-1 힐스테이트신촌상가 105호</t>
+          <t>서울특별시 서대문구 서소문로 21 충정타워빌딩 지하1층</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/jjanga4774</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -11424,12 +11268,12 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -11440,7 +11284,7 @@
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -11449,13 +11293,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="Q118" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="R118" t="n">
-        <v>44</v>
+        <v>151</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -11464,12 +11308,12 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>1976256692</t>
+          <t>35624131</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1976256692</t>
+          <t>https://m.place.naver.com/place/35624131</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
@@ -11486,29 +11330,29 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>손에담다</t>
+          <t>네일오엔</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>kjy88990@naver.com</t>
+          <t>checkmate_out@naver.com</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>0507-1307-7876</t>
+          <t>0507-1362-3291</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 153 손에담다</t>
+          <t>서울특별시 서대문구 연세로7길 58 102호</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail.oen?igsh=c2poN3MxZG5kcmR1&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -11518,7 +11362,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -11528,17 +11372,13 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4gro9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -11547,13 +11387,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="R119" t="n">
-        <v>163</v>
+        <v>3</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -11562,12 +11402,12 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>1681218410</t>
+          <t>1478444590</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1681218410</t>
+          <t>https://m.place.naver.com/place/1478444590</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
@@ -11584,25 +11424,29 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>한예진뷰티디자인</t>
+          <t>소우네일</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>bijou-artist@naver.com</t>
+          <t>snflcjswo54@naver.com</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>0507-1328-7467</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 189</t>
+          <t>서울특별시 서대문구 연희맛로 7-17 1층 202호</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/sounail__</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -11612,7 +11456,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -11633,17 +11477,17 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P120" t="n">
         <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -11652,12 +11496,12 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>1388645750</t>
+          <t>2021939074</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1388645750</t>
+          <t>https://m.place.naver.com/place/2021939074</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
@@ -11674,29 +11518,29 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>The서이</t>
+          <t>더 꼼네일</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>premier-music@naver.com</t>
+          <t>kjuuu0716@naver.com</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>0507-1410-5589</t>
+          <t>0507-1322-3992</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 수색로 100 DMC레미안e편한세상 103동상가 2호</t>
+          <t>서울특별시 서대문구 명지대길 56 1층</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/the_kkom</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -11706,7 +11550,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -11727,17 +11571,17 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P121" t="n">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="Q121" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="R121" t="n">
-        <v>9</v>
+        <v>146</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -11746,12 +11590,12 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>33928722</t>
+          <t>1616221232</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33928722</t>
+          <t>https://m.place.naver.com/place/1616221232</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
@@ -11768,29 +11612,29 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>마디마다네일</t>
+          <t>BK민방경네일</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>z1004__@naver.com</t>
+          <t>acquidigio7@naver.com</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>0507-1326-2539</t>
+          <t>02-393-7449</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 149 206호</t>
+          <t>서울특별시 서대문구 이화여대길 82 2층</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/madi_mada_nail/</t>
+          <t>https://blog.naver.com/acquidigio7</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -11805,7 +11649,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -11825,13 +11669,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>804</v>
+        <v>552</v>
       </c>
       <c r="Q122" t="n">
-        <v>17</v>
+        <v>1153</v>
       </c>
       <c r="R122" t="n">
-        <v>821</v>
+        <v>1705</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -11840,12 +11684,12 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>1156545059</t>
+          <t>38314950</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156545059</t>
+          <t>https://m.place.naver.com/place/38314950</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
@@ -11862,29 +11706,25 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>루나네일</t>
+          <t>마요네일</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>lunamika@naver.com</t>
+          <t>ynh3377@naver.com</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>0507-1329-7109</t>
-        </is>
-      </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 가재울미래로 15 1층 103호 루나네일</t>
+          <t>서울특별시 서대문구 연희로11가길 33-3 1층</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>http://instagram.com/lunarnail__</t>
+          <t>https://www.instagram.com/mayonail_official</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -11919,13 +11759,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R123" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -11934,12 +11774,12 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>1427499799</t>
+          <t>1434998291</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1427499799</t>
+          <t>https://m.place.naver.com/place/1434998291</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
@@ -11956,29 +11796,29 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>굥뷰티</t>
+          <t>오네일드잇 신촌점</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>sunday020@naver.com</t>
+          <t>travelsudal@naver.com</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>0505-685-7683</t>
+          <t>0507-1379-5740</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌역로 10</t>
+          <t>서울특별시 서대문구 신촌로 123 2층</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/oh_nailed_it</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -11988,7 +11828,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -12009,17 +11849,17 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>603</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -12028,12 +11868,12 @@
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>1137345145</t>
+          <t>1930241791</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1137345145</t>
+          <t>https://m.place.naver.com/place/1930241791</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
@@ -12050,29 +11890,29 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>베이네일</t>
+          <t>세컨드네일</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>4chi_27@naver.com</t>
+          <t>nail2nd@naver.com</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>0507-1337-7446</t>
+          <t>0507-1395-7369</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 증가로 217</t>
+          <t>서울특별시 서대문구 홍연길 69 1층 세컨드네일</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/baeynail</t>
+          <t>https://www.instagram.com/xecond_nail</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -12107,13 +11947,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>138</v>
+        <v>206</v>
       </c>
       <c r="Q125" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R125" t="n">
-        <v>139</v>
+        <v>211</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -12122,12 +11962,12 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>1239283152</t>
+          <t>1131608621</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1239283152</t>
+          <t>https://m.place.naver.com/place/1131608621</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
@@ -12144,29 +11984,25 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>공간네일 신촌점</t>
+          <t>코알라네일</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>tomi6@naver.com</t>
+          <t>zhdkffkekfekfo@naver.com</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>0507-1367-0798</t>
-        </is>
-      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 명물길 49 3층</t>
+          <t>서울특별시 서대문구 홍제원3길 17 1층 가운데호</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://linktr.ee/gonggan_sc</t>
+          <t>https://www.instagram.com/___nail.by.koala?igsh=MWpjaDB0MjIyNHBzcw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -12181,7 +12017,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -12197,17 +12033,17 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P126" t="n">
-        <v>1760</v>
+        <v>25</v>
       </c>
       <c r="Q126" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="R126" t="n">
-        <v>1813</v>
+        <v>27</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -12216,12 +12052,12 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>1412908076</t>
+          <t>1997616944</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1412908076</t>
+          <t>https://m.place.naver.com/place/1997616944</t>
         </is>
       </c>
       <c r="V126" t="inlineStr">
